--- a/output/faculty_requests/SCI - SR26 sustainability reporting request.xlsx
+++ b/output/faculty_requests/SCI - SR26 sustainability reporting request.xlsx
@@ -627,7 +627,7 @@
     <col width="38" customWidth="1" min="5" max="5"/>
     <col width="50" customWidth="1" min="6" max="6"/>
     <col width="34" customWidth="1" min="7" max="7"/>
-    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
     <col hidden="1" width="16" customWidth="1" min="9" max="9"/>
     <col hidden="1" width="50" customWidth="1" min="10" max="10"/>
     <col hidden="1" width="24" customWidth="1" min="11" max="11"/>
@@ -648,7 +648,7 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
-          <t>End-2026 target status assessment and reporting (v0.12)</t>
+          <t>End-2026 target status assessment and reporting (v0.13)</t>
         </is>
       </c>
     </row>
@@ -756,7 +756,7 @@
       </c>
       <c r="H13" s="12" t="inlineStr">
         <is>
-          <t>End-2025 reporting (click the ref to see your full SR25 response)</t>
+          <t>SR25 response</t>
         </is>
       </c>
       <c r="L13" s="13" t="inlineStr">
@@ -1451,9 +1451,8 @@
     <row r="25"/>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="1"/>
-  <mergeCells count="10">
+  <mergeCells count="9">
     <mergeCell ref="M7:N7"/>
-    <mergeCell ref="H13:K13"/>
     <mergeCell ref="B4:C8"/>
     <mergeCell ref="M6:N6"/>
     <mergeCell ref="L13:R13"/>

--- a/output/faculty_requests/SCI - SR26 sustainability reporting request.xlsx
+++ b/output/faculty_requests/SCI - SR26 sustainability reporting request.xlsx
@@ -20,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="20">
+  <fonts count="18">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -78,18 +78,6 @@
       <sz val="11"/>
     </font>
     <font>
-      <name val="Aptos"/>
-      <b val="1"/>
-    </font>
-    <font>
-      <name val="Aptos"/>
-    </font>
-    <font>
-      <name val="Aptos"/>
-      <i val="1"/>
-      <sz val="9"/>
-    </font>
-    <font>
       <name val="Aptos Narrow"/>
       <b val="1"/>
       <sz val="22"/>
@@ -125,8 +113,12 @@
       <sz val="11"/>
       <u val="single"/>
     </font>
+    <font>
+      <name val="Aptos"/>
+      <b val="1"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -146,11 +138,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00C1E4F5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00D9D9D9"/>
       </patternFill>
     </fill>
     <fill>
@@ -191,38 +178,31 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -234,13 +214,14 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
       <protection locked="0" hidden="0"/>
     </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -617,7 +598,7 @@
     <outlinePr summaryBelow="1" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R25"/>
+  <dimension ref="A1:Q25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -631,13 +612,12 @@
     <col hidden="1" width="16" customWidth="1" min="9" max="9"/>
     <col hidden="1" width="50" customWidth="1" min="10" max="10"/>
     <col hidden="1" width="24" customWidth="1" min="11" max="11"/>
-    <col width="22" customWidth="1" min="12" max="12"/>
+    <col width="48" customWidth="1" min="12" max="12"/>
     <col width="48" customWidth="1" min="13" max="13"/>
-    <col width="48" customWidth="1" min="14" max="14"/>
+    <col width="30" customWidth="1" min="14" max="14"/>
     <col width="30" customWidth="1" min="15" max="15"/>
-    <col width="30" customWidth="1" min="16" max="16"/>
-    <col width="20" customWidth="1" min="17" max="17"/>
-    <col width="24" customWidth="1" min="18" max="18"/>
+    <col width="20" customWidth="1" min="16" max="16"/>
+    <col width="24" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -648,304 +628,232 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
-          <t>End-2026 target status assessment and reporting (v0.13)</t>
+          <t>SR26 sustainability reporting (v0.14)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>End-2026 target status confirmation and reporting</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="L3" s="4" t="inlineStr">
-        <is>
-          <t>Target status assessment and definitions</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="32" customHeight="1">
-      <c r="B4" s="5" t="inlineStr">
+          <t>SR26 sustainability reporting request</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" s="4" t="inlineStr">
         <is>
           <t>How to use this spreadsheet:</t>
         </is>
       </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>• Confirm target status for each row below (Column L). Refer to target status definitions to the right for guidance.
-• Provide commentary on progress towards each target (Column M or N)
-• Provide supporting documentation if required (Column O), including links to images
-• Note the source of your information and any limitations (Column P), then confirm the information is accurate (Columns Q–R)
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>• For each row below, describe progress towards the target (Column L) and/or respond to the 2026 reporting request (Column M)
+• Provide supporting information if required (Column N), including links to documents or images
+• Note the source of your information and any limitations (Column O), then confirm the information is accurate (Columns P–Q)
 • Where a related end-2025 target existed, click the ref in Column H to see your full SR25 response (Tab 3)
 • Use Tab 2 of this spreadsheet to highlight key sustainability stories (optional)
-• 2026 is a transition year: Sustainability 2030 launched ~20 October 2026, so report on activity across all of 2026 and any early actions since launch.
+• 2026 is a transition year: Sustainability 2030 launched ~20 October 2026, so report on activity across all of 2026 and any early actions since launch. No target status rating is requested this year.
 • Due: Tuesday 15 December 2026. Questions: CDSS – questions and clarifications are recorded centrally (contact email TBC); optional 1:1 meetings available on request</t>
         </is>
       </c>
-      <c r="L4" s="7" t="inlineStr">
-        <is>
-          <t>Met or exceeded</t>
-        </is>
-      </c>
-      <c r="M4" s="8" t="inlineStr">
-        <is>
-          <t>The data and information provided demonstrates that the Faculty/Portfolio has met or exceeded the target</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="32" customHeight="1">
-      <c r="L5" s="7" t="inlineStr">
-        <is>
-          <t>Partially met</t>
-        </is>
-      </c>
-      <c r="M5" s="8" t="inlineStr">
-        <is>
-          <t>The data and information provided indicates that the target has not been met, but there has been a significant improvement and performance is trending towards the target</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="32" customHeight="1">
-      <c r="L6" s="7" t="inlineStr">
-        <is>
-          <t>Not met</t>
-        </is>
-      </c>
-      <c r="M6" s="8" t="inlineStr">
-        <is>
-          <t>Some action has been taken to address the target, but the data and information provided demonstrates that this has been insufficient to meet the target</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="32" customHeight="1">
-      <c r="L7" s="7" t="inlineStr">
-        <is>
-          <t>Not yet started</t>
-        </is>
-      </c>
-      <c r="M7" s="8" t="inlineStr">
-        <is>
-          <t>No action has been taken.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="60" customHeight="1">
-      <c r="L8" s="9" t="n"/>
-    </row>
-    <row r="9">
-      <c r="L9" s="10" t="inlineStr">
-        <is>
-          <t>Note: target status definitions are under review for 2027 reporting. 2026 ratings are for internal management reporting only.</t>
-        </is>
-      </c>
-    </row>
+    </row>
+    <row r="5"/>
+    <row r="6"/>
+    <row r="7"/>
+    <row r="8" ht="60" customHeight="1"/>
     <row r="11">
-      <c r="B11" s="11" t="inlineStr">
+      <c r="B11" s="6" t="inlineStr">
         <is>
           <t>SCI – Faculty of Science</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="C13" s="12" t="inlineStr">
+      <c r="C13" s="7" t="inlineStr">
         <is>
           <t>Sustainability 2030 target and indicator</t>
         </is>
       </c>
-      <c r="H13" s="12" t="inlineStr">
+      <c r="H13" s="7" t="inlineStr">
         <is>
           <t>SR25 response</t>
         </is>
       </c>
-      <c r="L13" s="13" t="inlineStr">
+      <c r="L13" s="8" t="inlineStr">
         <is>
           <t>End-2026 reporting (PLEASE COMPLETE THIS SECTION)</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="14" t="inlineStr">
+      <c r="B14" s="9" t="inlineStr">
         <is>
           <t>Ref</t>
         </is>
       </c>
-      <c r="C14" s="14" t="inlineStr">
+      <c r="C14" s="9" t="inlineStr">
         <is>
           <t>Priority area</t>
         </is>
       </c>
-      <c r="D14" s="14" t="inlineStr">
+      <c r="D14" s="9" t="inlineStr">
         <is>
           <t>Sustainability 2030 target</t>
         </is>
       </c>
-      <c r="E14" s="14" t="inlineStr">
+      <c r="E14" s="9" t="inlineStr">
         <is>
           <t>Indicator</t>
         </is>
       </c>
-      <c r="F14" s="14" t="inlineStr">
+      <c r="F14" s="9" t="inlineStr">
         <is>
           <t>2026 Reporting request</t>
         </is>
       </c>
-      <c r="G14" s="14" t="inlineStr">
+      <c r="G14" s="9" t="inlineStr">
         <is>
           <t>How SST will use this data</t>
         </is>
       </c>
-      <c r="H14" s="14" t="inlineStr">
+      <c r="H14" s="9" t="inlineStr">
         <is>
           <t>Related SR25 ref</t>
         </is>
       </c>
-      <c r="I14" s="14" t="inlineStr">
+      <c r="I14" s="9" t="inlineStr">
         <is>
           <t>End-2025 confirmed status</t>
         </is>
       </c>
-      <c r="J14" s="14" t="inlineStr">
+      <c r="J14" s="9" t="inlineStr">
         <is>
           <t>End-2025 reporting response</t>
         </is>
       </c>
-      <c r="K14" s="14" t="inlineStr">
+      <c r="K14" s="9" t="inlineStr">
         <is>
           <t>Links and supporting information</t>
         </is>
       </c>
-      <c r="L14" s="15" t="inlineStr">
-        <is>
-          <t>Confirm end-2026 target status</t>
-        </is>
-      </c>
-      <c r="M14" s="15" t="inlineStr">
+      <c r="L14" s="10" t="inlineStr">
         <is>
           <t>OPTION 1:  Target-level reporting (Column D)</t>
         </is>
       </c>
-      <c r="N14" s="15" t="inlineStr">
+      <c r="M14" s="10" t="inlineStr">
         <is>
           <t>OPTION 2:  Indicator level reporting (Column E/F)</t>
         </is>
       </c>
-      <c r="O14" s="15" t="inlineStr">
+      <c r="N14" s="10" t="inlineStr">
         <is>
           <t>Supporting information/comments</t>
         </is>
       </c>
-      <c r="P14" s="15" t="inlineStr">
+      <c r="O14" s="10" t="inlineStr">
         <is>
           <t>Data source and limitations</t>
         </is>
       </c>
-      <c r="Q14" s="15" t="inlineStr">
+      <c r="P14" s="10" t="inlineStr">
         <is>
           <t>Data owner confirms information is accurate</t>
         </is>
       </c>
-      <c r="R14" s="15" t="inlineStr">
+      <c r="Q14" s="10" t="inlineStr">
         <is>
           <t>Confirmed by (name, role, date)</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="B15" s="16" t="inlineStr"/>
-      <c r="C15" s="16" t="inlineStr"/>
-      <c r="D15" s="16" t="inlineStr"/>
-      <c r="E15" s="16" t="inlineStr"/>
-      <c r="F15" s="16" t="inlineStr"/>
-      <c r="G15" s="16" t="inlineStr"/>
-      <c r="H15" s="16" t="inlineStr"/>
-      <c r="I15" s="16" t="inlineStr"/>
-      <c r="J15" s="16" t="inlineStr"/>
-      <c r="K15" s="16" t="inlineStr"/>
-      <c r="L15" s="16" t="inlineStr">
-        <is>
-          <t>(Met or exceeded; partially met; not met; not yet started)</t>
-        </is>
-      </c>
-      <c r="M15" s="16" t="inlineStr">
-        <is>
-          <t>Provide further evidence of target status assessment in the form of:
-A general update on activities in relation to the overarching target (Column D)</t>
-        </is>
-      </c>
-      <c r="N15" s="16" t="inlineStr">
-        <is>
-          <t>Provide further evidence of target status assessment in the form of:
-Data and commentary in direct response to the reporting request (Column F)</t>
-        </is>
-      </c>
-      <c r="O15" s="16" t="inlineStr">
-        <is>
-          <t>Provide any additional information to support the target status assessment (e.g. links, images, rationale for selection of target status)</t>
-        </is>
-      </c>
-      <c r="P15" s="16" t="inlineStr">
+      <c r="B15" s="11" t="inlineStr"/>
+      <c r="C15" s="11" t="inlineStr"/>
+      <c r="D15" s="11" t="inlineStr"/>
+      <c r="E15" s="11" t="inlineStr"/>
+      <c r="F15" s="11" t="inlineStr"/>
+      <c r="G15" s="11" t="inlineStr"/>
+      <c r="H15" s="11" t="inlineStr"/>
+      <c r="I15" s="11" t="inlineStr"/>
+      <c r="J15" s="11" t="inlineStr"/>
+      <c r="K15" s="11" t="inlineStr"/>
+      <c r="L15" s="11" t="inlineStr">
+        <is>
+          <t>A general update on activities in relation to the overarching target (Column D)</t>
+        </is>
+      </c>
+      <c r="M15" s="11" t="inlineStr">
+        <is>
+          <t>Data and commentary in direct response to the reporting request (Column F)</t>
+        </is>
+      </c>
+      <c r="N15" s="11" t="inlineStr">
+        <is>
+          <t>Any additional information (e.g. links, images, documents)</t>
+        </is>
+      </c>
+      <c r="O15" s="11" t="inlineStr">
         <is>
           <t>Where did this information come from (system, report, survey, person)? Note any gaps or limitations.</t>
         </is>
       </c>
-      <c r="Q15" s="16" t="inlineStr">
+      <c r="P15" s="11" t="inlineStr">
         <is>
           <t>Select 'Yes' to confirm the information provided is accurate and can be used for reporting</t>
         </is>
       </c>
-      <c r="R15" s="16" t="inlineStr">
+      <c r="Q15" s="11" t="inlineStr">
         <is>
           <t>Name, role and date of the person confirming</t>
         </is>
       </c>
     </row>
     <row r="16" ht="150" customHeight="1">
-      <c r="B16" s="17" t="inlineStr">
+      <c r="B16" s="12" t="inlineStr">
         <is>
           <t>EE1(a)</t>
         </is>
       </c>
-      <c r="C16" s="18" t="inlineStr">
+      <c r="C16" s="13" t="inlineStr">
         <is>
           <t>Exceptional education</t>
         </is>
       </c>
-      <c r="D16" s="18" t="inlineStr">
+      <c r="D16" s="13" t="inlineStr">
         <is>
           <t>Provide our students with learning experiences that help them build the knowledge, skills and relationships to lead change for sustainable societies.</t>
         </is>
       </c>
-      <c r="E16" s="18" t="inlineStr">
+      <c r="E16" s="13" t="inlineStr">
         <is>
           <t>Evidence of innovative approaches to sustainability teaching and learning</t>
         </is>
       </c>
-      <c r="F16" s="19" t="inlineStr">
-        <is>
-          <t>In end-2025 reporting your faculty reported on the related SP2030 target 4a(ii) and rated it 'Met or exceeded' (click the ref in Column H to see it in full in Tab 3). Please build on this rather than repeating it, focusing on what is new in 2026.
+      <c r="F16" s="14" t="inlineStr">
+        <is>
+          <t>In end-2025 reporting your faculty reported on the related SP2030 target 4a(ii) (click the ref in Column H to see it in full in Tab 3). Please build on this rather than repeating it, focusing on what is new in 2026.
 Please give any examples from 2026 of how your faculty has embedded sustainability in teaching and learning. This could include innovative approaches (e.g. new or redesigned subjects, curriculum design, pedagogies, assessment or learning resources) and sustainability-focused experiential or co-curricular learning (e.g. industry or community projects, fieldwork, internships, student challenges). Include links and approximate student participation where known.
 This question also covers indicator EE1(c). Melbourne Plus and the Wattle Fellowship will be collected separately – no need to report these.</t>
         </is>
       </c>
-      <c r="G16" s="19" t="inlineStr">
+      <c r="G16" s="14" t="inlineStr">
         <is>
           <t>We will collate examples of sustainability teaching and learning, including experiential and co-curricular learning, across faculties to inform the Exceptional education section of the 2026 Sustainability Report. Strong examples may be followed up for the report.</t>
         </is>
       </c>
-      <c r="H16" s="20" t="inlineStr">
+      <c r="H16" s="15" t="inlineStr">
         <is>
           <t>4a(ii)
 → view SR25 response</t>
         </is>
       </c>
-      <c r="I16" s="19" t="inlineStr">
+      <c r="I16" s="14" t="inlineStr">
         <is>
           <t>Met or exceeded</t>
         </is>
       </c>
-      <c r="J16" s="19" t="inlineStr">
+      <c r="J16" s="14" t="inlineStr">
         <is>
           <t>Sustainability, conservation, biodiversity are elements of most courses and majors within the FoS. Several additional courses are being considered at PG level in 2026
 The FoS education strategy https://staff.unimelb.edu.au/science/learning-and-teaching-support/education-strategy has been developed with the following targets related to sustainability:  
@@ -955,108 +863,106 @@
 With the 12 month implementation plan noting that: "Understanding our students’ carbon footprint is the first step towards incorporating sustainability in teaching and learning."</t>
         </is>
       </c>
-      <c r="K16" s="19" t="inlineStr"/>
-      <c r="L16" s="21" t="n"/>
-      <c r="M16" s="21" t="n"/>
-      <c r="N16" s="21" t="n"/>
-      <c r="O16" s="21" t="n"/>
-      <c r="P16" s="21" t="n"/>
-      <c r="Q16" s="21" t="n"/>
-      <c r="R16" s="21" t="n"/>
+      <c r="K16" s="14" t="inlineStr"/>
+      <c r="L16" s="16" t="n"/>
+      <c r="M16" s="16" t="n"/>
+      <c r="N16" s="16" t="n"/>
+      <c r="O16" s="16" t="n"/>
+      <c r="P16" s="16" t="n"/>
+      <c r="Q16" s="16" t="n"/>
     </row>
     <row r="17" ht="150" customHeight="1">
-      <c r="B17" s="17" t="inlineStr">
+      <c r="B17" s="12" t="inlineStr">
         <is>
           <t>EE1(b)</t>
         </is>
       </c>
-      <c r="C17" s="18" t="inlineStr">
+      <c r="C17" s="13" t="inlineStr">
         <is>
           <t>Exceptional education</t>
         </is>
       </c>
-      <c r="D17" s="18" t="inlineStr">
+      <c r="D17" s="13" t="inlineStr">
         <is>
           <t>Provide our students with learning experiences that help them build the knowledge, skills and relationships to lead change for sustainable societies.</t>
         </is>
       </c>
-      <c r="E17" s="18" t="inlineStr">
+      <c r="E17" s="13" t="inlineStr">
         <is>
           <t>Pilots of possible approaches for understanding and developing students’ sustainability self-efficacy</t>
         </is>
       </c>
-      <c r="F17" s="19" t="inlineStr">
+      <c r="F17" s="14" t="inlineStr">
         <is>
           <t>Has your faculty piloted or trialled any approach in 2026 to understand or build students' confidence and capability to act on sustainability (sustainability self-efficacy)? If yes, briefly describe the approach, participating cohort, what was learned and next steps. If not, please respond 'none in 2026' – this is a new indicator and a nil response is useful.
 We are aware of the Sustainability Strengths Compass Living Lab project (CLLAP) and will collect it separately.</t>
         </is>
       </c>
-      <c r="G17" s="19" t="inlineStr">
+      <c r="G17" s="14" t="inlineStr">
         <is>
           <t>This is a new indicator. We will use responses to establish a baseline of how (and whether) faculties are understanding student sustainability self-efficacy, and report on early pilots in the 2026 Sustainability Report. A nil response is useful to us.</t>
         </is>
       </c>
-      <c r="H17" s="19" t="inlineStr">
+      <c r="H17" s="14" t="inlineStr">
         <is>
           <t>N/A – new indicator</t>
         </is>
       </c>
-      <c r="I17" s="19" t="inlineStr"/>
-      <c r="J17" s="19" t="inlineStr"/>
-      <c r="K17" s="19" t="inlineStr"/>
-      <c r="L17" s="21" t="n"/>
-      <c r="M17" s="21" t="n"/>
-      <c r="N17" s="21" t="n"/>
-      <c r="O17" s="21" t="n"/>
-      <c r="P17" s="21" t="n"/>
-      <c r="Q17" s="21" t="n"/>
-      <c r="R17" s="21" t="n"/>
+      <c r="I17" s="14" t="inlineStr"/>
+      <c r="J17" s="14" t="inlineStr"/>
+      <c r="K17" s="14" t="inlineStr"/>
+      <c r="L17" s="16" t="n"/>
+      <c r="M17" s="16" t="n"/>
+      <c r="N17" s="16" t="n"/>
+      <c r="O17" s="16" t="n"/>
+      <c r="P17" s="16" t="n"/>
+      <c r="Q17" s="16" t="n"/>
     </row>
     <row r="18" ht="150" customHeight="1">
-      <c r="B18" s="17" t="inlineStr">
+      <c r="B18" s="12" t="inlineStr">
         <is>
           <t>TR1(a)</t>
         </is>
       </c>
-      <c r="C18" s="18" t="inlineStr">
+      <c r="C18" s="13" t="inlineStr">
         <is>
           <t>Transformational research</t>
         </is>
       </c>
-      <c r="D18" s="18" t="inlineStr">
+      <c r="D18" s="13" t="inlineStr">
         <is>
           <t>Utilise the expertise of the University’s researchers through mutually beneficial partnerships to help address the University’s operational sustainability challenges.</t>
         </is>
       </c>
-      <c r="E18" s="18" t="inlineStr">
+      <c r="E18" s="13" t="inlineStr">
         <is>
           <t>Expert-reviewed evidence of researchers contributing to operational sustainability priorities through partnerships, advisory input, living labs, applied projects or decision-support</t>
         </is>
       </c>
-      <c r="F18" s="19" t="inlineStr">
-        <is>
-          <t>In end-2025 reporting your faculty reported on the related SP2030 target 2a and rated it 'Partially met' (click the ref in Column H to see it in full in Tab 3). Please build on this rather than repeating it, focusing on what is new in 2026.
+      <c r="F18" s="14" t="inlineStr">
+        <is>
+          <t>In end-2025 reporting your faculty reported on the related SP2030 target 2a (click the ref in Column H to see it in full in Tab 3). Please build on this rather than repeating it, focusing on what is new in 2026.
 Please give any examples from 2026 of researchers in your faculty contributing to the University's own operational sustainability challenges (e.g. advising on campus energy, biodiversity, waste or buildings; applied projects; decision-support tools). Briefly describe the operational challenge, the researchers' contribution, the University team involved and the result.
 We will collect Campus Living Lab Accelerator Program (CLLAP) projects separately from CI&amp;S – please include other examples only.</t>
         </is>
       </c>
-      <c r="G18" s="19" t="inlineStr">
+      <c r="G18" s="14" t="inlineStr">
         <is>
           <t>We will report on examples of researchers helping solve the University's own operational sustainability challenges, alongside CLLAP projects reported by CI&amp;S, and share them with operational teams to identify further collaboration.</t>
         </is>
       </c>
-      <c r="H18" s="20" t="inlineStr">
+      <c r="H18" s="15" t="inlineStr">
         <is>
           <t>2a
 → view SR25 response</t>
         </is>
       </c>
-      <c r="I18" s="19" t="inlineStr">
+      <c r="I18" s="14" t="inlineStr">
         <is>
           <t>Partially met</t>
         </is>
       </c>
-      <c r="J18" s="19" t="inlineStr">
+      <c r="J18" s="14" t="inlineStr">
         <is>
           <t>The faculty has many projects that can be considered living labs. A centralised approach is required to document them.
 2025 examples include how the undergraduate chemistry teaching laboratories redesigned their practicals to use less reagents and safer chemicals to achieve the same learning outcomes.
@@ -1064,65 +970,64 @@
 SAFES have worked on Indigenous food gardens and have an Indigenous food guide and there are examples of urban and woodland greening that serve as best practice examples across Australia</t>
         </is>
       </c>
-      <c r="K18" s="19" t="inlineStr">
+      <c r="K18" s="14" t="inlineStr">
         <is>
           <t>https://www.unimelb.edu.au/newsroom/news/2024/october/native-harvest-cookbook-aims-to-put-indigenous-food-in-every-aussie-kitchen
 https://theconversation.com/we-planted-two-woody-meadows-a-decade-ago-to-see-what-would-thrive-now-the-concept-is-popular-across-australia-269611</t>
         </is>
       </c>
-      <c r="L18" s="21" t="n"/>
-      <c r="M18" s="21" t="n"/>
-      <c r="N18" s="21" t="n"/>
-      <c r="O18" s="21" t="n"/>
-      <c r="P18" s="21" t="n"/>
-      <c r="Q18" s="21" t="n"/>
-      <c r="R18" s="21" t="n"/>
+      <c r="L18" s="16" t="n"/>
+      <c r="M18" s="16" t="n"/>
+      <c r="N18" s="16" t="n"/>
+      <c r="O18" s="16" t="n"/>
+      <c r="P18" s="16" t="n"/>
+      <c r="Q18" s="16" t="n"/>
     </row>
     <row r="19" ht="150" customHeight="1">
-      <c r="B19" s="17" t="inlineStr">
+      <c r="B19" s="12" t="inlineStr">
         <is>
           <t>TR2(a)</t>
         </is>
       </c>
-      <c r="C19" s="18" t="inlineStr">
+      <c r="C19" s="13" t="inlineStr">
         <is>
           <t>Transformational research</t>
         </is>
       </c>
-      <c r="D19" s="18" t="inlineStr">
+      <c r="D19" s="13" t="inlineStr">
         <is>
           <t>Deliver high-quality research and partnerships that contribute to sustainability outcomes and demonstrable societal benefit.</t>
         </is>
       </c>
-      <c r="E19" s="18" t="inlineStr">
+      <c r="E19" s="13" t="inlineStr">
         <is>
           <t>Evidence of sustainability-related research impact across diverse pathways, could include policy, industry, community, practice, cultural and institutional outcomes</t>
         </is>
       </c>
-      <c r="F19" s="19" t="inlineStr">
-        <is>
-          <t>In end-2025 reporting your faculty reported on the related SP2030 target 5b(i) and rated it 'Met or exceeded' (click the ref in Column H to see it in full in Tab 3). Please build on this rather than repeating it, focusing on what is new in 2026.
+      <c r="F19" s="14" t="inlineStr">
+        <is>
+          <t>In end-2025 reporting your faculty reported on the related SP2030 target 5b(i) (click the ref in Column H to see it in full in Tab 3). Please build on this rather than repeating it, focusing on what is new in 2026.
 Please give any examples from 2026 of sustainability-related research from your faculty that has had impact beyond academia – on policy, industry, community, practice, cultural or institutional outcomes. Briefly describe the research, the partner or user, and the resulting change or influence, with links (e.g. Pursuit articles, policy submissions, reports).
 We will source University-wide research metrics (e.g. SDG-mapped publications via SciVal) from MRE – publication counts are not required.</t>
         </is>
       </c>
-      <c r="G19" s="19" t="inlineStr">
+      <c r="G19" s="14" t="inlineStr">
         <is>
           <t>We will collate research impact examples across faculties to show the breadth of sustainability-related research impact in the Transformational research section of the 2026 Sustainability Report, complementing University-wide metrics from MRE.</t>
         </is>
       </c>
-      <c r="H19" s="20" t="inlineStr">
+      <c r="H19" s="15" t="inlineStr">
         <is>
           <t>5b(i)
 → view SR25 response</t>
         </is>
       </c>
-      <c r="I19" s="19" t="inlineStr">
+      <c r="I19" s="14" t="inlineStr">
         <is>
           <t>Met or exceeded</t>
         </is>
       </c>
-      <c r="J19" s="19" t="inlineStr">
+      <c r="J19" s="14" t="inlineStr">
         <is>
           <t>QS rankings, SDG research outputs all attest to our strength in environmental and sustainable research. 
 We have a research strategy which has clear deliverables for sustainability, including a focus on several "Big Research Challenges" which directly relate to Sustainability https://staff.unimelb.edu.au/science/research/research-governance/research-strategy-2023-2030/FOS-Research-strategy-_INTRANET-LINKS-FIXED.pdf
@@ -1132,60 +1037,59 @@
 https://science.unimelb.edu.au/about/news/australia-and-the-pacific-islands-solidarity-in-a-time-of-climate-crisis/_nocache</t>
         </is>
       </c>
-      <c r="K19" s="19" t="inlineStr"/>
-      <c r="L19" s="21" t="n"/>
-      <c r="M19" s="21" t="n"/>
-      <c r="N19" s="21" t="n"/>
-      <c r="O19" s="21" t="n"/>
-      <c r="P19" s="21" t="n"/>
-      <c r="Q19" s="21" t="n"/>
-      <c r="R19" s="21" t="n"/>
+      <c r="K19" s="14" t="inlineStr"/>
+      <c r="L19" s="16" t="n"/>
+      <c r="M19" s="16" t="n"/>
+      <c r="N19" s="16" t="n"/>
+      <c r="O19" s="16" t="n"/>
+      <c r="P19" s="16" t="n"/>
+      <c r="Q19" s="16" t="n"/>
     </row>
     <row r="20" ht="150" customHeight="1">
-      <c r="B20" s="17" t="inlineStr">
+      <c r="B20" s="12" t="inlineStr">
         <is>
           <t>TR2(d)</t>
         </is>
       </c>
-      <c r="C20" s="18" t="inlineStr">
+      <c r="C20" s="13" t="inlineStr">
         <is>
           <t>Transformational research</t>
         </is>
       </c>
-      <c r="D20" s="18" t="inlineStr">
+      <c r="D20" s="13" t="inlineStr">
         <is>
           <t>Deliver high-quality research and partnerships that contribute to sustainability outcomes and demonstrable societal benefit.</t>
         </is>
       </c>
-      <c r="E20" s="18" t="inlineStr">
+      <c r="E20" s="13" t="inlineStr">
         <is>
           <t>Case-based evidence demonstrating how research has contributed to meaningful sustainability outcomes.</t>
         </is>
       </c>
-      <c r="F20" s="19" t="inlineStr">
-        <is>
-          <t>In end-2025 reporting your faculty reported on the related SP2030 target 5b(i) and rated it 'Met or exceeded' (click the ref in Column H to see it in full in Tab 3). Please build on this rather than repeating it, focusing on what is new in 2026.
+      <c r="F20" s="14" t="inlineStr">
+        <is>
+          <t>In end-2025 reporting your faculty reported on the related SP2030 target 5b(i) (click the ref in Column H to see it in full in Tab 3). Please build on this rather than repeating it, focusing on what is new in 2026.
 Please give any examples of research activity from your faculty that has contributed to a meaningful sustainability outcome: the research, stakeholders involved, pathway to impact and evidence of the outcome. These can be the examples from TR2(a) described in more detail.
 We are also seeking examples from Melbourne Climate Futures, the Melbourne Biodiversity Institute and Strategic Communications.</t>
         </is>
       </c>
-      <c r="G20" s="19" t="inlineStr">
+      <c r="G20" s="14" t="inlineStr">
         <is>
           <t>We will select the strongest examples to develop as full research case studies for the 2026 Sustainability Report (we may contact you for more detail and images).</t>
         </is>
       </c>
-      <c r="H20" s="20" t="inlineStr">
+      <c r="H20" s="15" t="inlineStr">
         <is>
           <t>5b(i)
 → view SR25 response</t>
         </is>
       </c>
-      <c r="I20" s="19" t="inlineStr">
+      <c r="I20" s="14" t="inlineStr">
         <is>
           <t>Met or exceeded</t>
         </is>
       </c>
-      <c r="J20" s="19" t="inlineStr">
+      <c r="J20" s="14" t="inlineStr">
         <is>
           <t>QS rankings, SDG research outputs all attest to our strength in environmental and sustainable research. 
 We have a research strategy which has clear deliverables for sustainability, including a focus on several "Big Research Challenges" which directly relate to Sustainability https://staff.unimelb.edu.au/science/research/research-governance/research-strategy-2023-2030/FOS-Research-strategy-_INTRANET-LINKS-FIXED.pdf
@@ -1195,59 +1099,58 @@
 https://science.unimelb.edu.au/about/news/australia-and-the-pacific-islands-solidarity-in-a-time-of-climate-crisis/_nocache</t>
         </is>
       </c>
-      <c r="K20" s="19" t="inlineStr"/>
-      <c r="L20" s="21" t="n"/>
-      <c r="M20" s="21" t="n"/>
-      <c r="N20" s="21" t="n"/>
-      <c r="O20" s="21" t="n"/>
-      <c r="P20" s="21" t="n"/>
-      <c r="Q20" s="21" t="n"/>
-      <c r="R20" s="21" t="n"/>
+      <c r="K20" s="14" t="inlineStr"/>
+      <c r="L20" s="16" t="n"/>
+      <c r="M20" s="16" t="n"/>
+      <c r="N20" s="16" t="n"/>
+      <c r="O20" s="16" t="n"/>
+      <c r="P20" s="16" t="n"/>
+      <c r="Q20" s="16" t="n"/>
     </row>
     <row r="21" ht="150" customHeight="1">
-      <c r="B21" s="17" t="inlineStr">
+      <c r="B21" s="12" t="inlineStr">
         <is>
           <t>TR3(b)</t>
         </is>
       </c>
-      <c r="C21" s="18" t="inlineStr">
+      <c r="C21" s="13" t="inlineStr">
         <is>
           <t>Transformational research</t>
         </is>
       </c>
-      <c r="D21" s="18" t="inlineStr">
+      <c r="D21" s="13" t="inlineStr">
         <is>
           <t>Embed sustainability within research systems, processes, capability and culture, so research is conducted responsibly, efficiently and with reduced environmental impact.</t>
         </is>
       </c>
-      <c r="E21" s="18" t="inlineStr">
+      <c r="E21" s="13" t="inlineStr">
         <is>
           <t>Demonstrated examples of more sustainable research practices in laboratories, fieldwork, procurement, travel or infrastructure use</t>
         </is>
       </c>
-      <c r="F21" s="19" t="inlineStr">
-        <is>
-          <t>In end-2025 reporting your faculty reported on the related SP2030 target 5c(ii) and rated it 'Partially met' (click the ref in Column H to see it in full in Tab 3). Please build on this rather than repeating it, focusing on what is new in 2026.
+      <c r="F21" s="14" t="inlineStr">
+        <is>
+          <t>In end-2025 reporting your faculty reported on the related SP2030 target 5c(ii) (click the ref in Column H to see it in full in Tab 3). Please build on this rather than repeating it, focusing on what is new in 2026.
 Are there any efforts within the faculty to make research practices more sustainable (e.g. green lab certification, equipment sharing, reduced research travel, sustainable fieldwork, sustainable procurement of research consumables)? If so, please give any examples and any evidence of uptake, resource savings or emissions reductions.</t>
         </is>
       </c>
-      <c r="G21" s="19" t="inlineStr">
+      <c r="G21" s="14" t="inlineStr">
         <is>
           <t>We will report on ways the University is making research practices more sustainable in the 2026 Sustainability Report, and share practical examples (e.g. green labs) across faculties.</t>
         </is>
       </c>
-      <c r="H21" s="20" t="inlineStr">
+      <c r="H21" s="15" t="inlineStr">
         <is>
           <t>5c(ii)
 → view SR25 response</t>
         </is>
       </c>
-      <c r="I21" s="19" t="inlineStr">
+      <c r="I21" s="14" t="inlineStr">
         <is>
           <t>Partially met</t>
         </is>
       </c>
-      <c r="J21" s="19" t="inlineStr">
+      <c r="J21" s="14" t="inlineStr">
         <is>
           <t>We have a research strategy and implimentation plan which has clear deliverables for sustainability; 
 Link for Research strategy: https://staff.unimelb.edu.au/science/research/research-governance/research-strategy-2023-2030               
@@ -1255,59 +1158,58 @@
 which for example includes "Action 10. Improve sustainability of our core business practices"</t>
         </is>
       </c>
-      <c r="K21" s="19" t="inlineStr"/>
-      <c r="L21" s="21" t="n"/>
-      <c r="M21" s="21" t="n"/>
-      <c r="N21" s="21" t="n"/>
-      <c r="O21" s="21" t="n"/>
-      <c r="P21" s="21" t="n"/>
-      <c r="Q21" s="21" t="n"/>
-      <c r="R21" s="21" t="n"/>
+      <c r="K21" s="14" t="inlineStr"/>
+      <c r="L21" s="16" t="n"/>
+      <c r="M21" s="16" t="n"/>
+      <c r="N21" s="16" t="n"/>
+      <c r="O21" s="16" t="n"/>
+      <c r="P21" s="16" t="n"/>
+      <c r="Q21" s="16" t="n"/>
     </row>
     <row r="22" ht="150" customHeight="1">
-      <c r="B22" s="17" t="inlineStr">
+      <c r="B22" s="12" t="inlineStr">
         <is>
           <t>EN1(a)</t>
         </is>
       </c>
-      <c r="C22" s="18" t="inlineStr">
+      <c r="C22" s="13" t="inlineStr">
         <is>
           <t>Enablers</t>
         </is>
       </c>
-      <c r="D22" s="18" t="inlineStr">
+      <c r="D22" s="13" t="inlineStr">
         <is>
           <t>Enablers</t>
         </is>
       </c>
-      <c r="E22" s="18" t="inlineStr">
+      <c r="E22" s="13" t="inlineStr">
         <is>
           <t>Evidence of sustainability outcomes informed by Indigenous knowledges</t>
         </is>
       </c>
-      <c r="F22" s="19" t="inlineStr">
-        <is>
-          <t>In end-2025 reporting your faculty reported on the related SP2030 target 6a and rated it 'Partially met' (click the ref in Column H to see it in full in Tab 3). Please build on this rather than repeating it, focusing on what is new in 2026.
+      <c r="F22" s="14" t="inlineStr">
+        <is>
+          <t>In end-2025 reporting your faculty reported on the related SP2030 target 6a (click the ref in Column H to see it in full in Tab 3). Please build on this rather than repeating it, focusing on what is new in 2026.
 Please give any examples of activity in your faculty (education, research, engagement or operations) where Indigenous knowledges informed a sustainability outcome. Describe the activity, how Indigenous knowledges were incorporated or co-created and with whom, and the result. Please confirm that appropriate permissions are in place for sharing.</t>
         </is>
       </c>
-      <c r="G22" s="19" t="inlineStr">
+      <c r="G22" s="14" t="inlineStr">
         <is>
           <t>We will report on the ways Indigenous knowledges inform sustainability activities across the University, and develop selected examples into case studies with appropriate permissions.</t>
         </is>
       </c>
-      <c r="H22" s="20" t="inlineStr">
+      <c r="H22" s="15" t="inlineStr">
         <is>
           <t>6a
 → view SR25 response</t>
         </is>
       </c>
-      <c r="I22" s="19" t="inlineStr">
+      <c r="I22" s="14" t="inlineStr">
         <is>
           <t>Partially met</t>
         </is>
       </c>
-      <c r="J22" s="19" t="inlineStr">
+      <c r="J22" s="14" t="inlineStr">
         <is>
           <t>The Faculty of Science strategy has a specific goal of "Establish Indigenous lead caring for
 country course and resources " which sits under the theme of Living Sustaianbly. 
@@ -1315,60 +1217,59 @@
 Robyn Schofield working with Murujuga Rock Art Monitoring Program and being part of the Australian delegation that saw the inscription of Murujuga as a UN World Hertiage site in 2025 is one example.</t>
         </is>
       </c>
-      <c r="K22" s="19" t="inlineStr"/>
-      <c r="L22" s="21" t="n"/>
-      <c r="M22" s="21" t="n"/>
-      <c r="N22" s="21" t="n"/>
-      <c r="O22" s="21" t="n"/>
-      <c r="P22" s="21" t="n"/>
-      <c r="Q22" s="21" t="n"/>
-      <c r="R22" s="21" t="n"/>
+      <c r="K22" s="14" t="inlineStr"/>
+      <c r="L22" s="16" t="n"/>
+      <c r="M22" s="16" t="n"/>
+      <c r="N22" s="16" t="n"/>
+      <c r="O22" s="16" t="n"/>
+      <c r="P22" s="16" t="n"/>
+      <c r="Q22" s="16" t="n"/>
     </row>
     <row r="23" ht="150" customHeight="1">
-      <c r="B23" s="17" t="inlineStr">
+      <c r="B23" s="12" t="inlineStr">
         <is>
           <t>EN1(b)</t>
         </is>
       </c>
-      <c r="C23" s="18" t="inlineStr">
+      <c r="C23" s="13" t="inlineStr">
         <is>
           <t>Enablers</t>
         </is>
       </c>
-      <c r="D23" s="18" t="inlineStr">
+      <c r="D23" s="13" t="inlineStr">
         <is>
           <t>Enablers</t>
         </is>
       </c>
-      <c r="E23" s="18" t="inlineStr">
+      <c r="E23" s="13" t="inlineStr">
         <is>
           <t>Living laboratories enabling applied learning, research and operational sustainability outcomes</t>
         </is>
       </c>
-      <c r="F23" s="19" t="inlineStr">
-        <is>
-          <t>In end-2025 reporting your faculty reported on the related SP2030 target 2a and rated it 'Partially met' (click the ref in Column H to see it in full in Tab 3). Please build on this rather than repeating it, focusing on what is new in 2026.
+      <c r="F23" s="14" t="inlineStr">
+        <is>
+          <t>In end-2025 reporting your faculty reported on the related SP2030 target 2a (click the ref in Column H to see it in full in Tab 3). Please build on this rather than repeating it, focusing on what is new in 2026.
 Please give any examples of sustainability-related living labs operating within your faculty in 2026 – their activities, who is involved (students, researchers, operational staff) and their outputs, outcomes or impact.
 Please note we will approach living labs funded through the Campus Living Lab Accelerator Program (CLLAP) separately.</t>
         </is>
       </c>
-      <c r="G23" s="19" t="inlineStr">
+      <c r="G23" s="14" t="inlineStr">
         <is>
           <t>We will share examples of sustainability-related living labs from across the University in the 2026 Sustainability Report, alongside CLLAP projects reported by CI&amp;S.</t>
         </is>
       </c>
-      <c r="H23" s="20" t="inlineStr">
+      <c r="H23" s="15" t="inlineStr">
         <is>
           <t>2a
 → view SR25 response</t>
         </is>
       </c>
-      <c r="I23" s="19" t="inlineStr">
+      <c r="I23" s="14" t="inlineStr">
         <is>
           <t>Partially met</t>
         </is>
       </c>
-      <c r="J23" s="19" t="inlineStr">
+      <c r="J23" s="14" t="inlineStr">
         <is>
           <t>The faculty has many projects that can be considered living labs. A centralised approach is required to document them.
 2025 examples include how the undergraduate chemistry teaching laboratories redesigned their practicals to use less reagents and safer chemicals to achieve the same learning outcomes.
@@ -1376,97 +1277,87 @@
 SAFES have worked on Indigenous food gardens and have an Indigenous food guide and there are examples of urban and woodland greening that serve as best practice examples across Australia</t>
         </is>
       </c>
-      <c r="K23" s="19" t="inlineStr">
+      <c r="K23" s="14" t="inlineStr">
         <is>
           <t>https://www.unimelb.edu.au/newsroom/news/2024/october/native-harvest-cookbook-aims-to-put-indigenous-food-in-every-aussie-kitchen
 https://theconversation.com/we-planted-two-woody-meadows-a-decade-ago-to-see-what-would-thrive-now-the-concept-is-popular-across-australia-269611</t>
         </is>
       </c>
-      <c r="L23" s="21" t="n"/>
-      <c r="M23" s="21" t="n"/>
-      <c r="N23" s="21" t="n"/>
-      <c r="O23" s="21" t="n"/>
-      <c r="P23" s="21" t="n"/>
-      <c r="Q23" s="21" t="n"/>
-      <c r="R23" s="21" t="n"/>
+      <c r="L23" s="16" t="n"/>
+      <c r="M23" s="16" t="n"/>
+      <c r="N23" s="16" t="n"/>
+      <c r="O23" s="16" t="n"/>
+      <c r="P23" s="16" t="n"/>
+      <c r="Q23" s="16" t="n"/>
     </row>
     <row r="24" ht="150" customHeight="1">
-      <c r="B24" s="17" t="inlineStr">
+      <c r="B24" s="12" t="inlineStr">
         <is>
           <t>EN1(c)</t>
         </is>
       </c>
-      <c r="C24" s="18" t="inlineStr">
+      <c r="C24" s="13" t="inlineStr">
         <is>
           <t>Enablers</t>
         </is>
       </c>
-      <c r="D24" s="18" t="inlineStr">
+      <c r="D24" s="13" t="inlineStr">
         <is>
           <t>Enablers</t>
         </is>
       </c>
-      <c r="E24" s="18" t="inlineStr">
+      <c r="E24" s="13" t="inlineStr">
         <is>
           <t>Coordinated internal engagement and external partnerships contributing to delivery of sustainability outcomes across priority areas.</t>
         </is>
       </c>
-      <c r="F24" s="19" t="inlineStr">
-        <is>
-          <t>In end-2025 reporting your faculty reported on the related SP2030 target 3a(ii) and rated it 'Met or exceeded' (click the ref in Column H to see it in full in Tab 3). Please build on this rather than repeating it, focusing on what is new in 2026.
+      <c r="F24" s="14" t="inlineStr">
+        <is>
+          <t>In end-2025 reporting your faculty reported on the related SP2030 target 3a(ii) (click the ref in Column H to see it in full in Tab 3). Please build on this rather than repeating it, focusing on what is new in 2026.
 Please list the key sustainability-focused communities of practice, internal networks or external partnerships active in your faculty in 2026 (name, partners, priority area), and give any examples of activity that contributed to a Sustainability 2030 outcome.</t>
         </is>
       </c>
-      <c r="G24" s="19" t="inlineStr">
+      <c r="G24" s="14" t="inlineStr">
         <is>
           <t>We will report on internal engagement and partnerships contributing to Sustainability 2030 outcomes, and update our record of sustainability-focused communities of practice and contacts across the University.</t>
         </is>
       </c>
-      <c r="H24" s="20" t="inlineStr">
+      <c r="H24" s="15" t="inlineStr">
         <is>
           <t>3a(ii)
 → view SR25 response</t>
         </is>
       </c>
-      <c r="I24" s="19" t="inlineStr">
+      <c r="I24" s="14" t="inlineStr">
         <is>
           <t>Met or exceeded</t>
         </is>
       </c>
-      <c r="J24" s="19" t="inlineStr">
+      <c r="J24" s="14" t="inlineStr">
         <is>
           <t>The Associate/Assistant Deans of Sustainability exist in every faculty. While we interface with teaching, the DVCA, and A/Ds for UG and Postgraduate teaching are where the embedding of sustainability in formal learning outcomes occurs.
 In the FoS the UG Chemistry laboratory sustainability upgrades is a great example of embedding sustainability early in learning for students.</t>
         </is>
       </c>
-      <c r="K24" s="19" t="inlineStr"/>
-      <c r="L24" s="21" t="n"/>
-      <c r="M24" s="21" t="n"/>
-      <c r="N24" s="21" t="n"/>
-      <c r="O24" s="21" t="n"/>
-      <c r="P24" s="21" t="n"/>
-      <c r="Q24" s="21" t="n"/>
-      <c r="R24" s="21" t="n"/>
+      <c r="K24" s="14" t="inlineStr"/>
+      <c r="L24" s="16" t="n"/>
+      <c r="M24" s="16" t="n"/>
+      <c r="N24" s="16" t="n"/>
+      <c r="O24" s="16" t="n"/>
+      <c r="P24" s="16" t="n"/>
+      <c r="Q24" s="16" t="n"/>
     </row>
     <row r="25"/>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="1"/>
-  <mergeCells count="9">
-    <mergeCell ref="M7:N7"/>
+  <mergeCells count="4">
+    <mergeCell ref="C13:G13"/>
+    <mergeCell ref="L13:Q13"/>
+    <mergeCell ref="D4:G8"/>
     <mergeCell ref="B4:C8"/>
-    <mergeCell ref="M6:N6"/>
-    <mergeCell ref="L13:R13"/>
-    <mergeCell ref="M5:N5"/>
-    <mergeCell ref="D4:G8"/>
-    <mergeCell ref="C13:G13"/>
-    <mergeCell ref="L3:N3"/>
-    <mergeCell ref="M4:N4"/>
   </mergeCells>
-  <dataValidations count="2">
-    <dataValidation sqref="L16:L24" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please select from the dropdown" type="list">
-      <formula1>=Lists!$B$3:$B$7</formula1>
-    </dataValidation>
-    <dataValidation sqref="Q16:Q24" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please select from the dropdown" type="list">
+  <dataValidations count="1">
+    <dataValidation sqref="P16:P24" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please select from the dropdown" type="list">
       <formula1>=Lists!$C$2:$C$4</formula1>
     </dataValidation>
   </dataValidations>
@@ -1513,7 +1404,7 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
-          <t>End-2026 target status assessment and reporting</t>
+          <t>SR26 sustainability reporting</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1416,12 @@
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="7" t="inlineStr">
+      <c r="B5" s="17" t="inlineStr">
         <is>
           <t>How to use this spreadsheet</t>
         </is>
       </c>
-      <c r="C5" s="22" t="inlineStr">
+      <c r="C5" s="18" t="inlineStr">
         <is>
           <t>Please share up to 3 stories from 2026 which highlight your faculty's/portfolio's sustainability progress and/or impact. These stories can directly relate to Sustainability 2030 targets and indicators, or sustainability more generally. Due: Tuesday 15 December 2026 (early submission helps us develop case studies).</t>
         </is>
@@ -1538,77 +1429,77 @@
     </row>
     <row r="6"/>
     <row r="8">
-      <c r="B8" s="23" t="inlineStr">
+      <c r="B8" s="19" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="C8" s="23" t="inlineStr">
+      <c r="C8" s="19" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="D8" s="23" t="inlineStr">
+      <c r="D8" s="19" t="inlineStr">
         <is>
           <t>Related Sustainability 2030 targets (optional)</t>
         </is>
       </c>
-      <c r="E8" s="23" t="inlineStr">
+      <c r="E8" s="19" t="inlineStr">
         <is>
           <t>Images and other media</t>
         </is>
       </c>
-      <c r="F8" s="23" t="inlineStr">
+      <c r="F8" s="19" t="inlineStr">
         <is>
           <t>Links and supporting documentation</t>
         </is>
       </c>
     </row>
     <row r="9" ht="90" customHeight="1">
-      <c r="B9" s="24" t="inlineStr"/>
-      <c r="C9" s="24" t="inlineStr">
+      <c r="B9" s="20" t="inlineStr"/>
+      <c r="C9" s="20" t="inlineStr">
         <is>
           <t>• Please include a brief description of a project or activity that has made a significant contribution to sustainability at the University (up to 250 words)
 • Summarise the benefits. Benefits may relate to operational outcomes, environmental/social outcomes, and sector benefits.</t>
         </is>
       </c>
-      <c r="D9" s="24" t="inlineStr"/>
-      <c r="E9" s="24" t="inlineStr">
+      <c r="D9" s="20" t="inlineStr"/>
+      <c r="E9" s="20" t="inlineStr">
         <is>
           <t>(link to OneDrive/SharePoint files or published online content preferred)</t>
         </is>
       </c>
-      <c r="F9" s="24" t="inlineStr"/>
+      <c r="F9" s="20" t="inlineStr"/>
     </row>
     <row r="10" ht="120" customHeight="1">
       <c r="A10" t="n">
         <v>1</v>
       </c>
-      <c r="B10" s="21" t="n"/>
-      <c r="C10" s="21" t="n"/>
-      <c r="D10" s="21" t="n"/>
-      <c r="E10" s="21" t="n"/>
-      <c r="F10" s="21" t="n"/>
+      <c r="B10" s="16" t="n"/>
+      <c r="C10" s="16" t="n"/>
+      <c r="D10" s="16" t="n"/>
+      <c r="E10" s="16" t="n"/>
+      <c r="F10" s="16" t="n"/>
     </row>
     <row r="11" ht="120" customHeight="1">
       <c r="A11" t="n">
         <v>2</v>
       </c>
-      <c r="B11" s="21" t="n"/>
-      <c r="C11" s="21" t="n"/>
-      <c r="D11" s="21" t="n"/>
-      <c r="E11" s="21" t="n"/>
-      <c r="F11" s="21" t="n"/>
+      <c r="B11" s="16" t="n"/>
+      <c r="C11" s="16" t="n"/>
+      <c r="D11" s="16" t="n"/>
+      <c r="E11" s="16" t="n"/>
+      <c r="F11" s="16" t="n"/>
     </row>
     <row r="12" ht="120" customHeight="1">
       <c r="A12" t="n">
         <v>3</v>
       </c>
-      <c r="B12" s="21" t="n"/>
-      <c r="C12" s="21" t="n"/>
-      <c r="D12" s="21" t="n"/>
-      <c r="E12" s="21" t="n"/>
-      <c r="F12" s="21" t="n"/>
+      <c r="B12" s="16" t="n"/>
+      <c r="C12" s="16" t="n"/>
+      <c r="D12" s="16" t="n"/>
+      <c r="E12" s="16" t="n"/>
+      <c r="F12" s="16" t="n"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="1"/>
@@ -1659,90 +1550,90 @@
       </c>
     </row>
     <row r="3" ht="32" customHeight="1">
-      <c r="B3" s="22" t="inlineStr">
+      <c r="B3" s="18" t="inlineStr">
         <is>
           <t>Your responses to the end-2025 reporting request, against the former Sustainability Plan 2030 (SP2030) targets. For reference only – please do not edit. Use the 'Back to request' links to return to the reporting template.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="B4" s="25" t="inlineStr">
+      <c r="B4" s="21" t="inlineStr">
         <is>
           <t>← Back to request</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="26" t="inlineStr">
+      <c r="B5" s="22" t="inlineStr">
         <is>
           <t>SCI</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="14" t="inlineStr">
+      <c r="B6" s="9" t="inlineStr">
         <is>
           <t>SR25 ref</t>
         </is>
       </c>
-      <c r="C6" s="14" t="inlineStr">
+      <c r="C6" s="9" t="inlineStr">
         <is>
           <t>SP2030 target</t>
         </is>
       </c>
-      <c r="D6" s="14" t="inlineStr">
+      <c r="D6" s="9" t="inlineStr">
         <is>
           <t>2025 reporting request</t>
         </is>
       </c>
-      <c r="E6" s="14" t="inlineStr">
+      <c r="E6" s="9" t="inlineStr">
         <is>
           <t>Confirmed end-2025 status</t>
         </is>
       </c>
-      <c r="F6" s="14" t="inlineStr">
+      <c r="F6" s="9" t="inlineStr">
         <is>
           <t>OPTION 1: Target-level reporting</t>
         </is>
       </c>
-      <c r="G6" s="14" t="inlineStr">
+      <c r="G6" s="9" t="inlineStr">
         <is>
           <t>OPTION 2: Indicator-level reporting</t>
         </is>
       </c>
-      <c r="H6" s="14" t="inlineStr">
+      <c r="H6" s="9" t="inlineStr">
         <is>
           <t>Supporting information/comments</t>
         </is>
       </c>
-      <c r="I6" s="14" t="inlineStr">
+      <c r="I6" s="9" t="inlineStr">
         <is>
           <t>Related SR26 indicator(s)</t>
         </is>
       </c>
     </row>
     <row r="7" ht="160" customHeight="1">
-      <c r="B7" s="17" t="inlineStr">
+      <c r="B7" s="12" t="inlineStr">
         <is>
           <t>1a(i)</t>
         </is>
       </c>
-      <c r="C7" s="19" t="inlineStr">
+      <c r="C7" s="14" t="inlineStr">
         <is>
           <t>The University is certified carbon neutral by 2025</t>
         </is>
       </c>
-      <c r="D7" s="19" t="inlineStr">
+      <c r="D7" s="14" t="inlineStr">
         <is>
           <t>Comment on progress to reduce air travel emissions in the faculty</t>
         </is>
       </c>
-      <c r="E7" s="19" t="inlineStr">
+      <c r="E7" s="14" t="inlineStr">
         <is>
           <t>Met or exceeded</t>
         </is>
       </c>
-      <c r="F7" s="19" t="inlineStr">
+      <c r="F7" s="14" t="inlineStr">
         <is>
           <t>Provide commentary with reference to data in the Flights dashboard (link in Column O)
 Science:
@@ -1753,47 +1644,47 @@
 2025 emissions are tracking at  3312 tCO2e for science - this would again achieve a 10% reduction from 2019 emissions (target: &lt;3547 tCO2e). However, the emission intensity just from flights is higher than the goal of 2.7tCO2eq per person for total workplace emissions to be in line with Paris goals.</t>
         </is>
       </c>
-      <c r="G7" s="19" t="inlineStr">
+      <c r="G7" s="14" t="inlineStr">
         <is>
           <t>For context: In order to have a reasonable chance of staying below 2oC the per capita carbon emissions per year should be below ~8.2 tCO2eq per person per year (calculated from total 3700Gt CO2 eq budget to 2050 and assuming 9 billion people on Earth). As time at work consistutes about 1/3 of a person's life this gives ~2.7 tCO2eq per person would be a scientifically based target for total workplace emissions (including flights). Note: in 2023 Australians emitted ~14.5 tCO2eq per person.
  [link 3700 GtCO2eq target: https://www.climatechangeauthority.gov.au/sites/default/files/Targets%20and%20Progress%20Review%20Final%20Report_Chapter%203.pdf]</t>
         </is>
       </c>
-      <c r="H7" s="19" t="inlineStr">
+      <c r="H7" s="14" t="inlineStr">
         <is>
           <t>https://app.powerbi.com/links/SI8xYFLga4?ctid=0e5bf3cf-1ff4-46b7-9176-52c538c22a4d&amp;pbi_source=linkShare&amp;bookmarkGuid=499326eb-68f1-43e0-a3e6-0f252ee44ccb</t>
         </is>
       </c>
-      <c r="I7" s="19" t="inlineStr"/>
+      <c r="I7" s="14" t="inlineStr"/>
     </row>
     <row r="8" ht="160" customHeight="1">
-      <c r="B8" s="17" t="inlineStr">
+      <c r="B8" s="12" t="inlineStr">
         <is>
           <t>2a</t>
         </is>
       </c>
-      <c r="C8" s="19" t="inlineStr">
+      <c r="C8" s="14" t="inlineStr">
         <is>
           <t>The University has curated living labs covering the priority areas of this Plan</t>
         </is>
       </c>
-      <c r="D8" s="19" t="inlineStr">
+      <c r="D8" s="14" t="inlineStr">
         <is>
           <t>Please provide a case study of a living lab which operates within the faculty/portfolio, including a description of its activities and impact. 
 Please note we will approach living labs funded through the Campus Living Lab Accelerator program (CLLAP) separately report on their activities.</t>
         </is>
       </c>
-      <c r="E8" s="19" t="inlineStr">
+      <c r="E8" s="14" t="inlineStr">
         <is>
           <t>Partially met</t>
         </is>
       </c>
-      <c r="F8" s="19" t="inlineStr">
+      <c r="F8" s="14" t="inlineStr">
         <is>
           <t>The faculty has many projects that can be considered living labs. A centralised approach is required to document them.</t>
         </is>
       </c>
-      <c r="G8" s="19" t="inlineStr">
+      <c r="G8" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve">
 2025 examples include how the undergraduate chemistry teaching laboratories redesigned their practicals to use less reagents and safer chemicals to achieve the same learning outcomes.
@@ -1801,159 +1692,159 @@
 SAFES have worked on Indigenous food gardens and have an Indigenous food guide and there are examples of urban and woodland greening that serve as best practice examples across Australia</t>
         </is>
       </c>
-      <c r="H8" s="19" t="inlineStr">
+      <c r="H8" s="14" t="inlineStr">
         <is>
           <t>https://www.unimelb.edu.au/newsroom/news/2024/october/native-harvest-cookbook-aims-to-put-indigenous-food-in-every-aussie-kitchen
 https://theconversation.com/we-planted-two-woody-meadows-a-decade-ago-to-see-what-would-thrive-now-the-concept-is-popular-across-australia-269611</t>
         </is>
       </c>
-      <c r="I8" s="19" t="inlineStr">
+      <c r="I8" s="14" t="inlineStr">
         <is>
           <t>TR1(a), EN1(b)</t>
         </is>
       </c>
     </row>
     <row r="9" ht="160" customHeight="1">
-      <c r="B9" s="17" t="inlineStr">
+      <c r="B9" s="12" t="inlineStr">
         <is>
           <t>3a(i)</t>
         </is>
       </c>
-      <c r="C9" s="19" t="inlineStr">
+      <c r="C9" s="14" t="inlineStr">
         <is>
           <t>The University's Academic Divisions and portfolios support and learn from each other to embed sustainability in practice and in learning – formal, non-formal and informal</t>
         </is>
       </c>
-      <c r="D9" s="19" t="inlineStr">
+      <c r="D9" s="14" t="inlineStr">
         <is>
           <t>Please update data on sustainability-focused staff in the faculty/portfolio provided in the previous reporting period (additional staff/those who have left the University) (see Columns G [2024] and J [mid-2025])</t>
         </is>
       </c>
-      <c r="E9" s="19" t="inlineStr">
+      <c r="E9" s="14" t="inlineStr">
         <is>
           <t>Met or exceeded</t>
         </is>
       </c>
-      <c r="F9" s="19" t="inlineStr">
+      <c r="F9" s="14" t="inlineStr">
         <is>
           <t>2025 saw the faculty of science develop a strategy - with goals in sustainability detailed here: https://staff.unimelb.edu.au/science/temporary-assets-and-links/Draft-FoS-Strategic-Priorities-All-Staff-Forum-August-2025.pdf (not to be shared externally)
 We are the custodian faculty for the Melbourne Biodiversity Institute and Melbourne Energy Institute, we also contribute to Melbourne climate futures.
 Several of our researchers are lead authors under the IPCC assessment report 7: https://www.unimelb.edu.au/newsroom/news/2025/august/university-of-melbourne-researchers-contributing-to-global-climate-report</t>
         </is>
       </c>
-      <c r="G9" s="19" t="inlineStr">
+      <c r="G9" s="14" t="inlineStr">
         <is>
           <t>The faculty of science has sustainability focused staff that cover all of the SDGs with 590 staff members producing more than 4 outputs that fall under the SDG framework (8630 research outputs). 
 With a total of 954 academic staff members  in the Faculty of Science (857 FTE) -  62% (69% when considering FTE) of our staff have significant SDG aligned research outputs (&gt;4 outputs)</t>
         </is>
       </c>
-      <c r="H9" s="19" t="inlineStr">
+      <c r="H9" s="14" t="inlineStr">
         <is>
           <t>https://app.powerbi.com/groups/me/reports/10687142-d5e8-46ef-b6f9-3adbbe5950c9/7913ae78325b04001d16?ctid=0e5bf3cf-1ff4-46b7-9176-52c538c22a4d&amp;experience=power-bi</t>
         </is>
       </c>
-      <c r="I9" s="19" t="inlineStr"/>
+      <c r="I9" s="14" t="inlineStr"/>
     </row>
     <row r="10" ht="160" customHeight="1">
-      <c r="B10" s="17" t="inlineStr">
+      <c r="B10" s="12" t="inlineStr">
         <is>
           <t>3a(ii)</t>
         </is>
       </c>
-      <c r="C10" s="19" t="inlineStr">
+      <c r="C10" s="14" t="inlineStr">
         <is>
           <t>The University's Academic Divisions and portfolios support and learn from each other to embed sustainability in practice and in learning – formal, non-formal and informal</t>
         </is>
       </c>
-      <c r="D10" s="19" t="inlineStr">
+      <c r="D10" s="14" t="inlineStr">
         <is>
           <t>Please list sustainability-focused knowledge sharing activities or communities of practice active in the faculty/portfolio in 2025, and provide a short case study of one of these.</t>
         </is>
       </c>
-      <c r="E10" s="19" t="inlineStr">
+      <c r="E10" s="14" t="inlineStr">
         <is>
           <t>Met or exceeded</t>
         </is>
       </c>
-      <c r="F10" s="19" t="inlineStr">
+      <c r="F10" s="14" t="inlineStr">
         <is>
           <t>The Associate/Assistant Deans of Sustainability exist in every faculty. While we interface with teaching, the DVCA, and A/Ds for UG and Postgraduate teaching are where the embedding of sustainability in formal learning outcomes occurs.</t>
         </is>
       </c>
-      <c r="G10" s="19" t="inlineStr">
+      <c r="G10" s="14" t="inlineStr">
         <is>
           <t>In the FoS the UG Chemistry laboratory sustainability upgrades is a great example of embedding sustainability early in learning for students.</t>
         </is>
       </c>
-      <c r="H10" s="19" t="inlineStr"/>
-      <c r="I10" s="19" t="inlineStr">
+      <c r="H10" s="14" t="inlineStr"/>
+      <c r="I10" s="14" t="inlineStr">
         <is>
           <t>EN1(c)</t>
         </is>
       </c>
     </row>
     <row r="11" ht="160" customHeight="1">
-      <c r="B11" s="17" t="inlineStr">
+      <c r="B11" s="12" t="inlineStr">
         <is>
           <t>3d(ii)</t>
         </is>
       </c>
-      <c r="C11" s="19" t="inlineStr">
+      <c r="C11" s="14" t="inlineStr">
         <is>
           <t>Academic and professional staff have increased their participation in and contribution to formal and non_x0002_formal learning to develop their general and role-specific sustainability skills</t>
         </is>
       </c>
-      <c r="D11" s="19" t="inlineStr">
+      <c r="D11" s="14" t="inlineStr">
         <is>
           <t>Have any staff participated in sustainability-focused professional development in 2025? If yes, what kinds of activities have staff participated in and how are these learnings being applied in the faculty/portfolio?
 Please note, there is no need to include data on participation in Green Impact ('Green teams'), as this is reported on centrally.</t>
         </is>
       </c>
-      <c r="E11" s="19" t="inlineStr">
+      <c r="E11" s="14" t="inlineStr">
         <is>
           <t>Partially met</t>
         </is>
       </c>
-      <c r="F11" s="19" t="inlineStr">
+      <c r="F11" s="14" t="inlineStr">
         <is>
           <t>The Associate/Assistant Deans of Sustainability is heavily involved cross-faculty programs to share ideas.</t>
         </is>
       </c>
-      <c r="G11" s="19" t="inlineStr">
+      <c r="G11" s="14" t="inlineStr">
         <is>
           <t>Suggest that the relevant trainme model is promoted centrally to all faculties: https://uomtrainme.elmotalent.com.au/learning/view-activity/833/scorm/2057</t>
         </is>
       </c>
-      <c r="H11" s="19" t="inlineStr"/>
-      <c r="I11" s="19" t="inlineStr"/>
+      <c r="H11" s="14" t="inlineStr"/>
+      <c r="I11" s="14" t="inlineStr"/>
     </row>
     <row r="12" ht="160" customHeight="1">
-      <c r="B12" s="17" t="inlineStr">
+      <c r="B12" s="12" t="inlineStr">
         <is>
           <t>4a(ii)</t>
         </is>
       </c>
-      <c r="C12" s="19" t="inlineStr">
+      <c r="C12" s="14" t="inlineStr">
         <is>
           <t>Sustainability is integrated into curriculum to an extent that conscientiously extends, beyond a base threshold, each discipline’s (and associated professions/industries’) knowledge of the helpful and harmful impacts it has for the environmental and human systems we depend on</t>
         </is>
       </c>
-      <c r="D12" s="19" t="inlineStr">
+      <c r="D12" s="14" t="inlineStr">
         <is>
           <t>Please describe any efforts within your faculty to embed sustainability in the curriculum in line with this target.</t>
         </is>
       </c>
-      <c r="E12" s="19" t="inlineStr">
+      <c r="E12" s="14" t="inlineStr">
         <is>
           <t>Met or exceeded</t>
         </is>
       </c>
-      <c r="F12" s="19" t="inlineStr">
+      <c r="F12" s="14" t="inlineStr">
         <is>
           <t>Sustainability, conservation, biodiversity are elements of most courses and majors within the FoS. Several additional courses are being considered at PG level in 2026</t>
         </is>
       </c>
-      <c r="G12" s="19" t="inlineStr">
+      <c r="G12" s="14" t="inlineStr">
         <is>
           <t>The FoS education strategy https://staff.unimelb.edu.au/science/learning-and-teaching-support/education-strategy has been developed with the following targets related to sustainability:  
 Under Innovate: "Maintain a focus on embedding the principles of sustainability in our teaching and learning practices, including ‘green’ and sustainable laboratory initiatives"; Future ready graduates: "Our programs will embed the concepts of sustainability set out in the University’s Sustainability
@@ -1962,42 +1853,42 @@
 With the 12 month implementation plan noting that: "Understanding our students’ carbon footprint is the first step towards incorporating sustainability in teaching and learning."</t>
         </is>
       </c>
-      <c r="H12" s="19" t="inlineStr"/>
-      <c r="I12" s="19" t="inlineStr">
+      <c r="H12" s="14" t="inlineStr"/>
+      <c r="I12" s="14" t="inlineStr">
         <is>
           <t>EE1(a)</t>
         </is>
       </c>
     </row>
     <row r="13" ht="160" customHeight="1">
-      <c r="B13" s="17" t="inlineStr">
+      <c r="B13" s="12" t="inlineStr">
         <is>
           <t>4b(i)</t>
         </is>
       </c>
-      <c r="C13" s="19" t="inlineStr">
+      <c r="C13" s="14" t="inlineStr">
         <is>
           <t>Graduates have increased capabilities to shape, lead 
 and succeed in the careers, communities and industries 
 of sustainable societies (year on year).</t>
         </is>
       </c>
-      <c r="D13" s="19" t="inlineStr">
+      <c r="D13" s="14" t="inlineStr">
         <is>
           <t>Is there any way to measure graduate outcomes related to sustainability in your faculty? If so, please describe.</t>
         </is>
       </c>
-      <c r="E13" s="19" t="inlineStr">
+      <c r="E13" s="14" t="inlineStr">
         <is>
           <t>Met or exceeded</t>
         </is>
       </c>
-      <c r="F13" s="19" t="inlineStr">
+      <c r="F13" s="14" t="inlineStr">
         <is>
           <t>As above. FoS is the custodial faculty for the Office of Environmental Programs</t>
         </is>
       </c>
-      <c r="G13" s="19" t="inlineStr">
+      <c r="G13" s="14" t="inlineStr">
         <is>
           <t>The BSc had 208 graduates across the following environmental/sustainability focussed majors:
 Zoology 40
@@ -2020,35 +1911,35 @@
 24 Master of Urban Horticulture</t>
         </is>
       </c>
-      <c r="H13" s="19" t="inlineStr"/>
-      <c r="I13" s="19" t="inlineStr">
+      <c r="H13" s="14" t="inlineStr"/>
+      <c r="I13" s="14" t="inlineStr">
         <is>
           <t>EE1(d)</t>
         </is>
       </c>
     </row>
     <row r="14" ht="160" customHeight="1">
-      <c r="B14" s="17" t="inlineStr">
+      <c r="B14" s="12" t="inlineStr">
         <is>
           <t>5b(i)</t>
         </is>
       </c>
-      <c r="C14" s="19" t="inlineStr">
+      <c r="C14" s="14" t="inlineStr">
         <is>
           <t>The highest quality research is conducted that contributes to knowledge, action, and impact across the disciplinary and interdisciplinary dimensions of sustainability.</t>
         </is>
       </c>
-      <c r="D14" s="19" t="inlineStr">
+      <c r="D14" s="14" t="inlineStr">
         <is>
           <t>Please update data on sustainability-, climate- or environment-focused research institutes, and provide a case study of their key research impacts in 2025.</t>
         </is>
       </c>
-      <c r="E14" s="19" t="inlineStr">
+      <c r="E14" s="14" t="inlineStr">
         <is>
           <t>Met or exceeded</t>
         </is>
       </c>
-      <c r="F14" s="19" t="inlineStr">
+      <c r="F14" s="14" t="inlineStr">
         <is>
           <t>QS rankings, SDG research outputs all attest to our strength in environmental and sustainable research. 
 We have a research strategy which has clear deliverables for sustainability, including a focus on several "Big Research Challenges" which directly relate to Sustainability https://staff.unimelb.edu.au/science/research/research-governance/research-strategy-2023-2030/FOS-Research-strategy-_INTRANET-LINKS-FIXED.pdf
@@ -2058,36 +1949,36 @@
 https://science.unimelb.edu.au/about/news/australia-and-the-pacific-islands-solidarity-in-a-time-of-climate-crisis/_nocache</t>
         </is>
       </c>
-      <c r="G14" s="19" t="inlineStr"/>
-      <c r="H14" s="19" t="inlineStr"/>
-      <c r="I14" s="19" t="inlineStr">
+      <c r="G14" s="14" t="inlineStr"/>
+      <c r="H14" s="14" t="inlineStr"/>
+      <c r="I14" s="14" t="inlineStr">
         <is>
           <t>TR2(a), TR2(d)</t>
         </is>
       </c>
     </row>
     <row r="15" ht="160" customHeight="1">
-      <c r="B15" s="17" t="inlineStr">
+      <c r="B15" s="12" t="inlineStr">
         <is>
           <t>5c(ii)</t>
         </is>
       </c>
-      <c r="C15" s="19" t="inlineStr">
+      <c r="C15" s="14" t="inlineStr">
         <is>
           <t>Researchers make considered decisions on the sustainability impact of their research practices and activities</t>
         </is>
       </c>
-      <c r="D15" s="19" t="inlineStr">
+      <c r="D15" s="14" t="inlineStr">
         <is>
           <t>Are there any efforts within the faculty to make research practices more sustainable? If so, please describe these activities</t>
         </is>
       </c>
-      <c r="E15" s="19" t="inlineStr">
+      <c r="E15" s="14" t="inlineStr">
         <is>
           <t>Partially met</t>
         </is>
       </c>
-      <c r="F15" s="19" t="inlineStr">
+      <c r="F15" s="14" t="inlineStr">
         <is>
           <t>We have a research strategy and implimentation plan which has clear deliverables for sustainability; 
 Link for Research strategy: https://staff.unimelb.edu.au/science/research/research-governance/research-strategy-2023-2030               
@@ -2095,36 +1986,36 @@
 which for example includes "Action 10. Improve sustainability of our core business practices"</t>
         </is>
       </c>
-      <c r="G15" s="19" t="inlineStr"/>
-      <c r="H15" s="19" t="inlineStr"/>
-      <c r="I15" s="19" t="inlineStr">
+      <c r="G15" s="14" t="inlineStr"/>
+      <c r="H15" s="14" t="inlineStr"/>
+      <c r="I15" s="14" t="inlineStr">
         <is>
           <t>TR3(a), TR3(b)</t>
         </is>
       </c>
     </row>
     <row r="16" ht="160" customHeight="1">
-      <c r="B16" s="17" t="inlineStr">
+      <c r="B16" s="12" t="inlineStr">
         <is>
           <t>6a</t>
         </is>
       </c>
-      <c r="C16" s="19" t="inlineStr">
+      <c r="C16" s="14" t="inlineStr">
         <is>
           <t>The University has an increased understanding of sustainability from an Indigenous perspective through co-created or Indigenous-led reciprocal learning</t>
         </is>
       </c>
-      <c r="D16" s="19" t="inlineStr">
+      <c r="D16" s="14" t="inlineStr">
         <is>
           <t>Please provide a case study on activities in the faculty (related to education, research or partnerships) which operate at the nexus between Indigenous knowledges and the western concept of 'sustainability'.</t>
         </is>
       </c>
-      <c r="E16" s="19" t="inlineStr">
+      <c r="E16" s="14" t="inlineStr">
         <is>
           <t>Partially met</t>
         </is>
       </c>
-      <c r="F16" s="19" t="inlineStr">
+      <c r="F16" s="14" t="inlineStr">
         <is>
           <t>The Faculty of Science strategy has a specific goal of "Establish Indigenous lead caring for
 country course and resources " which sits under the theme of Living Sustaianbly. 
@@ -2132,9 +2023,9 @@
 Robyn Schofield working with Murujuga Rock Art Monitoring Program and being part of the Australian delegation that saw the inscription of Murujuga as a UN World Hertiage site in 2025 is one example.</t>
         </is>
       </c>
-      <c r="G16" s="19" t="inlineStr"/>
-      <c r="H16" s="19" t="inlineStr"/>
-      <c r="I16" s="19" t="inlineStr">
+      <c r="G16" s="14" t="inlineStr"/>
+      <c r="H16" s="14" t="inlineStr"/>
+      <c r="I16" s="14" t="inlineStr">
         <is>
           <t>EN1(a)</t>
         </is>
@@ -2157,13 +2048,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:I9"/>
+  <dimension ref="B1:E9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="B1" t="inlineStr">
         <is>
-          <t>End 2026 target status</t>
+          <t>(not used – no target status rating in 2026)</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
@@ -2179,21 +2070,6 @@
       <c r="E1" t="inlineStr">
         <is>
           <t>Y/N</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>Target status</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Score</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>Response count</t>
         </is>
       </c>
     </row>
@@ -2218,24 +2094,8 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Met or exceeded</t>
-        </is>
-      </c>
-      <c r="H2" t="n">
-        <v>3</v>
-      </c>
-      <c r="I2" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="3">
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Met or exceeded</t>
-        </is>
-      </c>
       <c r="C3" t="inlineStr">
         <is>
           <t>No</t>
@@ -2251,24 +2111,8 @@
           <t>No</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Partially met</t>
-        </is>
-      </c>
-      <c r="H3" t="n">
-        <v>2</v>
-      </c>
-      <c r="I3" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="4">
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Partially met</t>
-        </is>
-      </c>
       <c r="C4" t="inlineStr">
         <is>
           <t>Partially – see comments</t>
@@ -2284,47 +2128,15 @@
           <t>TBC</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Not met</t>
-        </is>
-      </c>
-      <c r="H4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I4" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="5">
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Not met</t>
-        </is>
-      </c>
       <c r="D5" t="inlineStr">
         <is>
           <t>Received</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Not yet started</t>
-        </is>
-      </c>
-      <c r="H5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="6">
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Not yet started</t>
-        </is>
-      </c>
       <c r="D6" t="inlineStr">
         <is>
           <t>First review</t>
@@ -2332,11 +2144,6 @@
       </c>
     </row>
     <row r="7">
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Not applicable</t>
-        </is>
-      </c>
       <c r="D7" t="inlineStr">
         <is>
           <t>Follow-up</t>

--- a/output/faculty_requests/SCI - SR26 sustainability reporting request.xlsx
+++ b/output/faculty_requests/SCI - SR26 sustainability reporting request.xlsx
@@ -628,7 +628,7 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
-          <t>SR26 sustainability reporting (v0.14)</t>
+          <t>SR26 sustainability reporting (v0.15)</t>
         </is>
       </c>
     </row>

--- a/output/faculty_requests/SCI - SR26 sustainability reporting request.xlsx
+++ b/output/faculty_requests/SCI - SR26 sustainability reporting request.xlsx
@@ -628,7 +628,7 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
-          <t>SR26 sustainability reporting (v0.15)</t>
+          <t>SR26 sustainability reporting (v0.16)</t>
         </is>
       </c>
     </row>

--- a/output/faculty_requests/SCI - SR26 sustainability reporting request.xlsx
+++ b/output/faculty_requests/SCI - SR26 sustainability reporting request.xlsx
@@ -20,21 +20,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="18">
+  <fonts count="16">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="Aptos"/>
-      <color rgb="00002060"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <sz val="11"/>
     </font>
     <font>
       <name val="Aptos"/>
@@ -178,61 +170,59 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -620,32 +610,22 @@
     <col width="24" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>SR26 sustainability reporting (v0.16)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="B2" s="3" t="inlineStr">
+    <row r="1"/>
+    <row r="2" ht="39" customHeight="1">
+      <c r="B2" s="1" t="inlineStr">
         <is>
           <t>SR26 sustainability reporting request</t>
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>How to use this spreadsheet:</t>
         </is>
       </c>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>• For each row below, describe progress towards the target (Column L) and/or respond to the 2026 reporting request (Column M)
 • Provide supporting information if required (Column N), including links to documents or images
@@ -661,199 +641,202 @@
     <row r="6"/>
     <row r="7"/>
     <row r="8" ht="60" customHeight="1"/>
-    <row r="11">
-      <c r="B11" s="6" t="inlineStr">
+    <row r="9"/>
+    <row r="10"/>
+    <row r="11" ht="39" customHeight="1">
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t>SCI – Faculty of Science</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="C13" s="7" t="inlineStr">
+    <row r="12"/>
+    <row r="13" ht="27" customHeight="1">
+      <c r="C13" s="5" t="inlineStr">
         <is>
           <t>Sustainability 2030 target and indicator</t>
         </is>
       </c>
-      <c r="H13" s="7" t="inlineStr">
+      <c r="H13" s="5" t="inlineStr">
         <is>
           <t>SR25 response</t>
         </is>
       </c>
-      <c r="L13" s="8" t="inlineStr">
+      <c r="L13" s="6" t="inlineStr">
         <is>
           <t>End-2026 reporting (PLEASE COMPLETE THIS SECTION)</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="B14" s="9" t="inlineStr">
+    <row r="14" ht="60" customHeight="1">
+      <c r="B14" s="7" t="inlineStr">
         <is>
           <t>Ref</t>
         </is>
       </c>
-      <c r="C14" s="9" t="inlineStr">
+      <c r="C14" s="7" t="inlineStr">
         <is>
           <t>Priority area</t>
         </is>
       </c>
-      <c r="D14" s="9" t="inlineStr">
+      <c r="D14" s="7" t="inlineStr">
         <is>
           <t>Sustainability 2030 target</t>
         </is>
       </c>
-      <c r="E14" s="9" t="inlineStr">
+      <c r="E14" s="7" t="inlineStr">
         <is>
           <t>Indicator</t>
         </is>
       </c>
-      <c r="F14" s="9" t="inlineStr">
+      <c r="F14" s="7" t="inlineStr">
         <is>
           <t>2026 Reporting request</t>
         </is>
       </c>
-      <c r="G14" s="9" t="inlineStr">
+      <c r="G14" s="7" t="inlineStr">
         <is>
           <t>How SST will use this data</t>
         </is>
       </c>
-      <c r="H14" s="9" t="inlineStr">
+      <c r="H14" s="7" t="inlineStr">
         <is>
           <t>Related SR25 ref</t>
         </is>
       </c>
-      <c r="I14" s="9" t="inlineStr">
+      <c r="I14" s="7" t="inlineStr">
         <is>
           <t>End-2025 confirmed status</t>
         </is>
       </c>
-      <c r="J14" s="9" t="inlineStr">
+      <c r="J14" s="7" t="inlineStr">
         <is>
           <t>End-2025 reporting response</t>
         </is>
       </c>
-      <c r="K14" s="9" t="inlineStr">
+      <c r="K14" s="7" t="inlineStr">
         <is>
           <t>Links and supporting information</t>
         </is>
       </c>
-      <c r="L14" s="10" t="inlineStr">
+      <c r="L14" s="8" t="inlineStr">
         <is>
           <t>OPTION 1:  Target-level reporting (Column D)</t>
         </is>
       </c>
-      <c r="M14" s="10" t="inlineStr">
+      <c r="M14" s="8" t="inlineStr">
         <is>
           <t>OPTION 2:  Indicator level reporting (Column E/F)</t>
         </is>
       </c>
-      <c r="N14" s="10" t="inlineStr">
+      <c r="N14" s="8" t="inlineStr">
         <is>
           <t>Supporting information/comments</t>
         </is>
       </c>
-      <c r="O14" s="10" t="inlineStr">
+      <c r="O14" s="8" t="inlineStr">
         <is>
           <t>Data source and limitations</t>
         </is>
       </c>
-      <c r="P14" s="10" t="inlineStr">
+      <c r="P14" s="8" t="inlineStr">
         <is>
           <t>Data owner confirms information is accurate</t>
         </is>
       </c>
-      <c r="Q14" s="10" t="inlineStr">
+      <c r="Q14" s="8" t="inlineStr">
         <is>
           <t>Confirmed by (name, role, date)</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="B15" s="11" t="inlineStr"/>
-      <c r="C15" s="11" t="inlineStr"/>
-      <c r="D15" s="11" t="inlineStr"/>
-      <c r="E15" s="11" t="inlineStr"/>
-      <c r="F15" s="11" t="inlineStr"/>
-      <c r="G15" s="11" t="inlineStr"/>
-      <c r="H15" s="11" t="inlineStr"/>
-      <c r="I15" s="11" t="inlineStr"/>
-      <c r="J15" s="11" t="inlineStr"/>
-      <c r="K15" s="11" t="inlineStr"/>
-      <c r="L15" s="11" t="inlineStr">
+    <row r="15" ht="81" customHeight="1">
+      <c r="B15" s="9" t="inlineStr"/>
+      <c r="C15" s="9" t="inlineStr"/>
+      <c r="D15" s="9" t="inlineStr"/>
+      <c r="E15" s="9" t="inlineStr"/>
+      <c r="F15" s="9" t="inlineStr"/>
+      <c r="G15" s="9" t="inlineStr"/>
+      <c r="H15" s="9" t="inlineStr"/>
+      <c r="I15" s="9" t="inlineStr"/>
+      <c r="J15" s="9" t="inlineStr"/>
+      <c r="K15" s="9" t="inlineStr"/>
+      <c r="L15" s="9" t="inlineStr">
         <is>
           <t>A general update on activities in relation to the overarching target (Column D)</t>
         </is>
       </c>
-      <c r="M15" s="11" t="inlineStr">
+      <c r="M15" s="9" t="inlineStr">
         <is>
           <t>Data and commentary in direct response to the reporting request (Column F)</t>
         </is>
       </c>
-      <c r="N15" s="11" t="inlineStr">
+      <c r="N15" s="9" t="inlineStr">
         <is>
           <t>Any additional information (e.g. links, images, documents)</t>
         </is>
       </c>
-      <c r="O15" s="11" t="inlineStr">
+      <c r="O15" s="9" t="inlineStr">
         <is>
           <t>Where did this information come from (system, report, survey, person)? Note any gaps or limitations.</t>
         </is>
       </c>
-      <c r="P15" s="11" t="inlineStr">
+      <c r="P15" s="9" t="inlineStr">
         <is>
           <t>Select 'Yes' to confirm the information provided is accurate and can be used for reporting</t>
         </is>
       </c>
-      <c r="Q15" s="11" t="inlineStr">
+      <c r="Q15" s="9" t="inlineStr">
         <is>
           <t>Name, role and date of the person confirming</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="150" customHeight="1">
-      <c r="B16" s="12" t="inlineStr">
+    <row r="16" ht="320" customHeight="1">
+      <c r="B16" s="10" t="inlineStr">
         <is>
           <t>EE1(a)</t>
         </is>
       </c>
-      <c r="C16" s="13" t="inlineStr">
+      <c r="C16" s="11" t="inlineStr">
         <is>
           <t>Exceptional education</t>
         </is>
       </c>
-      <c r="D16" s="13" t="inlineStr">
+      <c r="D16" s="11" t="inlineStr">
         <is>
           <t>Provide our students with learning experiences that help them build the knowledge, skills and relationships to lead change for sustainable societies.</t>
         </is>
       </c>
-      <c r="E16" s="13" t="inlineStr">
+      <c r="E16" s="11" t="inlineStr">
         <is>
           <t>Evidence of innovative approaches to sustainability teaching and learning</t>
         </is>
       </c>
-      <c r="F16" s="14" t="inlineStr">
+      <c r="F16" s="12" t="inlineStr">
         <is>
           <t>In end-2025 reporting your faculty reported on the related SP2030 target 4a(ii) (click the ref in Column H to see it in full in Tab 3). Please build on this rather than repeating it, focusing on what is new in 2026.
 Please give any examples from 2026 of how your faculty has embedded sustainability in teaching and learning. This could include innovative approaches (e.g. new or redesigned subjects, curriculum design, pedagogies, assessment or learning resources) and sustainability-focused experiential or co-curricular learning (e.g. industry or community projects, fieldwork, internships, student challenges). Include links and approximate student participation where known.
 This question also covers indicator EE1(c). Melbourne Plus and the Wattle Fellowship will be collected separately – no need to report these.</t>
         </is>
       </c>
-      <c r="G16" s="14" t="inlineStr">
+      <c r="G16" s="12" t="inlineStr">
         <is>
           <t>We will collate examples of sustainability teaching and learning, including experiential and co-curricular learning, across faculties to inform the Exceptional education section of the 2026 Sustainability Report. Strong examples may be followed up for the report.</t>
         </is>
       </c>
-      <c r="H16" s="15" t="inlineStr">
+      <c r="H16" s="13" t="inlineStr">
         <is>
           <t>4a(ii)
 → view SR25 response</t>
         </is>
       </c>
-      <c r="I16" s="14" t="inlineStr">
+      <c r="I16" s="12" t="inlineStr">
         <is>
           <t>Met or exceeded</t>
         </is>
       </c>
-      <c r="J16" s="14" t="inlineStr">
+      <c r="J16" s="12" t="inlineStr">
         <is>
           <t>Sustainability, conservation, biodiversity are elements of most courses and majors within the FoS. Several additional courses are being considered at PG level in 2026
 The FoS education strategy https://staff.unimelb.edu.au/science/learning-and-teaching-support/education-strategy has been developed with the following targets related to sustainability:  
@@ -863,106 +846,106 @@
 With the 12 month implementation plan noting that: "Understanding our students’ carbon footprint is the first step towards incorporating sustainability in teaching and learning."</t>
         </is>
       </c>
-      <c r="K16" s="14" t="inlineStr"/>
-      <c r="L16" s="16" t="n"/>
-      <c r="M16" s="16" t="n"/>
-      <c r="N16" s="16" t="n"/>
-      <c r="O16" s="16" t="n"/>
-      <c r="P16" s="16" t="n"/>
-      <c r="Q16" s="16" t="n"/>
-    </row>
-    <row r="17" ht="150" customHeight="1">
-      <c r="B17" s="12" t="inlineStr">
+      <c r="K16" s="12" t="inlineStr"/>
+      <c r="L16" s="14" t="n"/>
+      <c r="M16" s="14" t="n"/>
+      <c r="N16" s="14" t="n"/>
+      <c r="O16" s="14" t="n"/>
+      <c r="P16" s="14" t="n"/>
+      <c r="Q16" s="14" t="n"/>
+    </row>
+    <row r="17" ht="188" customHeight="1">
+      <c r="B17" s="10" t="inlineStr">
         <is>
           <t>EE1(b)</t>
         </is>
       </c>
-      <c r="C17" s="13" t="inlineStr">
+      <c r="C17" s="11" t="inlineStr">
         <is>
           <t>Exceptional education</t>
         </is>
       </c>
-      <c r="D17" s="13" t="inlineStr">
+      <c r="D17" s="11" t="inlineStr">
         <is>
           <t>Provide our students with learning experiences that help them build the knowledge, skills and relationships to lead change for sustainable societies.</t>
         </is>
       </c>
-      <c r="E17" s="13" t="inlineStr">
+      <c r="E17" s="11" t="inlineStr">
         <is>
           <t>Pilots of possible approaches for understanding and developing students’ sustainability self-efficacy</t>
         </is>
       </c>
-      <c r="F17" s="14" t="inlineStr">
+      <c r="F17" s="12" t="inlineStr">
         <is>
           <t>Has your faculty piloted or trialled any approach in 2026 to understand or build students' confidence and capability to act on sustainability (sustainability self-efficacy)? If yes, briefly describe the approach, participating cohort, what was learned and next steps. If not, please respond 'none in 2026' – this is a new indicator and a nil response is useful.
 We are aware of the Sustainability Strengths Compass Living Lab project (CLLAP) and will collect it separately.</t>
         </is>
       </c>
-      <c r="G17" s="14" t="inlineStr">
+      <c r="G17" s="12" t="inlineStr">
         <is>
           <t>This is a new indicator. We will use responses to establish a baseline of how (and whether) faculties are understanding student sustainability self-efficacy, and report on early pilots in the 2026 Sustainability Report. A nil response is useful to us.</t>
         </is>
       </c>
-      <c r="H17" s="14" t="inlineStr">
+      <c r="H17" s="12" t="inlineStr">
         <is>
           <t>N/A – new indicator</t>
         </is>
       </c>
-      <c r="I17" s="14" t="inlineStr"/>
-      <c r="J17" s="14" t="inlineStr"/>
-      <c r="K17" s="14" t="inlineStr"/>
-      <c r="L17" s="16" t="n"/>
-      <c r="M17" s="16" t="n"/>
-      <c r="N17" s="16" t="n"/>
-      <c r="O17" s="16" t="n"/>
-      <c r="P17" s="16" t="n"/>
-      <c r="Q17" s="16" t="n"/>
-    </row>
-    <row r="18" ht="150" customHeight="1">
-      <c r="B18" s="12" t="inlineStr">
+      <c r="I17" s="12" t="inlineStr"/>
+      <c r="J17" s="12" t="inlineStr"/>
+      <c r="K17" s="12" t="inlineStr"/>
+      <c r="L17" s="14" t="n"/>
+      <c r="M17" s="14" t="n"/>
+      <c r="N17" s="14" t="n"/>
+      <c r="O17" s="14" t="n"/>
+      <c r="P17" s="14" t="n"/>
+      <c r="Q17" s="14" t="n"/>
+    </row>
+    <row r="18" ht="303" customHeight="1">
+      <c r="B18" s="10" t="inlineStr">
         <is>
           <t>TR1(a)</t>
         </is>
       </c>
-      <c r="C18" s="13" t="inlineStr">
+      <c r="C18" s="11" t="inlineStr">
         <is>
           <t>Transformational research</t>
         </is>
       </c>
-      <c r="D18" s="13" t="inlineStr">
+      <c r="D18" s="11" t="inlineStr">
         <is>
           <t>Utilise the expertise of the University’s researchers through mutually beneficial partnerships to help address the University’s operational sustainability challenges.</t>
         </is>
       </c>
-      <c r="E18" s="13" t="inlineStr">
+      <c r="E18" s="11" t="inlineStr">
         <is>
           <t>Expert-reviewed evidence of researchers contributing to operational sustainability priorities through partnerships, advisory input, living labs, applied projects or decision-support</t>
         </is>
       </c>
-      <c r="F18" s="14" t="inlineStr">
+      <c r="F18" s="12" t="inlineStr">
         <is>
           <t>In end-2025 reporting your faculty reported on the related SP2030 target 2a (click the ref in Column H to see it in full in Tab 3). Please build on this rather than repeating it, focusing on what is new in 2026.
 Please give any examples from 2026 of researchers in your faculty contributing to the University's own operational sustainability challenges (e.g. advising on campus energy, biodiversity, waste or buildings; applied projects; decision-support tools). Briefly describe the operational challenge, the researchers' contribution, the University team involved and the result.
 We will collect Campus Living Lab Accelerator Program (CLLAP) projects separately from CI&amp;S – please include other examples only.</t>
         </is>
       </c>
-      <c r="G18" s="14" t="inlineStr">
+      <c r="G18" s="12" t="inlineStr">
         <is>
           <t>We will report on examples of researchers helping solve the University's own operational sustainability challenges, alongside CLLAP projects reported by CI&amp;S, and share them with operational teams to identify further collaboration.</t>
         </is>
       </c>
-      <c r="H18" s="15" t="inlineStr">
+      <c r="H18" s="13" t="inlineStr">
         <is>
           <t>2a
 → view SR25 response</t>
         </is>
       </c>
-      <c r="I18" s="14" t="inlineStr">
+      <c r="I18" s="12" t="inlineStr">
         <is>
           <t>Partially met</t>
         </is>
       </c>
-      <c r="J18" s="14" t="inlineStr">
+      <c r="J18" s="12" t="inlineStr">
         <is>
           <t>The faculty has many projects that can be considered living labs. A centralised approach is required to document them.
 2025 examples include how the undergraduate chemistry teaching laboratories redesigned their practicals to use less reagents and safer chemicals to achieve the same learning outcomes.
@@ -970,64 +953,64 @@
 SAFES have worked on Indigenous food gardens and have an Indigenous food guide and there are examples of urban and woodland greening that serve as best practice examples across Australia</t>
         </is>
       </c>
-      <c r="K18" s="14" t="inlineStr">
+      <c r="K18" s="12" t="inlineStr">
         <is>
           <t>https://www.unimelb.edu.au/newsroom/news/2024/october/native-harvest-cookbook-aims-to-put-indigenous-food-in-every-aussie-kitchen
 https://theconversation.com/we-planted-two-woody-meadows-a-decade-ago-to-see-what-would-thrive-now-the-concept-is-popular-across-australia-269611</t>
         </is>
       </c>
-      <c r="L18" s="16" t="n"/>
-      <c r="M18" s="16" t="n"/>
-      <c r="N18" s="16" t="n"/>
-      <c r="O18" s="16" t="n"/>
-      <c r="P18" s="16" t="n"/>
-      <c r="Q18" s="16" t="n"/>
-    </row>
-    <row r="19" ht="150" customHeight="1">
-      <c r="B19" s="12" t="inlineStr">
+      <c r="L18" s="14" t="n"/>
+      <c r="M18" s="14" t="n"/>
+      <c r="N18" s="14" t="n"/>
+      <c r="O18" s="14" t="n"/>
+      <c r="P18" s="14" t="n"/>
+      <c r="Q18" s="14" t="n"/>
+    </row>
+    <row r="19" ht="286" customHeight="1">
+      <c r="B19" s="10" t="inlineStr">
         <is>
           <t>TR2(a)</t>
         </is>
       </c>
-      <c r="C19" s="13" t="inlineStr">
+      <c r="C19" s="11" t="inlineStr">
         <is>
           <t>Transformational research</t>
         </is>
       </c>
-      <c r="D19" s="13" t="inlineStr">
+      <c r="D19" s="11" t="inlineStr">
         <is>
           <t>Deliver high-quality research and partnerships that contribute to sustainability outcomes and demonstrable societal benefit.</t>
         </is>
       </c>
-      <c r="E19" s="13" t="inlineStr">
+      <c r="E19" s="11" t="inlineStr">
         <is>
           <t>Evidence of sustainability-related research impact across diverse pathways, could include policy, industry, community, practice, cultural and institutional outcomes</t>
         </is>
       </c>
-      <c r="F19" s="14" t="inlineStr">
+      <c r="F19" s="12" t="inlineStr">
         <is>
           <t>In end-2025 reporting your faculty reported on the related SP2030 target 5b(i) (click the ref in Column H to see it in full in Tab 3). Please build on this rather than repeating it, focusing on what is new in 2026.
 Please give any examples from 2026 of sustainability-related research from your faculty that has had impact beyond academia – on policy, industry, community, practice, cultural or institutional outcomes. Briefly describe the research, the partner or user, and the resulting change or influence, with links (e.g. Pursuit articles, policy submissions, reports).
 We will source University-wide research metrics (e.g. SDG-mapped publications via SciVal) from MRE – publication counts are not required.</t>
         </is>
       </c>
-      <c r="G19" s="14" t="inlineStr">
+      <c r="G19" s="12" t="inlineStr">
         <is>
           <t>We will collate research impact examples across faculties to show the breadth of sustainability-related research impact in the Transformational research section of the 2026 Sustainability Report, complementing University-wide metrics from MRE.</t>
         </is>
       </c>
-      <c r="H19" s="15" t="inlineStr">
+      <c r="H19" s="13" t="inlineStr">
         <is>
           <t>5b(i)
 → view SR25 response</t>
         </is>
       </c>
-      <c r="I19" s="14" t="inlineStr">
+      <c r="I19" s="12" t="inlineStr">
         <is>
           <t>Met or exceeded</t>
         </is>
       </c>
-      <c r="J19" s="14" t="inlineStr">
+      <c r="J19" s="12" t="inlineStr">
         <is>
           <t>QS rankings, SDG research outputs all attest to our strength in environmental and sustainable research. 
 We have a research strategy which has clear deliverables for sustainability, including a focus on several "Big Research Challenges" which directly relate to Sustainability https://staff.unimelb.edu.au/science/research/research-governance/research-strategy-2023-2030/FOS-Research-strategy-_INTRANET-LINKS-FIXED.pdf
@@ -1037,59 +1020,59 @@
 https://science.unimelb.edu.au/about/news/australia-and-the-pacific-islands-solidarity-in-a-time-of-climate-crisis/_nocache</t>
         </is>
       </c>
-      <c r="K19" s="14" t="inlineStr"/>
-      <c r="L19" s="16" t="n"/>
-      <c r="M19" s="16" t="n"/>
-      <c r="N19" s="16" t="n"/>
-      <c r="O19" s="16" t="n"/>
-      <c r="P19" s="16" t="n"/>
-      <c r="Q19" s="16" t="n"/>
-    </row>
-    <row r="20" ht="150" customHeight="1">
-      <c r="B20" s="12" t="inlineStr">
+      <c r="K19" s="12" t="inlineStr"/>
+      <c r="L19" s="14" t="n"/>
+      <c r="M19" s="14" t="n"/>
+      <c r="N19" s="14" t="n"/>
+      <c r="O19" s="14" t="n"/>
+      <c r="P19" s="14" t="n"/>
+      <c r="Q19" s="14" t="n"/>
+    </row>
+    <row r="20" ht="270" customHeight="1">
+      <c r="B20" s="10" t="inlineStr">
         <is>
           <t>TR2(d)</t>
         </is>
       </c>
-      <c r="C20" s="13" t="inlineStr">
+      <c r="C20" s="11" t="inlineStr">
         <is>
           <t>Transformational research</t>
         </is>
       </c>
-      <c r="D20" s="13" t="inlineStr">
+      <c r="D20" s="11" t="inlineStr">
         <is>
           <t>Deliver high-quality research and partnerships that contribute to sustainability outcomes and demonstrable societal benefit.</t>
         </is>
       </c>
-      <c r="E20" s="13" t="inlineStr">
+      <c r="E20" s="11" t="inlineStr">
         <is>
           <t>Case-based evidence demonstrating how research has contributed to meaningful sustainability outcomes.</t>
         </is>
       </c>
-      <c r="F20" s="14" t="inlineStr">
+      <c r="F20" s="12" t="inlineStr">
         <is>
           <t>In end-2025 reporting your faculty reported on the related SP2030 target 5b(i) (click the ref in Column H to see it in full in Tab 3). Please build on this rather than repeating it, focusing on what is new in 2026.
 Please give any examples of research activity from your faculty that has contributed to a meaningful sustainability outcome: the research, stakeholders involved, pathway to impact and evidence of the outcome. These can be the examples from TR2(a) described in more detail.
 We are also seeking examples from Melbourne Climate Futures, the Melbourne Biodiversity Institute and Strategic Communications.</t>
         </is>
       </c>
-      <c r="G20" s="14" t="inlineStr">
+      <c r="G20" s="12" t="inlineStr">
         <is>
           <t>We will select the strongest examples to develop as full research case studies for the 2026 Sustainability Report (we may contact you for more detail and images).</t>
         </is>
       </c>
-      <c r="H20" s="15" t="inlineStr">
+      <c r="H20" s="13" t="inlineStr">
         <is>
           <t>5b(i)
 → view SR25 response</t>
         </is>
       </c>
-      <c r="I20" s="14" t="inlineStr">
+      <c r="I20" s="12" t="inlineStr">
         <is>
           <t>Met or exceeded</t>
         </is>
       </c>
-      <c r="J20" s="14" t="inlineStr">
+      <c r="J20" s="12" t="inlineStr">
         <is>
           <t>QS rankings, SDG research outputs all attest to our strength in environmental and sustainable research. 
 We have a research strategy which has clear deliverables for sustainability, including a focus on several "Big Research Challenges" which directly relate to Sustainability https://staff.unimelb.edu.au/science/research/research-governance/research-strategy-2023-2030/FOS-Research-strategy-_INTRANET-LINKS-FIXED.pdf
@@ -1099,58 +1082,58 @@
 https://science.unimelb.edu.au/about/news/australia-and-the-pacific-islands-solidarity-in-a-time-of-climate-crisis/_nocache</t>
         </is>
       </c>
-      <c r="K20" s="14" t="inlineStr"/>
-      <c r="L20" s="16" t="n"/>
-      <c r="M20" s="16" t="n"/>
-      <c r="N20" s="16" t="n"/>
-      <c r="O20" s="16" t="n"/>
-      <c r="P20" s="16" t="n"/>
-      <c r="Q20" s="16" t="n"/>
-    </row>
-    <row r="21" ht="150" customHeight="1">
-      <c r="B21" s="12" t="inlineStr">
+      <c r="K20" s="12" t="inlineStr"/>
+      <c r="L20" s="14" t="n"/>
+      <c r="M20" s="14" t="n"/>
+      <c r="N20" s="14" t="n"/>
+      <c r="O20" s="14" t="n"/>
+      <c r="P20" s="14" t="n"/>
+      <c r="Q20" s="14" t="n"/>
+    </row>
+    <row r="21" ht="220" customHeight="1">
+      <c r="B21" s="10" t="inlineStr">
         <is>
           <t>TR3(b)</t>
         </is>
       </c>
-      <c r="C21" s="13" t="inlineStr">
+      <c r="C21" s="11" t="inlineStr">
         <is>
           <t>Transformational research</t>
         </is>
       </c>
-      <c r="D21" s="13" t="inlineStr">
+      <c r="D21" s="11" t="inlineStr">
         <is>
           <t>Embed sustainability within research systems, processes, capability and culture, so research is conducted responsibly, efficiently and with reduced environmental impact.</t>
         </is>
       </c>
-      <c r="E21" s="13" t="inlineStr">
+      <c r="E21" s="11" t="inlineStr">
         <is>
           <t>Demonstrated examples of more sustainable research practices in laboratories, fieldwork, procurement, travel or infrastructure use</t>
         </is>
       </c>
-      <c r="F21" s="14" t="inlineStr">
+      <c r="F21" s="12" t="inlineStr">
         <is>
           <t>In end-2025 reporting your faculty reported on the related SP2030 target 5c(ii) (click the ref in Column H to see it in full in Tab 3). Please build on this rather than repeating it, focusing on what is new in 2026.
 Are there any efforts within the faculty to make research practices more sustainable (e.g. green lab certification, equipment sharing, reduced research travel, sustainable fieldwork, sustainable procurement of research consumables)? If so, please give any examples and any evidence of uptake, resource savings or emissions reductions.</t>
         </is>
       </c>
-      <c r="G21" s="14" t="inlineStr">
+      <c r="G21" s="12" t="inlineStr">
         <is>
           <t>We will report on ways the University is making research practices more sustainable in the 2026 Sustainability Report, and share practical examples (e.g. green labs) across faculties.</t>
         </is>
       </c>
-      <c r="H21" s="15" t="inlineStr">
+      <c r="H21" s="13" t="inlineStr">
         <is>
           <t>5c(ii)
 → view SR25 response</t>
         </is>
       </c>
-      <c r="I21" s="14" t="inlineStr">
+      <c r="I21" s="12" t="inlineStr">
         <is>
           <t>Partially met</t>
         </is>
       </c>
-      <c r="J21" s="14" t="inlineStr">
+      <c r="J21" s="12" t="inlineStr">
         <is>
           <t>We have a research strategy and implimentation plan which has clear deliverables for sustainability; 
 Link for Research strategy: https://staff.unimelb.edu.au/science/research/research-governance/research-strategy-2023-2030               
@@ -1158,58 +1141,58 @@
 which for example includes "Action 10. Improve sustainability of our core business practices"</t>
         </is>
       </c>
-      <c r="K21" s="14" t="inlineStr"/>
-      <c r="L21" s="16" t="n"/>
-      <c r="M21" s="16" t="n"/>
-      <c r="N21" s="16" t="n"/>
-      <c r="O21" s="16" t="n"/>
-      <c r="P21" s="16" t="n"/>
-      <c r="Q21" s="16" t="n"/>
-    </row>
-    <row r="22" ht="150" customHeight="1">
-      <c r="B22" s="12" t="inlineStr">
+      <c r="K21" s="12" t="inlineStr"/>
+      <c r="L21" s="14" t="n"/>
+      <c r="M21" s="14" t="n"/>
+      <c r="N21" s="14" t="n"/>
+      <c r="O21" s="14" t="n"/>
+      <c r="P21" s="14" t="n"/>
+      <c r="Q21" s="14" t="n"/>
+    </row>
+    <row r="22" ht="220" customHeight="1">
+      <c r="B22" s="10" t="inlineStr">
         <is>
           <t>EN1(a)</t>
         </is>
       </c>
-      <c r="C22" s="13" t="inlineStr">
+      <c r="C22" s="11" t="inlineStr">
         <is>
           <t>Enablers</t>
         </is>
       </c>
-      <c r="D22" s="13" t="inlineStr">
+      <c r="D22" s="11" t="inlineStr">
         <is>
           <t>Enablers</t>
         </is>
       </c>
-      <c r="E22" s="13" t="inlineStr">
+      <c r="E22" s="11" t="inlineStr">
         <is>
           <t>Evidence of sustainability outcomes informed by Indigenous knowledges</t>
         </is>
       </c>
-      <c r="F22" s="14" t="inlineStr">
+      <c r="F22" s="12" t="inlineStr">
         <is>
           <t>In end-2025 reporting your faculty reported on the related SP2030 target 6a (click the ref in Column H to see it in full in Tab 3). Please build on this rather than repeating it, focusing on what is new in 2026.
 Please give any examples of activity in your faculty (education, research, engagement or operations) where Indigenous knowledges informed a sustainability outcome. Describe the activity, how Indigenous knowledges were incorporated or co-created and with whom, and the result. Please confirm that appropriate permissions are in place for sharing.</t>
         </is>
       </c>
-      <c r="G22" s="14" t="inlineStr">
+      <c r="G22" s="12" t="inlineStr">
         <is>
           <t>We will report on the ways Indigenous knowledges inform sustainability activities across the University, and develop selected examples into case studies with appropriate permissions.</t>
         </is>
       </c>
-      <c r="H22" s="15" t="inlineStr">
+      <c r="H22" s="13" t="inlineStr">
         <is>
           <t>6a
 → view SR25 response</t>
         </is>
       </c>
-      <c r="I22" s="14" t="inlineStr">
+      <c r="I22" s="12" t="inlineStr">
         <is>
           <t>Partially met</t>
         </is>
       </c>
-      <c r="J22" s="14" t="inlineStr">
+      <c r="J22" s="12" t="inlineStr">
         <is>
           <t>The Faculty of Science strategy has a specific goal of "Establish Indigenous lead caring for
 country course and resources " which sits under the theme of Living Sustaianbly. 
@@ -1217,59 +1200,59 @@
 Robyn Schofield working with Murujuga Rock Art Monitoring Program and being part of the Australian delegation that saw the inscription of Murujuga as a UN World Hertiage site in 2025 is one example.</t>
         </is>
       </c>
-      <c r="K22" s="14" t="inlineStr"/>
-      <c r="L22" s="16" t="n"/>
-      <c r="M22" s="16" t="n"/>
-      <c r="N22" s="16" t="n"/>
-      <c r="O22" s="16" t="n"/>
-      <c r="P22" s="16" t="n"/>
-      <c r="Q22" s="16" t="n"/>
-    </row>
-    <row r="23" ht="150" customHeight="1">
-      <c r="B23" s="12" t="inlineStr">
+      <c r="K22" s="12" t="inlineStr"/>
+      <c r="L22" s="14" t="n"/>
+      <c r="M22" s="14" t="n"/>
+      <c r="N22" s="14" t="n"/>
+      <c r="O22" s="14" t="n"/>
+      <c r="P22" s="14" t="n"/>
+      <c r="Q22" s="14" t="n"/>
+    </row>
+    <row r="23" ht="254" customHeight="1">
+      <c r="B23" s="10" t="inlineStr">
         <is>
           <t>EN1(b)</t>
         </is>
       </c>
-      <c r="C23" s="13" t="inlineStr">
+      <c r="C23" s="11" t="inlineStr">
         <is>
           <t>Enablers</t>
         </is>
       </c>
-      <c r="D23" s="13" t="inlineStr">
+      <c r="D23" s="11" t="inlineStr">
         <is>
           <t>Enablers</t>
         </is>
       </c>
-      <c r="E23" s="13" t="inlineStr">
+      <c r="E23" s="11" t="inlineStr">
         <is>
           <t>Living laboratories enabling applied learning, research and operational sustainability outcomes</t>
         </is>
       </c>
-      <c r="F23" s="14" t="inlineStr">
+      <c r="F23" s="12" t="inlineStr">
         <is>
           <t>In end-2025 reporting your faculty reported on the related SP2030 target 2a (click the ref in Column H to see it in full in Tab 3). Please build on this rather than repeating it, focusing on what is new in 2026.
 Please give any examples of sustainability-related living labs operating within your faculty in 2026 – their activities, who is involved (students, researchers, operational staff) and their outputs, outcomes or impact.
 Please note we will approach living labs funded through the Campus Living Lab Accelerator Program (CLLAP) separately.</t>
         </is>
       </c>
-      <c r="G23" s="14" t="inlineStr">
+      <c r="G23" s="12" t="inlineStr">
         <is>
           <t>We will share examples of sustainability-related living labs from across the University in the 2026 Sustainability Report, alongside CLLAP projects reported by CI&amp;S.</t>
         </is>
       </c>
-      <c r="H23" s="15" t="inlineStr">
+      <c r="H23" s="13" t="inlineStr">
         <is>
           <t>2a
 → view SR25 response</t>
         </is>
       </c>
-      <c r="I23" s="14" t="inlineStr">
+      <c r="I23" s="12" t="inlineStr">
         <is>
           <t>Partially met</t>
         </is>
       </c>
-      <c r="J23" s="14" t="inlineStr">
+      <c r="J23" s="12" t="inlineStr">
         <is>
           <t>The faculty has many projects that can be considered living labs. A centralised approach is required to document them.
 2025 examples include how the undergraduate chemistry teaching laboratories redesigned their practicals to use less reagents and safer chemicals to achieve the same learning outcomes.
@@ -1277,75 +1260,75 @@
 SAFES have worked on Indigenous food gardens and have an Indigenous food guide and there are examples of urban and woodland greening that serve as best practice examples across Australia</t>
         </is>
       </c>
-      <c r="K23" s="14" t="inlineStr">
+      <c r="K23" s="12" t="inlineStr">
         <is>
           <t>https://www.unimelb.edu.au/newsroom/news/2024/october/native-harvest-cookbook-aims-to-put-indigenous-food-in-every-aussie-kitchen
 https://theconversation.com/we-planted-two-woody-meadows-a-decade-ago-to-see-what-would-thrive-now-the-concept-is-popular-across-australia-269611</t>
         </is>
       </c>
-      <c r="L23" s="16" t="n"/>
-      <c r="M23" s="16" t="n"/>
-      <c r="N23" s="16" t="n"/>
-      <c r="O23" s="16" t="n"/>
-      <c r="P23" s="16" t="n"/>
-      <c r="Q23" s="16" t="n"/>
-    </row>
-    <row r="24" ht="150" customHeight="1">
-      <c r="B24" s="12" t="inlineStr">
+      <c r="L23" s="14" t="n"/>
+      <c r="M23" s="14" t="n"/>
+      <c r="N23" s="14" t="n"/>
+      <c r="O23" s="14" t="n"/>
+      <c r="P23" s="14" t="n"/>
+      <c r="Q23" s="14" t="n"/>
+    </row>
+    <row r="24" ht="188" customHeight="1">
+      <c r="B24" s="10" t="inlineStr">
         <is>
           <t>EN1(c)</t>
         </is>
       </c>
-      <c r="C24" s="13" t="inlineStr">
+      <c r="C24" s="11" t="inlineStr">
         <is>
           <t>Enablers</t>
         </is>
       </c>
-      <c r="D24" s="13" t="inlineStr">
+      <c r="D24" s="11" t="inlineStr">
         <is>
           <t>Enablers</t>
         </is>
       </c>
-      <c r="E24" s="13" t="inlineStr">
+      <c r="E24" s="11" t="inlineStr">
         <is>
           <t>Coordinated internal engagement and external partnerships contributing to delivery of sustainability outcomes across priority areas.</t>
         </is>
       </c>
-      <c r="F24" s="14" t="inlineStr">
+      <c r="F24" s="12" t="inlineStr">
         <is>
           <t>In end-2025 reporting your faculty reported on the related SP2030 target 3a(ii) (click the ref in Column H to see it in full in Tab 3). Please build on this rather than repeating it, focusing on what is new in 2026.
 Please list the key sustainability-focused communities of practice, internal networks or external partnerships active in your faculty in 2026 (name, partners, priority area), and give any examples of activity that contributed to a Sustainability 2030 outcome.</t>
         </is>
       </c>
-      <c r="G24" s="14" t="inlineStr">
+      <c r="G24" s="12" t="inlineStr">
         <is>
           <t>We will report on internal engagement and partnerships contributing to Sustainability 2030 outcomes, and update our record of sustainability-focused communities of practice and contacts across the University.</t>
         </is>
       </c>
-      <c r="H24" s="15" t="inlineStr">
+      <c r="H24" s="13" t="inlineStr">
         <is>
           <t>3a(ii)
 → view SR25 response</t>
         </is>
       </c>
-      <c r="I24" s="14" t="inlineStr">
+      <c r="I24" s="12" t="inlineStr">
         <is>
           <t>Met or exceeded</t>
         </is>
       </c>
-      <c r="J24" s="14" t="inlineStr">
+      <c r="J24" s="12" t="inlineStr">
         <is>
           <t>The Associate/Assistant Deans of Sustainability exist in every faculty. While we interface with teaching, the DVCA, and A/Ds for UG and Postgraduate teaching are where the embedding of sustainability in formal learning outcomes occurs.
 In the FoS the UG Chemistry laboratory sustainability upgrades is a great example of embedding sustainability early in learning for students.</t>
         </is>
       </c>
-      <c r="K24" s="14" t="inlineStr"/>
-      <c r="L24" s="16" t="n"/>
-      <c r="M24" s="16" t="n"/>
-      <c r="N24" s="16" t="n"/>
-      <c r="O24" s="16" t="n"/>
-      <c r="P24" s="16" t="n"/>
-      <c r="Q24" s="16" t="n"/>
+      <c r="K24" s="12" t="inlineStr"/>
+      <c r="L24" s="14" t="n"/>
+      <c r="M24" s="14" t="n"/>
+      <c r="N24" s="14" t="n"/>
+      <c r="O24" s="14" t="n"/>
+      <c r="P24" s="14" t="n"/>
+      <c r="Q24" s="14" t="n"/>
     </row>
     <row r="25"/>
   </sheetData>
@@ -1396,110 +1379,102 @@
     <col width="30" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>SR26 sustainability reporting</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="B2" s="3" t="inlineStr">
+    <row r="1"/>
+    <row r="2" ht="39" customHeight="1">
+      <c r="B2" s="1" t="inlineStr">
         <is>
           <t>Highlighted stories (optional)</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="B5" s="17" t="inlineStr">
+    <row r="3"/>
+    <row r="4"/>
+    <row r="5" ht="22" customHeight="1">
+      <c r="B5" s="15" t="inlineStr">
         <is>
           <t>How to use this spreadsheet</t>
         </is>
       </c>
-      <c r="C5" s="18" t="inlineStr">
+      <c r="C5" s="16" t="inlineStr">
         <is>
           <t>Please share up to 3 stories from 2026 which highlight your faculty's/portfolio's sustainability progress and/or impact. These stories can directly relate to Sustainability 2030 targets and indicators, or sustainability more generally. Due: Tuesday 15 December 2026 (early submission helps us develop case studies).</t>
         </is>
       </c>
     </row>
     <row r="6"/>
-    <row r="8">
-      <c r="B8" s="19" t="inlineStr">
+    <row r="7"/>
+    <row r="8" ht="39" customHeight="1">
+      <c r="B8" s="17" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="C8" s="19" t="inlineStr">
+      <c r="C8" s="17" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="D8" s="19" t="inlineStr">
+      <c r="D8" s="17" t="inlineStr">
         <is>
           <t>Related Sustainability 2030 targets (optional)</t>
         </is>
       </c>
-      <c r="E8" s="19" t="inlineStr">
+      <c r="E8" s="17" t="inlineStr">
         <is>
           <t>Images and other media</t>
         </is>
       </c>
-      <c r="F8" s="19" t="inlineStr">
+      <c r="F8" s="17" t="inlineStr">
         <is>
           <t>Links and supporting documentation</t>
         </is>
       </c>
     </row>
     <row r="9" ht="90" customHeight="1">
-      <c r="B9" s="20" t="inlineStr"/>
-      <c r="C9" s="20" t="inlineStr">
+      <c r="B9" s="18" t="inlineStr"/>
+      <c r="C9" s="18" t="inlineStr">
         <is>
           <t>• Please include a brief description of a project or activity that has made a significant contribution to sustainability at the University (up to 250 words)
 • Summarise the benefits. Benefits may relate to operational outcomes, environmental/social outcomes, and sector benefits.</t>
         </is>
       </c>
-      <c r="D9" s="20" t="inlineStr"/>
-      <c r="E9" s="20" t="inlineStr">
+      <c r="D9" s="18" t="inlineStr"/>
+      <c r="E9" s="18" t="inlineStr">
         <is>
           <t>(link to OneDrive/SharePoint files or published online content preferred)</t>
         </is>
       </c>
-      <c r="F9" s="20" t="inlineStr"/>
+      <c r="F9" s="18" t="inlineStr"/>
     </row>
     <row r="10" ht="120" customHeight="1">
       <c r="A10" t="n">
         <v>1</v>
       </c>
-      <c r="B10" s="16" t="n"/>
-      <c r="C10" s="16" t="n"/>
-      <c r="D10" s="16" t="n"/>
-      <c r="E10" s="16" t="n"/>
-      <c r="F10" s="16" t="n"/>
+      <c r="B10" s="14" t="n"/>
+      <c r="C10" s="14" t="n"/>
+      <c r="D10" s="14" t="n"/>
+      <c r="E10" s="14" t="n"/>
+      <c r="F10" s="14" t="n"/>
     </row>
     <row r="11" ht="120" customHeight="1">
       <c r="A11" t="n">
         <v>2</v>
       </c>
-      <c r="B11" s="16" t="n"/>
-      <c r="C11" s="16" t="n"/>
-      <c r="D11" s="16" t="n"/>
-      <c r="E11" s="16" t="n"/>
-      <c r="F11" s="16" t="n"/>
+      <c r="B11" s="14" t="n"/>
+      <c r="C11" s="14" t="n"/>
+      <c r="D11" s="14" t="n"/>
+      <c r="E11" s="14" t="n"/>
+      <c r="F11" s="14" t="n"/>
     </row>
     <row r="12" ht="120" customHeight="1">
       <c r="A12" t="n">
         <v>3</v>
       </c>
-      <c r="B12" s="16" t="n"/>
-      <c r="C12" s="16" t="n"/>
-      <c r="D12" s="16" t="n"/>
-      <c r="E12" s="16" t="n"/>
-      <c r="F12" s="16" t="n"/>
+      <c r="B12" s="14" t="n"/>
+      <c r="C12" s="14" t="n"/>
+      <c r="D12" s="14" t="n"/>
+      <c r="E12" s="14" t="n"/>
+      <c r="F12" s="14" t="n"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="1"/>
@@ -1530,110 +1505,99 @@
     <col width="16" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>End-2025 target status assessment and reporting (for reference)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="B2" s="3" t="inlineStr">
+    <row r="1"/>
+    <row r="2" ht="39" customHeight="1">
+      <c r="B2" s="1" t="inlineStr">
         <is>
           <t>Your SR25 responses – Faculty of Science</t>
         </is>
       </c>
     </row>
     <row r="3" ht="32" customHeight="1">
-      <c r="B3" s="18" t="inlineStr">
+      <c r="B3" s="16" t="inlineStr">
         <is>
           <t>Your responses to the end-2025 reporting request, against the former Sustainability Plan 2030 (SP2030) targets. For reference only – please do not edit. Use the 'Back to request' links to return to the reporting template.</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="B4" s="21" t="inlineStr">
+    <row r="4" ht="22" customHeight="1">
+      <c r="B4" s="19" t="inlineStr">
         <is>
           <t>← Back to request</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="B5" s="22" t="inlineStr">
+    <row r="5" ht="30" customHeight="1">
+      <c r="B5" s="20" t="inlineStr">
         <is>
           <t>SCI</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="B6" s="9" t="inlineStr">
+    <row r="6" ht="42" customHeight="1">
+      <c r="B6" s="7" t="inlineStr">
         <is>
           <t>SR25 ref</t>
         </is>
       </c>
-      <c r="C6" s="9" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
         <is>
           <t>SP2030 target</t>
         </is>
       </c>
-      <c r="D6" s="9" t="inlineStr">
+      <c r="D6" s="7" t="inlineStr">
         <is>
           <t>2025 reporting request</t>
         </is>
       </c>
-      <c r="E6" s="9" t="inlineStr">
+      <c r="E6" s="7" t="inlineStr">
         <is>
           <t>Confirmed end-2025 status</t>
         </is>
       </c>
-      <c r="F6" s="9" t="inlineStr">
+      <c r="F6" s="7" t="inlineStr">
         <is>
           <t>OPTION 1: Target-level reporting</t>
         </is>
       </c>
-      <c r="G6" s="9" t="inlineStr">
+      <c r="G6" s="7" t="inlineStr">
         <is>
           <t>OPTION 2: Indicator-level reporting</t>
         </is>
       </c>
-      <c r="H6" s="9" t="inlineStr">
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>Supporting information/comments</t>
         </is>
       </c>
-      <c r="I6" s="9" t="inlineStr">
+      <c r="I6" s="7" t="inlineStr">
         <is>
           <t>Related SR26 indicator(s)</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="160" customHeight="1">
-      <c r="B7" s="12" t="inlineStr">
+    <row r="7" ht="303" customHeight="1">
+      <c r="B7" s="10" t="inlineStr">
         <is>
           <t>1a(i)</t>
         </is>
       </c>
-      <c r="C7" s="14" t="inlineStr">
+      <c r="C7" s="12" t="inlineStr">
         <is>
           <t>The University is certified carbon neutral by 2025</t>
         </is>
       </c>
-      <c r="D7" s="14" t="inlineStr">
+      <c r="D7" s="12" t="inlineStr">
         <is>
           <t>Comment on progress to reduce air travel emissions in the faculty</t>
         </is>
       </c>
-      <c r="E7" s="14" t="inlineStr">
+      <c r="E7" s="12" t="inlineStr">
         <is>
           <t>Met or exceeded</t>
         </is>
       </c>
-      <c r="F7" s="14" t="inlineStr">
+      <c r="F7" s="12" t="inlineStr">
         <is>
           <t>Provide commentary with reference to data in the Flights dashboard (link in Column O)
 Science:
@@ -1644,47 +1608,47 @@
 2025 emissions are tracking at  3312 tCO2e for science - this would again achieve a 10% reduction from 2019 emissions (target: &lt;3547 tCO2e). However, the emission intensity just from flights is higher than the goal of 2.7tCO2eq per person for total workplace emissions to be in line with Paris goals.</t>
         </is>
       </c>
-      <c r="G7" s="14" t="inlineStr">
+      <c r="G7" s="12" t="inlineStr">
         <is>
           <t>For context: In order to have a reasonable chance of staying below 2oC the per capita carbon emissions per year should be below ~8.2 tCO2eq per person per year (calculated from total 3700Gt CO2 eq budget to 2050 and assuming 9 billion people on Earth). As time at work consistutes about 1/3 of a person's life this gives ~2.7 tCO2eq per person would be a scientifically based target for total workplace emissions (including flights). Note: in 2023 Australians emitted ~14.5 tCO2eq per person.
  [link 3700 GtCO2eq target: https://www.climatechangeauthority.gov.au/sites/default/files/Targets%20and%20Progress%20Review%20Final%20Report_Chapter%203.pdf]</t>
         </is>
       </c>
-      <c r="H7" s="14" t="inlineStr">
+      <c r="H7" s="12" t="inlineStr">
         <is>
           <t>https://app.powerbi.com/links/SI8xYFLga4?ctid=0e5bf3cf-1ff4-46b7-9176-52c538c22a4d&amp;pbi_source=linkShare&amp;bookmarkGuid=499326eb-68f1-43e0-a3e6-0f252ee44ccb</t>
         </is>
       </c>
-      <c r="I7" s="14" t="inlineStr"/>
-    </row>
-    <row r="8" ht="160" customHeight="1">
-      <c r="B8" s="12" t="inlineStr">
+      <c r="I7" s="12" t="inlineStr"/>
+    </row>
+    <row r="8" ht="237" customHeight="1">
+      <c r="B8" s="10" t="inlineStr">
         <is>
           <t>2a</t>
         </is>
       </c>
-      <c r="C8" s="14" t="inlineStr">
+      <c r="C8" s="12" t="inlineStr">
         <is>
           <t>The University has curated living labs covering the priority areas of this Plan</t>
         </is>
       </c>
-      <c r="D8" s="14" t="inlineStr">
+      <c r="D8" s="12" t="inlineStr">
         <is>
           <t>Please provide a case study of a living lab which operates within the faculty/portfolio, including a description of its activities and impact. 
 Please note we will approach living labs funded through the Campus Living Lab Accelerator program (CLLAP) separately report on their activities.</t>
         </is>
       </c>
-      <c r="E8" s="14" t="inlineStr">
+      <c r="E8" s="12" t="inlineStr">
         <is>
           <t>Partially met</t>
         </is>
       </c>
-      <c r="F8" s="14" t="inlineStr">
+      <c r="F8" s="12" t="inlineStr">
         <is>
           <t>The faculty has many projects that can be considered living labs. A centralised approach is required to document them.</t>
         </is>
       </c>
-      <c r="G8" s="14" t="inlineStr">
+      <c r="G8" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">
 2025 examples include how the undergraduate chemistry teaching laboratories redesigned their practicals to use less reagents and safer chemicals to achieve the same learning outcomes.
@@ -1692,159 +1656,159 @@
 SAFES have worked on Indigenous food gardens and have an Indigenous food guide and there are examples of urban and woodland greening that serve as best practice examples across Australia</t>
         </is>
       </c>
-      <c r="H8" s="14" t="inlineStr">
+      <c r="H8" s="12" t="inlineStr">
         <is>
           <t>https://www.unimelb.edu.au/newsroom/news/2024/october/native-harvest-cookbook-aims-to-put-indigenous-food-in-every-aussie-kitchen
 https://theconversation.com/we-planted-two-woody-meadows-a-decade-ago-to-see-what-would-thrive-now-the-concept-is-popular-across-australia-269611</t>
         </is>
       </c>
-      <c r="I8" s="14" t="inlineStr">
+      <c r="I8" s="12" t="inlineStr">
         <is>
           <t>TR1(a), EN1(b)</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="160" customHeight="1">
-      <c r="B9" s="12" t="inlineStr">
+    <row r="9" ht="237" customHeight="1">
+      <c r="B9" s="10" t="inlineStr">
         <is>
           <t>3a(i)</t>
         </is>
       </c>
-      <c r="C9" s="14" t="inlineStr">
+      <c r="C9" s="12" t="inlineStr">
         <is>
           <t>The University's Academic Divisions and portfolios support and learn from each other to embed sustainability in practice and in learning – formal, non-formal and informal</t>
         </is>
       </c>
-      <c r="D9" s="14" t="inlineStr">
+      <c r="D9" s="12" t="inlineStr">
         <is>
           <t>Please update data on sustainability-focused staff in the faculty/portfolio provided in the previous reporting period (additional staff/those who have left the University) (see Columns G [2024] and J [mid-2025])</t>
         </is>
       </c>
-      <c r="E9" s="14" t="inlineStr">
+      <c r="E9" s="12" t="inlineStr">
         <is>
           <t>Met or exceeded</t>
         </is>
       </c>
-      <c r="F9" s="14" t="inlineStr">
+      <c r="F9" s="12" t="inlineStr">
         <is>
           <t>2025 saw the faculty of science develop a strategy - with goals in sustainability detailed here: https://staff.unimelb.edu.au/science/temporary-assets-and-links/Draft-FoS-Strategic-Priorities-All-Staff-Forum-August-2025.pdf (not to be shared externally)
 We are the custodian faculty for the Melbourne Biodiversity Institute and Melbourne Energy Institute, we also contribute to Melbourne climate futures.
 Several of our researchers are lead authors under the IPCC assessment report 7: https://www.unimelb.edu.au/newsroom/news/2025/august/university-of-melbourne-researchers-contributing-to-global-climate-report</t>
         </is>
       </c>
-      <c r="G9" s="14" t="inlineStr">
+      <c r="G9" s="12" t="inlineStr">
         <is>
           <t>The faculty of science has sustainability focused staff that cover all of the SDGs with 590 staff members producing more than 4 outputs that fall under the SDG framework (8630 research outputs). 
 With a total of 954 academic staff members  in the Faculty of Science (857 FTE) -  62% (69% when considering FTE) of our staff have significant SDG aligned research outputs (&gt;4 outputs)</t>
         </is>
       </c>
-      <c r="H9" s="14" t="inlineStr">
+      <c r="H9" s="12" t="inlineStr">
         <is>
           <t>https://app.powerbi.com/groups/me/reports/10687142-d5e8-46ef-b6f9-3adbbe5950c9/7913ae78325b04001d16?ctid=0e5bf3cf-1ff4-46b7-9176-52c538c22a4d&amp;experience=power-bi</t>
         </is>
       </c>
-      <c r="I9" s="14" t="inlineStr"/>
+      <c r="I9" s="12" t="inlineStr"/>
     </row>
     <row r="10" ht="160" customHeight="1">
-      <c r="B10" s="12" t="inlineStr">
+      <c r="B10" s="10" t="inlineStr">
         <is>
           <t>3a(ii)</t>
         </is>
       </c>
-      <c r="C10" s="14" t="inlineStr">
+      <c r="C10" s="12" t="inlineStr">
         <is>
           <t>The University's Academic Divisions and portfolios support and learn from each other to embed sustainability in practice and in learning – formal, non-formal and informal</t>
         </is>
       </c>
-      <c r="D10" s="14" t="inlineStr">
+      <c r="D10" s="12" t="inlineStr">
         <is>
           <t>Please list sustainability-focused knowledge sharing activities or communities of practice active in the faculty/portfolio in 2025, and provide a short case study of one of these.</t>
         </is>
       </c>
-      <c r="E10" s="14" t="inlineStr">
+      <c r="E10" s="12" t="inlineStr">
         <is>
           <t>Met or exceeded</t>
         </is>
       </c>
-      <c r="F10" s="14" t="inlineStr">
+      <c r="F10" s="12" t="inlineStr">
         <is>
           <t>The Associate/Assistant Deans of Sustainability exist in every faculty. While we interface with teaching, the DVCA, and A/Ds for UG and Postgraduate teaching are where the embedding of sustainability in formal learning outcomes occurs.</t>
         </is>
       </c>
-      <c r="G10" s="14" t="inlineStr">
+      <c r="G10" s="12" t="inlineStr">
         <is>
           <t>In the FoS the UG Chemistry laboratory sustainability upgrades is a great example of embedding sustainability early in learning for students.</t>
         </is>
       </c>
-      <c r="H10" s="14" t="inlineStr"/>
-      <c r="I10" s="14" t="inlineStr">
+      <c r="H10" s="12" t="inlineStr"/>
+      <c r="I10" s="12" t="inlineStr">
         <is>
           <t>EN1(c)</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="160" customHeight="1">
-      <c r="B11" s="12" t="inlineStr">
+    <row r="11" ht="188" customHeight="1">
+      <c r="B11" s="10" t="inlineStr">
         <is>
           <t>3d(ii)</t>
         </is>
       </c>
-      <c r="C11" s="14" t="inlineStr">
+      <c r="C11" s="12" t="inlineStr">
         <is>
           <t>Academic and professional staff have increased their participation in and contribution to formal and non_x0002_formal learning to develop their general and role-specific sustainability skills</t>
         </is>
       </c>
-      <c r="D11" s="14" t="inlineStr">
+      <c r="D11" s="12" t="inlineStr">
         <is>
           <t>Have any staff participated in sustainability-focused professional development in 2025? If yes, what kinds of activities have staff participated in and how are these learnings being applied in the faculty/portfolio?
 Please note, there is no need to include data on participation in Green Impact ('Green teams'), as this is reported on centrally.</t>
         </is>
       </c>
-      <c r="E11" s="14" t="inlineStr">
+      <c r="E11" s="12" t="inlineStr">
         <is>
           <t>Partially met</t>
         </is>
       </c>
-      <c r="F11" s="14" t="inlineStr">
+      <c r="F11" s="12" t="inlineStr">
         <is>
           <t>The Associate/Assistant Deans of Sustainability is heavily involved cross-faculty programs to share ideas.</t>
         </is>
       </c>
-      <c r="G11" s="14" t="inlineStr">
+      <c r="G11" s="12" t="inlineStr">
         <is>
           <t>Suggest that the relevant trainme model is promoted centrally to all faculties: https://uomtrainme.elmotalent.com.au/learning/view-activity/833/scorm/2057</t>
         </is>
       </c>
-      <c r="H11" s="14" t="inlineStr"/>
-      <c r="I11" s="14" t="inlineStr"/>
-    </row>
-    <row r="12" ht="160" customHeight="1">
-      <c r="B12" s="12" t="inlineStr">
+      <c r="H11" s="12" t="inlineStr"/>
+      <c r="I11" s="12" t="inlineStr"/>
+    </row>
+    <row r="12" ht="254" customHeight="1">
+      <c r="B12" s="10" t="inlineStr">
         <is>
           <t>4a(ii)</t>
         </is>
       </c>
-      <c r="C12" s="14" t="inlineStr">
+      <c r="C12" s="12" t="inlineStr">
         <is>
           <t>Sustainability is integrated into curriculum to an extent that conscientiously extends, beyond a base threshold, each discipline’s (and associated professions/industries’) knowledge of the helpful and harmful impacts it has for the environmental and human systems we depend on</t>
         </is>
       </c>
-      <c r="D12" s="14" t="inlineStr">
+      <c r="D12" s="12" t="inlineStr">
         <is>
           <t>Please describe any efforts within your faculty to embed sustainability in the curriculum in line with this target.</t>
         </is>
       </c>
-      <c r="E12" s="14" t="inlineStr">
+      <c r="E12" s="12" t="inlineStr">
         <is>
           <t>Met or exceeded</t>
         </is>
       </c>
-      <c r="F12" s="14" t="inlineStr">
+      <c r="F12" s="12" t="inlineStr">
         <is>
           <t>Sustainability, conservation, biodiversity are elements of most courses and majors within the FoS. Several additional courses are being considered at PG level in 2026</t>
         </is>
       </c>
-      <c r="G12" s="14" t="inlineStr">
+      <c r="G12" s="12" t="inlineStr">
         <is>
           <t>The FoS education strategy https://staff.unimelb.edu.au/science/learning-and-teaching-support/education-strategy has been developed with the following targets related to sustainability:  
 Under Innovate: "Maintain a focus on embedding the principles of sustainability in our teaching and learning practices, including ‘green’ and sustainable laboratory initiatives"; Future ready graduates: "Our programs will embed the concepts of sustainability set out in the University’s Sustainability
@@ -1853,42 +1817,42 @@
 With the 12 month implementation plan noting that: "Understanding our students’ carbon footprint is the first step towards incorporating sustainability in teaching and learning."</t>
         </is>
       </c>
-      <c r="H12" s="14" t="inlineStr"/>
-      <c r="I12" s="14" t="inlineStr">
+      <c r="H12" s="12" t="inlineStr"/>
+      <c r="I12" s="12" t="inlineStr">
         <is>
           <t>EE1(a)</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="160" customHeight="1">
-      <c r="B13" s="12" t="inlineStr">
+    <row r="13" ht="369" customHeight="1">
+      <c r="B13" s="10" t="inlineStr">
         <is>
           <t>4b(i)</t>
         </is>
       </c>
-      <c r="C13" s="14" t="inlineStr">
+      <c r="C13" s="12" t="inlineStr">
         <is>
           <t>Graduates have increased capabilities to shape, lead 
 and succeed in the careers, communities and industries 
 of sustainable societies (year on year).</t>
         </is>
       </c>
-      <c r="D13" s="14" t="inlineStr">
+      <c r="D13" s="12" t="inlineStr">
         <is>
           <t>Is there any way to measure graduate outcomes related to sustainability in your faculty? If so, please describe.</t>
         </is>
       </c>
-      <c r="E13" s="14" t="inlineStr">
+      <c r="E13" s="12" t="inlineStr">
         <is>
           <t>Met or exceeded</t>
         </is>
       </c>
-      <c r="F13" s="14" t="inlineStr">
+      <c r="F13" s="12" t="inlineStr">
         <is>
           <t>As above. FoS is the custodial faculty for the Office of Environmental Programs</t>
         </is>
       </c>
-      <c r="G13" s="14" t="inlineStr">
+      <c r="G13" s="12" t="inlineStr">
         <is>
           <t>The BSc had 208 graduates across the following environmental/sustainability focussed majors:
 Zoology 40
@@ -1911,35 +1875,35 @@
 24 Master of Urban Horticulture</t>
         </is>
       </c>
-      <c r="H13" s="14" t="inlineStr"/>
-      <c r="I13" s="14" t="inlineStr">
+      <c r="H13" s="12" t="inlineStr"/>
+      <c r="I13" s="12" t="inlineStr">
         <is>
           <t>EE1(d)</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="160" customHeight="1">
-      <c r="B14" s="12" t="inlineStr">
+    <row r="14" ht="303" customHeight="1">
+      <c r="B14" s="10" t="inlineStr">
         <is>
           <t>5b(i)</t>
         </is>
       </c>
-      <c r="C14" s="14" t="inlineStr">
+      <c r="C14" s="12" t="inlineStr">
         <is>
           <t>The highest quality research is conducted that contributes to knowledge, action, and impact across the disciplinary and interdisciplinary dimensions of sustainability.</t>
         </is>
       </c>
-      <c r="D14" s="14" t="inlineStr">
+      <c r="D14" s="12" t="inlineStr">
         <is>
           <t>Please update data on sustainability-, climate- or environment-focused research institutes, and provide a case study of their key research impacts in 2025.</t>
         </is>
       </c>
-      <c r="E14" s="14" t="inlineStr">
+      <c r="E14" s="12" t="inlineStr">
         <is>
           <t>Met or exceeded</t>
         </is>
       </c>
-      <c r="F14" s="14" t="inlineStr">
+      <c r="F14" s="12" t="inlineStr">
         <is>
           <t>QS rankings, SDG research outputs all attest to our strength in environmental and sustainable research. 
 We have a research strategy which has clear deliverables for sustainability, including a focus on several "Big Research Challenges" which directly relate to Sustainability https://staff.unimelb.edu.au/science/research/research-governance/research-strategy-2023-2030/FOS-Research-strategy-_INTRANET-LINKS-FIXED.pdf
@@ -1949,36 +1913,36 @@
 https://science.unimelb.edu.au/about/news/australia-and-the-pacific-islands-solidarity-in-a-time-of-climate-crisis/_nocache</t>
         </is>
       </c>
-      <c r="G14" s="14" t="inlineStr"/>
-      <c r="H14" s="14" t="inlineStr"/>
-      <c r="I14" s="14" t="inlineStr">
+      <c r="G14" s="12" t="inlineStr"/>
+      <c r="H14" s="12" t="inlineStr"/>
+      <c r="I14" s="12" t="inlineStr">
         <is>
           <t>TR2(a), TR2(d)</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="160" customHeight="1">
-      <c r="B15" s="12" t="inlineStr">
+    <row r="15" ht="171" customHeight="1">
+      <c r="B15" s="10" t="inlineStr">
         <is>
           <t>5c(ii)</t>
         </is>
       </c>
-      <c r="C15" s="14" t="inlineStr">
+      <c r="C15" s="12" t="inlineStr">
         <is>
           <t>Researchers make considered decisions on the sustainability impact of their research practices and activities</t>
         </is>
       </c>
-      <c r="D15" s="14" t="inlineStr">
+      <c r="D15" s="12" t="inlineStr">
         <is>
           <t>Are there any efforts within the faculty to make research practices more sustainable? If so, please describe these activities</t>
         </is>
       </c>
-      <c r="E15" s="14" t="inlineStr">
+      <c r="E15" s="12" t="inlineStr">
         <is>
           <t>Partially met</t>
         </is>
       </c>
-      <c r="F15" s="14" t="inlineStr">
+      <c r="F15" s="12" t="inlineStr">
         <is>
           <t>We have a research strategy and implimentation plan which has clear deliverables for sustainability; 
 Link for Research strategy: https://staff.unimelb.edu.au/science/research/research-governance/research-strategy-2023-2030               
@@ -1986,36 +1950,36 @@
 which for example includes "Action 10. Improve sustainability of our core business practices"</t>
         </is>
       </c>
-      <c r="G15" s="14" t="inlineStr"/>
-      <c r="H15" s="14" t="inlineStr"/>
-      <c r="I15" s="14" t="inlineStr">
+      <c r="G15" s="12" t="inlineStr"/>
+      <c r="H15" s="12" t="inlineStr"/>
+      <c r="I15" s="12" t="inlineStr">
         <is>
           <t>TR3(a), TR3(b)</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="160" customHeight="1">
-      <c r="B16" s="12" t="inlineStr">
+    <row r="16" ht="270" customHeight="1">
+      <c r="B16" s="10" t="inlineStr">
         <is>
           <t>6a</t>
         </is>
       </c>
-      <c r="C16" s="14" t="inlineStr">
+      <c r="C16" s="12" t="inlineStr">
         <is>
           <t>The University has an increased understanding of sustainability from an Indigenous perspective through co-created or Indigenous-led reciprocal learning</t>
         </is>
       </c>
-      <c r="D16" s="14" t="inlineStr">
+      <c r="D16" s="12" t="inlineStr">
         <is>
           <t>Please provide a case study on activities in the faculty (related to education, research or partnerships) which operate at the nexus between Indigenous knowledges and the western concept of 'sustainability'.</t>
         </is>
       </c>
-      <c r="E16" s="14" t="inlineStr">
+      <c r="E16" s="12" t="inlineStr">
         <is>
           <t>Partially met</t>
         </is>
       </c>
-      <c r="F16" s="14" t="inlineStr">
+      <c r="F16" s="12" t="inlineStr">
         <is>
           <t>The Faculty of Science strategy has a specific goal of "Establish Indigenous lead caring for
 country course and resources " which sits under the theme of Living Sustaianbly. 
@@ -2023,9 +1987,9 @@
 Robyn Schofield working with Murujuga Rock Art Monitoring Program and being part of the Australian delegation that saw the inscription of Murujuga as a UN World Hertiage site in 2025 is one example.</t>
         </is>
       </c>
-      <c r="G16" s="14" t="inlineStr"/>
-      <c r="H16" s="14" t="inlineStr"/>
-      <c r="I16" s="14" t="inlineStr">
+      <c r="G16" s="12" t="inlineStr"/>
+      <c r="H16" s="12" t="inlineStr"/>
+      <c r="I16" s="12" t="inlineStr">
         <is>
           <t>EN1(a)</t>
         </is>
@@ -2048,10 +2012,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:E9"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+  </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="22" customHeight="1">
       <c r="B1" t="inlineStr">
         <is>
           <t>(not used – no target status rating in 2026)</t>
@@ -2073,7 +2044,7 @@
         </is>
       </c>
     </row>
-    <row r="2">
+    <row r="2" ht="22" customHeight="1">
       <c r="B2" t="inlineStr">
         <is>
           <t>Please select from dropdown</t>
@@ -2095,7 +2066,7 @@
         </is>
       </c>
     </row>
-    <row r="3">
+    <row r="3" ht="22" customHeight="1">
       <c r="C3" t="inlineStr">
         <is>
           <t>No</t>
@@ -2112,7 +2083,7 @@
         </is>
       </c>
     </row>
-    <row r="4">
+    <row r="4" ht="22" customHeight="1">
       <c r="C4" t="inlineStr">
         <is>
           <t>Partially – see comments</t>
@@ -2129,35 +2100,35 @@
         </is>
       </c>
     </row>
-    <row r="5">
+    <row r="5" ht="22" customHeight="1">
       <c r="D5" t="inlineStr">
         <is>
           <t>Received</t>
         </is>
       </c>
     </row>
-    <row r="6">
+    <row r="6" ht="22" customHeight="1">
       <c r="D6" t="inlineStr">
         <is>
           <t>First review</t>
         </is>
       </c>
     </row>
-    <row r="7">
+    <row r="7" ht="22" customHeight="1">
       <c r="D7" t="inlineStr">
         <is>
           <t>Follow-up</t>
         </is>
       </c>
     </row>
-    <row r="8">
+    <row r="8" ht="22" customHeight="1">
       <c r="D8" t="inlineStr">
         <is>
           <t>Complete</t>
         </is>
       </c>
     </row>
-    <row r="9">
+    <row r="9" ht="22" customHeight="1">
       <c r="D9" t="inlineStr">
         <is>
           <t>Not required</t>

--- a/output/faculty_requests/SCI - SR26 sustainability reporting request.xlsx
+++ b/output/faculty_requests/SCI - SR26 sustainability reporting request.xlsx
@@ -633,7 +633,7 @@
 • Where a related end-2025 target existed, click the ref in Column H to see your full SR25 response (Tab 3)
 • Use Tab 2 of this spreadsheet to highlight key sustainability stories (optional)
 • 2026 is a transition year: Sustainability 2030 launched ~20 October 2026, so report on activity across all of 2026 and any early actions since launch. No target status rating is requested this year.
-• Due: Tuesday 15 December 2026. Questions: CDSS – questions and clarifications are recorded centrally (contact email TBC); optional 1:1 meetings available on request</t>
+• Due: Tuesday 15 December 2026. Questions: Sustainability Strategy team (SST) – questions and clarifications are recorded centrally (contact email TBC); optional 1:1 meetings available on request</t>
         </is>
       </c>
     </row>

--- a/output/faculty_requests/SCI - SR26 sustainability reporting request.xlsx
+++ b/output/faculty_requests/SCI - SR26 sustainability reporting request.xlsx
@@ -31,7 +31,7 @@
     <font>
       <name val="Aptos"/>
       <b val="1"/>
-      <color rgb="00002060"/>
+      <color rgb="00FFFFFF"/>
       <sz val="22"/>
     </font>
     <font>
@@ -110,7 +110,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -135,6 +135,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFC000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00000F46"/>
       </patternFill>
     </fill>
   </fills>
@@ -170,9 +175,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="4"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -297,6 +305,96 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>57150</colOff>
+      <row>1</row>
+      <rowOff>57150</rowOff>
+    </from>
+    <ext cx="609600" cy="609600"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>57150</colOff>
+      <row>1</row>
+      <rowOff>57150</rowOff>
+    </from>
+    <ext cx="609600" cy="609600"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>57150</colOff>
+      <row>1</row>
+      <rowOff>57150</rowOff>
+    </from>
+    <ext cx="609600" cy="609600"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -588,7 +686,7 @@
     <outlinePr summaryBelow="1" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q25"/>
+  <dimension ref="A1:R25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -608,24 +706,61 @@
     <col width="30" customWidth="1" min="15" max="15"/>
     <col width="20" customWidth="1" min="16" max="16"/>
     <col width="24" customWidth="1" min="17" max="17"/>
+    <col width="13" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
-    <row r="1"/>
-    <row r="2" ht="39" customHeight="1">
-      <c r="B2" s="1" t="inlineStr">
+    <row r="1" ht="8" customHeight="1">
+      <c r="A1" s="1" t="n"/>
+      <c r="B1" s="1" t="n"/>
+      <c r="C1" s="1" t="n"/>
+      <c r="D1" s="1" t="n"/>
+      <c r="E1" s="1" t="n"/>
+      <c r="F1" s="1" t="n"/>
+      <c r="G1" s="1" t="n"/>
+      <c r="H1" s="1" t="n"/>
+      <c r="I1" s="1" t="n"/>
+      <c r="J1" s="1" t="n"/>
+      <c r="K1" s="1" t="n"/>
+      <c r="L1" s="1" t="n"/>
+      <c r="M1" s="1" t="n"/>
+      <c r="N1" s="1" t="n"/>
+      <c r="O1" s="1" t="n"/>
+      <c r="P1" s="1" t="n"/>
+      <c r="Q1" s="1" t="n"/>
+      <c r="R1" s="1" t="n"/>
+    </row>
+    <row r="2" ht="58" customHeight="1">
+      <c r="A2" s="1" t="n"/>
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>SR26 sustainability reporting request</t>
         </is>
       </c>
+      <c r="C2" s="1" t="n"/>
+      <c r="D2" s="1" t="n"/>
+      <c r="E2" s="1" t="n"/>
+      <c r="F2" s="1" t="n"/>
+      <c r="G2" s="1" t="n"/>
+      <c r="H2" s="1" t="n"/>
+      <c r="I2" s="1" t="n"/>
+      <c r="J2" s="1" t="n"/>
+      <c r="K2" s="1" t="n"/>
+      <c r="L2" s="1" t="n"/>
+      <c r="M2" s="1" t="n"/>
+      <c r="N2" s="1" t="n"/>
+      <c r="O2" s="1" t="n"/>
+      <c r="P2" s="1" t="n"/>
+      <c r="Q2" s="1" t="n"/>
+      <c r="R2" s="1" t="n"/>
     </row>
     <row r="3"/>
     <row r="4">
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>How to use this spreadsheet:</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D4" s="4" t="inlineStr">
         <is>
           <t>• For each row below, describe progress towards the target (Column L) and/or respond to the 2026 reporting request (Column M)
 • Provide supporting information if required (Column N), including links to documents or images
@@ -633,7 +768,7 @@
 • Where a related end-2025 target existed, click the ref in Column H to see your full SR25 response (Tab 3)
 • Use Tab 2 of this spreadsheet to highlight key sustainability stories (optional)
 • 2026 is a transition year: Sustainability 2030 launched ~20 October 2026, so report on activity across all of 2026 and any early actions since launch. No target status rating is requested this year.
-• Due: Tuesday 15 December 2026. Questions: Sustainability Strategy team (SST) – questions and clarifications are recorded centrally (contact email TBC); optional 1:1 meetings available on request</t>
+• Due: Thursday 24 December 2026 (Christmas shutdown). Questions: Sustainability Strategy team (SST) – questions and clarifications are recorded centrally (contact email TBC); optional 1:1 meetings available on request</t>
         </is>
       </c>
     </row>
@@ -644,7 +779,7 @@
     <row r="9"/>
     <row r="10"/>
     <row r="11" ht="39" customHeight="1">
-      <c r="B11" s="4" t="inlineStr">
+      <c r="B11" s="5" t="inlineStr">
         <is>
           <t>SCI – Faculty of Science</t>
         </is>
@@ -652,191 +787,191 @@
     </row>
     <row r="12"/>
     <row r="13" ht="27" customHeight="1">
-      <c r="C13" s="5" t="inlineStr">
+      <c r="C13" s="6" t="inlineStr">
         <is>
           <t>Sustainability 2030 target and indicator</t>
         </is>
       </c>
-      <c r="H13" s="5" t="inlineStr">
+      <c r="H13" s="6" t="inlineStr">
         <is>
           <t>SR25 response</t>
         </is>
       </c>
-      <c r="L13" s="6" t="inlineStr">
+      <c r="L13" s="7" t="inlineStr">
         <is>
           <t>End-2026 reporting (PLEASE COMPLETE THIS SECTION)</t>
         </is>
       </c>
     </row>
     <row r="14" ht="60" customHeight="1">
-      <c r="B14" s="7" t="inlineStr">
+      <c r="B14" s="8" t="inlineStr">
         <is>
           <t>Ref</t>
         </is>
       </c>
-      <c r="C14" s="7" t="inlineStr">
+      <c r="C14" s="8" t="inlineStr">
         <is>
           <t>Priority area</t>
         </is>
       </c>
-      <c r="D14" s="7" t="inlineStr">
+      <c r="D14" s="8" t="inlineStr">
         <is>
           <t>Sustainability 2030 target</t>
         </is>
       </c>
-      <c r="E14" s="7" t="inlineStr">
+      <c r="E14" s="8" t="inlineStr">
         <is>
           <t>Indicator</t>
         </is>
       </c>
-      <c r="F14" s="7" t="inlineStr">
+      <c r="F14" s="8" t="inlineStr">
         <is>
           <t>2026 Reporting request</t>
         </is>
       </c>
-      <c r="G14" s="7" t="inlineStr">
+      <c r="G14" s="8" t="inlineStr">
         <is>
           <t>How SST will use this data</t>
         </is>
       </c>
-      <c r="H14" s="7" t="inlineStr">
+      <c r="H14" s="8" t="inlineStr">
         <is>
           <t>Related SR25 ref</t>
         </is>
       </c>
-      <c r="I14" s="7" t="inlineStr">
+      <c r="I14" s="8" t="inlineStr">
         <is>
           <t>End-2025 confirmed status</t>
         </is>
       </c>
-      <c r="J14" s="7" t="inlineStr">
+      <c r="J14" s="8" t="inlineStr">
         <is>
           <t>End-2025 reporting response</t>
         </is>
       </c>
-      <c r="K14" s="7" t="inlineStr">
+      <c r="K14" s="8" t="inlineStr">
         <is>
           <t>Links and supporting information</t>
         </is>
       </c>
-      <c r="L14" s="8" t="inlineStr">
+      <c r="L14" s="9" t="inlineStr">
         <is>
           <t>OPTION 1:  Target-level reporting (Column D)</t>
         </is>
       </c>
-      <c r="M14" s="8" t="inlineStr">
+      <c r="M14" s="9" t="inlineStr">
         <is>
           <t>OPTION 2:  Indicator level reporting (Column E/F)</t>
         </is>
       </c>
-      <c r="N14" s="8" t="inlineStr">
+      <c r="N14" s="9" t="inlineStr">
         <is>
           <t>Supporting information/comments</t>
         </is>
       </c>
-      <c r="O14" s="8" t="inlineStr">
+      <c r="O14" s="9" t="inlineStr">
         <is>
           <t>Data source and limitations</t>
         </is>
       </c>
-      <c r="P14" s="8" t="inlineStr">
+      <c r="P14" s="9" t="inlineStr">
         <is>
           <t>Data owner confirms information is accurate</t>
         </is>
       </c>
-      <c r="Q14" s="8" t="inlineStr">
+      <c r="Q14" s="9" t="inlineStr">
         <is>
           <t>Confirmed by (name, role, date)</t>
         </is>
       </c>
     </row>
     <row r="15" ht="81" customHeight="1">
-      <c r="B15" s="9" t="inlineStr"/>
-      <c r="C15" s="9" t="inlineStr"/>
-      <c r="D15" s="9" t="inlineStr"/>
-      <c r="E15" s="9" t="inlineStr"/>
-      <c r="F15" s="9" t="inlineStr"/>
-      <c r="G15" s="9" t="inlineStr"/>
-      <c r="H15" s="9" t="inlineStr"/>
-      <c r="I15" s="9" t="inlineStr"/>
-      <c r="J15" s="9" t="inlineStr"/>
-      <c r="K15" s="9" t="inlineStr"/>
-      <c r="L15" s="9" t="inlineStr">
+      <c r="B15" s="10" t="inlineStr"/>
+      <c r="C15" s="10" t="inlineStr"/>
+      <c r="D15" s="10" t="inlineStr"/>
+      <c r="E15" s="10" t="inlineStr"/>
+      <c r="F15" s="10" t="inlineStr"/>
+      <c r="G15" s="10" t="inlineStr"/>
+      <c r="H15" s="10" t="inlineStr"/>
+      <c r="I15" s="10" t="inlineStr"/>
+      <c r="J15" s="10" t="inlineStr"/>
+      <c r="K15" s="10" t="inlineStr"/>
+      <c r="L15" s="10" t="inlineStr">
         <is>
           <t>A general update on activities in relation to the overarching target (Column D)</t>
         </is>
       </c>
-      <c r="M15" s="9" t="inlineStr">
+      <c r="M15" s="10" t="inlineStr">
         <is>
           <t>Data and commentary in direct response to the reporting request (Column F)</t>
         </is>
       </c>
-      <c r="N15" s="9" t="inlineStr">
+      <c r="N15" s="10" t="inlineStr">
         <is>
           <t>Any additional information (e.g. links, images, documents)</t>
         </is>
       </c>
-      <c r="O15" s="9" t="inlineStr">
+      <c r="O15" s="10" t="inlineStr">
         <is>
           <t>Where did this information come from (system, report, survey, person)? Note any gaps or limitations.</t>
         </is>
       </c>
-      <c r="P15" s="9" t="inlineStr">
+      <c r="P15" s="10" t="inlineStr">
         <is>
           <t>Select 'Yes' to confirm the information provided is accurate and can be used for reporting</t>
         </is>
       </c>
-      <c r="Q15" s="9" t="inlineStr">
+      <c r="Q15" s="10" t="inlineStr">
         <is>
           <t>Name, role and date of the person confirming</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="320" customHeight="1">
-      <c r="B16" s="10" t="inlineStr">
+    <row r="16" ht="352" customHeight="1">
+      <c r="B16" s="11" t="inlineStr">
         <is>
           <t>EE1(a)</t>
         </is>
       </c>
-      <c r="C16" s="11" t="inlineStr">
+      <c r="C16" s="12" t="inlineStr">
         <is>
           <t>Exceptional education</t>
         </is>
       </c>
-      <c r="D16" s="11" t="inlineStr">
+      <c r="D16" s="12" t="inlineStr">
         <is>
           <t>Provide our students with learning experiences that help them build the knowledge, skills and relationships to lead change for sustainable societies.</t>
         </is>
       </c>
-      <c r="E16" s="11" t="inlineStr">
+      <c r="E16" s="12" t="inlineStr">
         <is>
           <t>Evidence of innovative approaches to sustainability teaching and learning</t>
         </is>
       </c>
-      <c r="F16" s="12" t="inlineStr">
-        <is>
-          <t>In end-2025 reporting your faculty reported on the related SP2030 target 4a(ii) (click the ref in Column H to see it in full in Tab 3). Please build on this rather than repeating it, focusing on what is new in 2026.
-Please give any examples from 2026 of how your faculty has embedded sustainability in teaching and learning. This could include innovative approaches (e.g. new or redesigned subjects, curriculum design, pedagogies, assessment or learning resources) and sustainability-focused experiential or co-curricular learning (e.g. industry or community projects, fieldwork, internships, student challenges). Include links and approximate student participation where known.
-This question also covers indicator EE1(c). Melbourne Plus and the Wattle Fellowship will be collected separately – no need to report these.</t>
-        </is>
-      </c>
-      <c r="G16" s="12" t="inlineStr">
+      <c r="F16" s="13" t="inlineStr">
+        <is>
+          <t>Please give any examples from 2026 of how your faculty has embedded sustainability in teaching and learning. This could include innovative approaches (e.g. new or redesigned subjects, curriculum design, pedagogies, assessment or learning resources) and sustainability-focused experiential or co-curricular learning (e.g. industry or community projects, fieldwork, internships, student challenges). Include links and approximate student participation where known.
+This question also covers indicator EE1(c). Please note that this indicator will be addressed at the joint Associate Deans Sustainability and Associate Deans Teaching and Learning session on 23 November 2026. Please feel free to summarise what your faculty presented at this session - further information is welcome but not required.
+In end-2025 reporting your faculty reported on the related SP2030 target 4a(ii) (click the ref in Column H to see it in full in Tab 3).</t>
+        </is>
+      </c>
+      <c r="G16" s="13" t="inlineStr">
         <is>
           <t>We will collate examples of sustainability teaching and learning, including experiential and co-curricular learning, across faculties to inform the Exceptional education section of the 2026 Sustainability Report. Strong examples may be followed up for the report.</t>
         </is>
       </c>
-      <c r="H16" s="13" t="inlineStr">
+      <c r="H16" s="14" t="inlineStr">
         <is>
           <t>4a(ii)
 → view SR25 response</t>
         </is>
       </c>
-      <c r="I16" s="12" t="inlineStr">
+      <c r="I16" s="13" t="inlineStr">
         <is>
           <t>Met or exceeded</t>
         </is>
       </c>
-      <c r="J16" s="12" t="inlineStr">
+      <c r="J16" s="13" t="inlineStr">
         <is>
           <t>Sustainability, conservation, biodiversity are elements of most courses and majors within the FoS. Several additional courses are being considered at PG level in 2026
 The FoS education strategy https://staff.unimelb.edu.au/science/learning-and-teaching-support/education-strategy has been developed with the following targets related to sustainability:  
@@ -846,106 +981,106 @@
 With the 12 month implementation plan noting that: "Understanding our students’ carbon footprint is the first step towards incorporating sustainability in teaching and learning."</t>
         </is>
       </c>
-      <c r="K16" s="12" t="inlineStr"/>
-      <c r="L16" s="14" t="n"/>
-      <c r="M16" s="14" t="n"/>
-      <c r="N16" s="14" t="n"/>
-      <c r="O16" s="14" t="n"/>
-      <c r="P16" s="14" t="n"/>
-      <c r="Q16" s="14" t="n"/>
+      <c r="K16" s="13" t="inlineStr"/>
+      <c r="L16" s="15" t="n"/>
+      <c r="M16" s="15" t="n"/>
+      <c r="N16" s="15" t="n"/>
+      <c r="O16" s="15" t="n"/>
+      <c r="P16" s="15" t="n"/>
+      <c r="Q16" s="15" t="n"/>
     </row>
     <row r="17" ht="188" customHeight="1">
-      <c r="B17" s="10" t="inlineStr">
+      <c r="B17" s="11" t="inlineStr">
         <is>
           <t>EE1(b)</t>
         </is>
       </c>
-      <c r="C17" s="11" t="inlineStr">
+      <c r="C17" s="12" t="inlineStr">
         <is>
           <t>Exceptional education</t>
         </is>
       </c>
-      <c r="D17" s="11" t="inlineStr">
+      <c r="D17" s="12" t="inlineStr">
         <is>
           <t>Provide our students with learning experiences that help them build the knowledge, skills and relationships to lead change for sustainable societies.</t>
         </is>
       </c>
-      <c r="E17" s="11" t="inlineStr">
+      <c r="E17" s="12" t="inlineStr">
         <is>
           <t>Pilots of possible approaches for understanding and developing students’ sustainability self-efficacy</t>
         </is>
       </c>
-      <c r="F17" s="12" t="inlineStr">
+      <c r="F17" s="13" t="inlineStr">
         <is>
           <t>Has your faculty piloted or trialled any approach in 2026 to understand or build students' confidence and capability to act on sustainability (sustainability self-efficacy)? If yes, briefly describe the approach, participating cohort, what was learned and next steps. If not, please respond 'none in 2026' – this is a new indicator and a nil response is useful.
 We are aware of the Sustainability Strengths Compass Living Lab project (CLLAP) and will collect it separately.</t>
         </is>
       </c>
-      <c r="G17" s="12" t="inlineStr">
+      <c r="G17" s="13" t="inlineStr">
         <is>
           <t>This is a new indicator. We will use responses to establish a baseline of how (and whether) faculties are understanding student sustainability self-efficacy, and report on early pilots in the 2026 Sustainability Report. A nil response is useful to us.</t>
         </is>
       </c>
-      <c r="H17" s="12" t="inlineStr">
+      <c r="H17" s="13" t="inlineStr">
         <is>
           <t>N/A – new indicator</t>
         </is>
       </c>
-      <c r="I17" s="12" t="inlineStr"/>
-      <c r="J17" s="12" t="inlineStr"/>
-      <c r="K17" s="12" t="inlineStr"/>
-      <c r="L17" s="14" t="n"/>
-      <c r="M17" s="14" t="n"/>
-      <c r="N17" s="14" t="n"/>
-      <c r="O17" s="14" t="n"/>
-      <c r="P17" s="14" t="n"/>
-      <c r="Q17" s="14" t="n"/>
-    </row>
-    <row r="18" ht="303" customHeight="1">
-      <c r="B18" s="10" t="inlineStr">
+      <c r="I17" s="13" t="inlineStr"/>
+      <c r="J17" s="13" t="inlineStr"/>
+      <c r="K17" s="13" t="inlineStr"/>
+      <c r="L17" s="15" t="n"/>
+      <c r="M17" s="15" t="n"/>
+      <c r="N17" s="15" t="n"/>
+      <c r="O17" s="15" t="n"/>
+      <c r="P17" s="15" t="n"/>
+      <c r="Q17" s="15" t="n"/>
+    </row>
+    <row r="18" ht="270" customHeight="1">
+      <c r="B18" s="11" t="inlineStr">
         <is>
           <t>TR1(a)</t>
         </is>
       </c>
-      <c r="C18" s="11" t="inlineStr">
+      <c r="C18" s="12" t="inlineStr">
         <is>
           <t>Transformational research</t>
         </is>
       </c>
-      <c r="D18" s="11" t="inlineStr">
+      <c r="D18" s="12" t="inlineStr">
         <is>
           <t>Utilise the expertise of the University’s researchers through mutually beneficial partnerships to help address the University’s operational sustainability challenges.</t>
         </is>
       </c>
-      <c r="E18" s="11" t="inlineStr">
+      <c r="E18" s="12" t="inlineStr">
         <is>
           <t>Expert-reviewed evidence of researchers contributing to operational sustainability priorities through partnerships, advisory input, living labs, applied projects or decision-support</t>
         </is>
       </c>
-      <c r="F18" s="12" t="inlineStr">
-        <is>
-          <t>In end-2025 reporting your faculty reported on the related SP2030 target 2a (click the ref in Column H to see it in full in Tab 3). Please build on this rather than repeating it, focusing on what is new in 2026.
-Please give any examples from 2026 of researchers in your faculty contributing to the University's own operational sustainability challenges (e.g. advising on campus energy, biodiversity, waste or buildings; applied projects; decision-support tools). Briefly describe the operational challenge, the researchers' contribution, the University team involved and the result.
-We will collect Campus Living Lab Accelerator Program (CLLAP) projects separately from CI&amp;S – please include other examples only.</t>
-        </is>
-      </c>
-      <c r="G18" s="12" t="inlineStr">
-        <is>
-          <t>We will report on examples of researchers helping solve the University's own operational sustainability challenges, alongside CLLAP projects reported by CI&amp;S, and share them with operational teams to identify further collaboration.</t>
-        </is>
-      </c>
-      <c r="H18" s="13" t="inlineStr">
+      <c r="F18" s="13" t="inlineStr">
+        <is>
+          <t>Please give any examples from 2026 of researchers in your faculty contributing to the University's own operational sustainability challenges (e.g. advising on campus energy, biodiversity, waste or buildings; applied projects; decision-support tools). Briefly describe the operational challenge, the researchers' contribution, the University team involved and the result.
+Please note, we will collect case studies on Campus Living Lab Accelerator Program projects directly from project owners - no need to include these.
+In end-2025 reporting your faculty reported on the related SP2030 target 2a (click the ref in Column H to see it in full in Tab 3).</t>
+        </is>
+      </c>
+      <c r="G18" s="13" t="inlineStr">
+        <is>
+          <t>We will report on examples of researchers helping solve the University's own operational sustainability challenges, alongside Campus Living Lab Accelerator Program case studies collected directly from project owners, and share them with operational teams to identify further collaboration.</t>
+        </is>
+      </c>
+      <c r="H18" s="14" t="inlineStr">
         <is>
           <t>2a
 → view SR25 response</t>
         </is>
       </c>
-      <c r="I18" s="12" t="inlineStr">
+      <c r="I18" s="13" t="inlineStr">
         <is>
           <t>Partially met</t>
         </is>
       </c>
-      <c r="J18" s="12" t="inlineStr">
+      <c r="J18" s="13" t="inlineStr">
         <is>
           <t>The faculty has many projects that can be considered living labs. A centralised approach is required to document them.
 2025 examples include how the undergraduate chemistry teaching laboratories redesigned their practicals to use less reagents and safer chemicals to achieve the same learning outcomes.
@@ -953,64 +1088,64 @@
 SAFES have worked on Indigenous food gardens and have an Indigenous food guide and there are examples of urban and woodland greening that serve as best practice examples across Australia</t>
         </is>
       </c>
-      <c r="K18" s="12" t="inlineStr">
+      <c r="K18" s="13" t="inlineStr">
         <is>
           <t>https://www.unimelb.edu.au/newsroom/news/2024/october/native-harvest-cookbook-aims-to-put-indigenous-food-in-every-aussie-kitchen
 https://theconversation.com/we-planted-two-woody-meadows-a-decade-ago-to-see-what-would-thrive-now-the-concept-is-popular-across-australia-269611</t>
         </is>
       </c>
-      <c r="L18" s="14" t="n"/>
-      <c r="M18" s="14" t="n"/>
-      <c r="N18" s="14" t="n"/>
-      <c r="O18" s="14" t="n"/>
-      <c r="P18" s="14" t="n"/>
-      <c r="Q18" s="14" t="n"/>
-    </row>
-    <row r="19" ht="286" customHeight="1">
-      <c r="B19" s="10" t="inlineStr">
+      <c r="L18" s="15" t="n"/>
+      <c r="M18" s="15" t="n"/>
+      <c r="N18" s="15" t="n"/>
+      <c r="O18" s="15" t="n"/>
+      <c r="P18" s="15" t="n"/>
+      <c r="Q18" s="15" t="n"/>
+    </row>
+    <row r="19" ht="270" customHeight="1">
+      <c r="B19" s="11" t="inlineStr">
         <is>
           <t>TR2(a)</t>
         </is>
       </c>
-      <c r="C19" s="11" t="inlineStr">
+      <c r="C19" s="12" t="inlineStr">
         <is>
           <t>Transformational research</t>
         </is>
       </c>
-      <c r="D19" s="11" t="inlineStr">
+      <c r="D19" s="12" t="inlineStr">
         <is>
           <t>Deliver high-quality research and partnerships that contribute to sustainability outcomes and demonstrable societal benefit.</t>
         </is>
       </c>
-      <c r="E19" s="11" t="inlineStr">
+      <c r="E19" s="12" t="inlineStr">
         <is>
           <t>Evidence of sustainability-related research impact across diverse pathways, could include policy, industry, community, practice, cultural and institutional outcomes</t>
         </is>
       </c>
-      <c r="F19" s="12" t="inlineStr">
-        <is>
-          <t>In end-2025 reporting your faculty reported on the related SP2030 target 5b(i) (click the ref in Column H to see it in full in Tab 3). Please build on this rather than repeating it, focusing on what is new in 2026.
-Please give any examples from 2026 of sustainability-related research from your faculty that has had impact beyond academia – on policy, industry, community, practice, cultural or institutional outcomes. Briefly describe the research, the partner or user, and the resulting change or influence, with links (e.g. Pursuit articles, policy submissions, reports).
-We will source University-wide research metrics (e.g. SDG-mapped publications via SciVal) from MRE – publication counts are not required.</t>
-        </is>
-      </c>
-      <c r="G19" s="12" t="inlineStr">
-        <is>
-          <t>We will collate research impact examples across faculties to show the breadth of sustainability-related research impact in the Transformational research section of the 2026 Sustainability Report, complementing University-wide metrics from MRE.</t>
-        </is>
-      </c>
-      <c r="H19" s="13" t="inlineStr">
+      <c r="F19" s="13" t="inlineStr">
+        <is>
+          <t>Please give any examples from 2026 of sustainability-related research from your faculty that has had impact beyond academia – on policy, industry, community, practice, cultural or institutional outcomes. Briefly describe the research, the partner or user, and the resulting change or influence, with links (e.g. Pursuit articles, policy submissions, reports).
+We will source University-wide research metrics (e.g. SDG-mapped publications via SciVal) from Melbourne Research and Enterprise (MRE) – publication counts are not required.
+In end-2025 reporting your faculty reported on the related SP2030 target 5b(i) (click the ref in Column H to see it in full in Tab 3).</t>
+        </is>
+      </c>
+      <c r="G19" s="13" t="inlineStr">
+        <is>
+          <t>We will collate research impact examples across faculties to show the breadth of sustainability-related research impact in the Transformational research section of the 2026 Sustainability Report, complementing University-wide metrics from Melbourne Research and Enterprise (MRE).</t>
+        </is>
+      </c>
+      <c r="H19" s="14" t="inlineStr">
         <is>
           <t>5b(i)
 → view SR25 response</t>
         </is>
       </c>
-      <c r="I19" s="12" t="inlineStr">
+      <c r="I19" s="13" t="inlineStr">
         <is>
           <t>Met or exceeded</t>
         </is>
       </c>
-      <c r="J19" s="12" t="inlineStr">
+      <c r="J19" s="13" t="inlineStr">
         <is>
           <t>QS rankings, SDG research outputs all attest to our strength in environmental and sustainable research. 
 We have a research strategy which has clear deliverables for sustainability, including a focus on several "Big Research Challenges" which directly relate to Sustainability https://staff.unimelb.edu.au/science/research/research-governance/research-strategy-2023-2030/FOS-Research-strategy-_INTRANET-LINKS-FIXED.pdf
@@ -1020,59 +1155,59 @@
 https://science.unimelb.edu.au/about/news/australia-and-the-pacific-islands-solidarity-in-a-time-of-climate-crisis/_nocache</t>
         </is>
       </c>
-      <c r="K19" s="12" t="inlineStr"/>
-      <c r="L19" s="14" t="n"/>
-      <c r="M19" s="14" t="n"/>
-      <c r="N19" s="14" t="n"/>
-      <c r="O19" s="14" t="n"/>
-      <c r="P19" s="14" t="n"/>
-      <c r="Q19" s="14" t="n"/>
-    </row>
-    <row r="20" ht="270" customHeight="1">
-      <c r="B20" s="10" t="inlineStr">
+      <c r="K19" s="13" t="inlineStr"/>
+      <c r="L19" s="15" t="n"/>
+      <c r="M19" s="15" t="n"/>
+      <c r="N19" s="15" t="n"/>
+      <c r="O19" s="15" t="n"/>
+      <c r="P19" s="15" t="n"/>
+      <c r="Q19" s="15" t="n"/>
+    </row>
+    <row r="20" ht="237" customHeight="1">
+      <c r="B20" s="11" t="inlineStr">
         <is>
           <t>TR2(d)</t>
         </is>
       </c>
-      <c r="C20" s="11" t="inlineStr">
+      <c r="C20" s="12" t="inlineStr">
         <is>
           <t>Transformational research</t>
         </is>
       </c>
-      <c r="D20" s="11" t="inlineStr">
+      <c r="D20" s="12" t="inlineStr">
         <is>
           <t>Deliver high-quality research and partnerships that contribute to sustainability outcomes and demonstrable societal benefit.</t>
         </is>
       </c>
-      <c r="E20" s="11" t="inlineStr">
+      <c r="E20" s="12" t="inlineStr">
         <is>
           <t>Case-based evidence demonstrating how research has contributed to meaningful sustainability outcomes.</t>
         </is>
       </c>
-      <c r="F20" s="12" t="inlineStr">
-        <is>
-          <t>In end-2025 reporting your faculty reported on the related SP2030 target 5b(i) (click the ref in Column H to see it in full in Tab 3). Please build on this rather than repeating it, focusing on what is new in 2026.
-Please give any examples of research activity from your faculty that has contributed to a meaningful sustainability outcome: the research, stakeholders involved, pathway to impact and evidence of the outcome. These can be the examples from TR2(a) described in more detail.
-We are also seeking examples from Melbourne Climate Futures, the Melbourne Biodiversity Institute and Strategic Communications.</t>
-        </is>
-      </c>
-      <c r="G20" s="12" t="inlineStr">
+      <c r="F20" s="13" t="inlineStr">
+        <is>
+          <t>Please give any examples of research activity from your faculty that has contributed to a meaningful sustainability outcome: the research, stakeholders involved, pathway to impact and evidence of the outcome. These can be the examples from TR2(a) described in more detail.
+We are also seeking examples from Melbourne Climate Futures, the Melbourne Biodiversity Institute and Strategic Communications.
+In end-2025 reporting your faculty reported on the related SP2030 target 5b(i) (click the ref in Column H to see it in full in Tab 3).</t>
+        </is>
+      </c>
+      <c r="G20" s="13" t="inlineStr">
         <is>
           <t>We will select the strongest examples to develop as full research case studies for the 2026 Sustainability Report (we may contact you for more detail and images).</t>
         </is>
       </c>
-      <c r="H20" s="13" t="inlineStr">
+      <c r="H20" s="14" t="inlineStr">
         <is>
           <t>5b(i)
 → view SR25 response</t>
         </is>
       </c>
-      <c r="I20" s="12" t="inlineStr">
+      <c r="I20" s="13" t="inlineStr">
         <is>
           <t>Met or exceeded</t>
         </is>
       </c>
-      <c r="J20" s="12" t="inlineStr">
+      <c r="J20" s="13" t="inlineStr">
         <is>
           <t>QS rankings, SDG research outputs all attest to our strength in environmental and sustainable research. 
 We have a research strategy which has clear deliverables for sustainability, including a focus on several "Big Research Challenges" which directly relate to Sustainability https://staff.unimelb.edu.au/science/research/research-governance/research-strategy-2023-2030/FOS-Research-strategy-_INTRANET-LINKS-FIXED.pdf
@@ -1082,58 +1217,58 @@
 https://science.unimelb.edu.au/about/news/australia-and-the-pacific-islands-solidarity-in-a-time-of-climate-crisis/_nocache</t>
         </is>
       </c>
-      <c r="K20" s="12" t="inlineStr"/>
-      <c r="L20" s="14" t="n"/>
-      <c r="M20" s="14" t="n"/>
-      <c r="N20" s="14" t="n"/>
-      <c r="O20" s="14" t="n"/>
-      <c r="P20" s="14" t="n"/>
-      <c r="Q20" s="14" t="n"/>
-    </row>
-    <row r="21" ht="220" customHeight="1">
-      <c r="B21" s="10" t="inlineStr">
+      <c r="K20" s="13" t="inlineStr"/>
+      <c r="L20" s="15" t="n"/>
+      <c r="M20" s="15" t="n"/>
+      <c r="N20" s="15" t="n"/>
+      <c r="O20" s="15" t="n"/>
+      <c r="P20" s="15" t="n"/>
+      <c r="Q20" s="15" t="n"/>
+    </row>
+    <row r="21" ht="188" customHeight="1">
+      <c r="B21" s="11" t="inlineStr">
         <is>
           <t>TR3(b)</t>
         </is>
       </c>
-      <c r="C21" s="11" t="inlineStr">
+      <c r="C21" s="12" t="inlineStr">
         <is>
           <t>Transformational research</t>
         </is>
       </c>
-      <c r="D21" s="11" t="inlineStr">
+      <c r="D21" s="12" t="inlineStr">
         <is>
           <t>Embed sustainability within research systems, processes, capability and culture, so research is conducted responsibly, efficiently and with reduced environmental impact.</t>
         </is>
       </c>
-      <c r="E21" s="11" t="inlineStr">
+      <c r="E21" s="12" t="inlineStr">
         <is>
           <t>Demonstrated examples of more sustainable research practices in laboratories, fieldwork, procurement, travel or infrastructure use</t>
         </is>
       </c>
-      <c r="F21" s="12" t="inlineStr">
-        <is>
-          <t>In end-2025 reporting your faculty reported on the related SP2030 target 5c(ii) (click the ref in Column H to see it in full in Tab 3). Please build on this rather than repeating it, focusing on what is new in 2026.
-Are there any efforts within the faculty to make research practices more sustainable (e.g. green lab certification, equipment sharing, reduced research travel, sustainable fieldwork, sustainable procurement of research consumables)? If so, please give any examples and any evidence of uptake, resource savings or emissions reductions.</t>
-        </is>
-      </c>
-      <c r="G21" s="12" t="inlineStr">
+      <c r="F21" s="13" t="inlineStr">
+        <is>
+          <t>Are there any efforts within the faculty to make research practices more sustainable (e.g. green lab certification, equipment sharing, reduced research travel, sustainable fieldwork, sustainable procurement of research consumables)? If so, please give any examples and any evidence of uptake, resource savings or emissions reductions.
+In end-2025 reporting your faculty reported on the related SP2030 target 5c(ii) (click the ref in Column H to see it in full in Tab 3).</t>
+        </is>
+      </c>
+      <c r="G21" s="13" t="inlineStr">
         <is>
           <t>We will report on ways the University is making research practices more sustainable in the 2026 Sustainability Report, and share practical examples (e.g. green labs) across faculties.</t>
         </is>
       </c>
-      <c r="H21" s="13" t="inlineStr">
+      <c r="H21" s="14" t="inlineStr">
         <is>
           <t>5c(ii)
 → view SR25 response</t>
         </is>
       </c>
-      <c r="I21" s="12" t="inlineStr">
+      <c r="I21" s="13" t="inlineStr">
         <is>
           <t>Partially met</t>
         </is>
       </c>
-      <c r="J21" s="12" t="inlineStr">
+      <c r="J21" s="13" t="inlineStr">
         <is>
           <t>We have a research strategy and implimentation plan which has clear deliverables for sustainability; 
 Link for Research strategy: https://staff.unimelb.edu.au/science/research/research-governance/research-strategy-2023-2030               
@@ -1141,58 +1276,58 @@
 which for example includes "Action 10. Improve sustainability of our core business practices"</t>
         </is>
       </c>
-      <c r="K21" s="12" t="inlineStr"/>
-      <c r="L21" s="14" t="n"/>
-      <c r="M21" s="14" t="n"/>
-      <c r="N21" s="14" t="n"/>
-      <c r="O21" s="14" t="n"/>
-      <c r="P21" s="14" t="n"/>
-      <c r="Q21" s="14" t="n"/>
-    </row>
-    <row r="22" ht="220" customHeight="1">
-      <c r="B22" s="10" t="inlineStr">
+      <c r="K21" s="13" t="inlineStr"/>
+      <c r="L21" s="15" t="n"/>
+      <c r="M21" s="15" t="n"/>
+      <c r="N21" s="15" t="n"/>
+      <c r="O21" s="15" t="n"/>
+      <c r="P21" s="15" t="n"/>
+      <c r="Q21" s="15" t="n"/>
+    </row>
+    <row r="22" ht="188" customHeight="1">
+      <c r="B22" s="11" t="inlineStr">
         <is>
           <t>EN1(a)</t>
         </is>
       </c>
-      <c r="C22" s="11" t="inlineStr">
+      <c r="C22" s="12" t="inlineStr">
         <is>
           <t>Enablers</t>
         </is>
       </c>
-      <c r="D22" s="11" t="inlineStr">
+      <c r="D22" s="12" t="inlineStr">
         <is>
           <t>Enablers</t>
         </is>
       </c>
-      <c r="E22" s="11" t="inlineStr">
+      <c r="E22" s="12" t="inlineStr">
         <is>
           <t>Evidence of sustainability outcomes informed by Indigenous knowledges</t>
         </is>
       </c>
-      <c r="F22" s="12" t="inlineStr">
-        <is>
-          <t>In end-2025 reporting your faculty reported on the related SP2030 target 6a (click the ref in Column H to see it in full in Tab 3). Please build on this rather than repeating it, focusing on what is new in 2026.
-Please give any examples of activity in your faculty (education, research, engagement or operations) where Indigenous knowledges informed a sustainability outcome. Describe the activity, how Indigenous knowledges were incorporated or co-created and with whom, and the result. Please confirm that appropriate permissions are in place for sharing.</t>
-        </is>
-      </c>
-      <c r="G22" s="12" t="inlineStr">
+      <c r="F22" s="13" t="inlineStr">
+        <is>
+          <t>Please give any examples of activity in your faculty (education, research, engagement or operations) where Indigenous knowledges informed a sustainability outcome. Describe the activity, how Indigenous knowledges were incorporated or co-created and with whom, and the result. Please confirm that appropriate permissions are in place for sharing.
+In end-2025 reporting your faculty reported on the related SP2030 target 6a (click the ref in Column H to see it in full in Tab 3).</t>
+        </is>
+      </c>
+      <c r="G22" s="13" t="inlineStr">
         <is>
           <t>We will report on the ways Indigenous knowledges inform sustainability activities across the University, and develop selected examples into case studies with appropriate permissions.</t>
         </is>
       </c>
-      <c r="H22" s="13" t="inlineStr">
+      <c r="H22" s="14" t="inlineStr">
         <is>
           <t>6a
 → view SR25 response</t>
         </is>
       </c>
-      <c r="I22" s="12" t="inlineStr">
+      <c r="I22" s="13" t="inlineStr">
         <is>
           <t>Partially met</t>
         </is>
       </c>
-      <c r="J22" s="12" t="inlineStr">
+      <c r="J22" s="13" t="inlineStr">
         <is>
           <t>The Faculty of Science strategy has a specific goal of "Establish Indigenous lead caring for
 country course and resources " which sits under the theme of Living Sustaianbly. 
@@ -1200,59 +1335,59 @@
 Robyn Schofield working with Murujuga Rock Art Monitoring Program and being part of the Australian delegation that saw the inscription of Murujuga as a UN World Hertiage site in 2025 is one example.</t>
         </is>
       </c>
-      <c r="K22" s="12" t="inlineStr"/>
-      <c r="L22" s="14" t="n"/>
-      <c r="M22" s="14" t="n"/>
-      <c r="N22" s="14" t="n"/>
-      <c r="O22" s="14" t="n"/>
-      <c r="P22" s="14" t="n"/>
-      <c r="Q22" s="14" t="n"/>
-    </row>
-    <row r="23" ht="254" customHeight="1">
-      <c r="B23" s="10" t="inlineStr">
+      <c r="K22" s="13" t="inlineStr"/>
+      <c r="L22" s="15" t="n"/>
+      <c r="M22" s="15" t="n"/>
+      <c r="N22" s="15" t="n"/>
+      <c r="O22" s="15" t="n"/>
+      <c r="P22" s="15" t="n"/>
+      <c r="Q22" s="15" t="n"/>
+    </row>
+    <row r="23" ht="220" customHeight="1">
+      <c r="B23" s="11" t="inlineStr">
         <is>
           <t>EN1(b)</t>
         </is>
       </c>
-      <c r="C23" s="11" t="inlineStr">
+      <c r="C23" s="12" t="inlineStr">
         <is>
           <t>Enablers</t>
         </is>
       </c>
-      <c r="D23" s="11" t="inlineStr">
+      <c r="D23" s="12" t="inlineStr">
         <is>
           <t>Enablers</t>
         </is>
       </c>
-      <c r="E23" s="11" t="inlineStr">
+      <c r="E23" s="12" t="inlineStr">
         <is>
           <t>Living laboratories enabling applied learning, research and operational sustainability outcomes</t>
         </is>
       </c>
-      <c r="F23" s="12" t="inlineStr">
-        <is>
-          <t>In end-2025 reporting your faculty reported on the related SP2030 target 2a (click the ref in Column H to see it in full in Tab 3). Please build on this rather than repeating it, focusing on what is new in 2026.
-Please give any examples of sustainability-related living labs operating within your faculty in 2026 – their activities, who is involved (students, researchers, operational staff) and their outputs, outcomes or impact.
-Please note we will approach living labs funded through the Campus Living Lab Accelerator Program (CLLAP) separately.</t>
-        </is>
-      </c>
-      <c r="G23" s="12" t="inlineStr">
-        <is>
-          <t>We will share examples of sustainability-related living labs from across the University in the 2026 Sustainability Report, alongside CLLAP projects reported by CI&amp;S.</t>
-        </is>
-      </c>
-      <c r="H23" s="13" t="inlineStr">
+      <c r="F23" s="13" t="inlineStr">
+        <is>
+          <t>Please give any examples of sustainability-related living labs operating within your faculty in 2026 – their activities, who is involved (students, researchers, operational staff) and their outputs, outcomes or impact.
+Please note, we will collect case studies on Campus Living Lab Accelerator Program projects directly from project owners - no need to include these.
+In end-2025 reporting your faculty reported on the related SP2030 target 2a (click the ref in Column H to see it in full in Tab 3).</t>
+        </is>
+      </c>
+      <c r="G23" s="13" t="inlineStr">
+        <is>
+          <t>We will share examples of sustainability-related living labs from across the University in the 2026 Sustainability Report, alongside Campus Living Lab Accelerator Program case studies collected directly from project owners.</t>
+        </is>
+      </c>
+      <c r="H23" s="14" t="inlineStr">
         <is>
           <t>2a
 → view SR25 response</t>
         </is>
       </c>
-      <c r="I23" s="12" t="inlineStr">
+      <c r="I23" s="13" t="inlineStr">
         <is>
           <t>Partially met</t>
         </is>
       </c>
-      <c r="J23" s="12" t="inlineStr">
+      <c r="J23" s="13" t="inlineStr">
         <is>
           <t>The faculty has many projects that can be considered living labs. A centralised approach is required to document them.
 2025 examples include how the undergraduate chemistry teaching laboratories redesigned their practicals to use less reagents and safer chemicals to achieve the same learning outcomes.
@@ -1260,75 +1395,75 @@
 SAFES have worked on Indigenous food gardens and have an Indigenous food guide and there are examples of urban and woodland greening that serve as best practice examples across Australia</t>
         </is>
       </c>
-      <c r="K23" s="12" t="inlineStr">
+      <c r="K23" s="13" t="inlineStr">
         <is>
           <t>https://www.unimelb.edu.au/newsroom/news/2024/october/native-harvest-cookbook-aims-to-put-indigenous-food-in-every-aussie-kitchen
 https://theconversation.com/we-planted-two-woody-meadows-a-decade-ago-to-see-what-would-thrive-now-the-concept-is-popular-across-australia-269611</t>
         </is>
       </c>
-      <c r="L23" s="14" t="n"/>
-      <c r="M23" s="14" t="n"/>
-      <c r="N23" s="14" t="n"/>
-      <c r="O23" s="14" t="n"/>
-      <c r="P23" s="14" t="n"/>
-      <c r="Q23" s="14" t="n"/>
-    </row>
-    <row r="24" ht="188" customHeight="1">
-      <c r="B24" s="10" t="inlineStr">
+      <c r="L23" s="15" t="n"/>
+      <c r="M23" s="15" t="n"/>
+      <c r="N23" s="15" t="n"/>
+      <c r="O23" s="15" t="n"/>
+      <c r="P23" s="15" t="n"/>
+      <c r="Q23" s="15" t="n"/>
+    </row>
+    <row r="24" ht="154" customHeight="1">
+      <c r="B24" s="11" t="inlineStr">
         <is>
           <t>EN1(c)</t>
         </is>
       </c>
-      <c r="C24" s="11" t="inlineStr">
+      <c r="C24" s="12" t="inlineStr">
         <is>
           <t>Enablers</t>
         </is>
       </c>
-      <c r="D24" s="11" t="inlineStr">
+      <c r="D24" s="12" t="inlineStr">
         <is>
           <t>Enablers</t>
         </is>
       </c>
-      <c r="E24" s="11" t="inlineStr">
+      <c r="E24" s="12" t="inlineStr">
         <is>
           <t>Coordinated internal engagement and external partnerships contributing to delivery of sustainability outcomes across priority areas.</t>
         </is>
       </c>
-      <c r="F24" s="12" t="inlineStr">
-        <is>
-          <t>In end-2025 reporting your faculty reported on the related SP2030 target 3a(ii) (click the ref in Column H to see it in full in Tab 3). Please build on this rather than repeating it, focusing on what is new in 2026.
-Please list the key sustainability-focused communities of practice, internal networks or external partnerships active in your faculty in 2026 (name, partners, priority area), and give any examples of activity that contributed to a Sustainability 2030 outcome.</t>
-        </is>
-      </c>
-      <c r="G24" s="12" t="inlineStr">
+      <c r="F24" s="13" t="inlineStr">
+        <is>
+          <t>Please list the key sustainability-focused communities of practice, internal networks or external partnerships active in your faculty in 2026 (name, partners, priority area), and give any examples of activity that contributed to a Sustainability 2030 outcome.
+In end-2025 reporting your faculty reported on the related SP2030 target 3a(ii) (click the ref in Column H to see it in full in Tab 3).</t>
+        </is>
+      </c>
+      <c r="G24" s="13" t="inlineStr">
         <is>
           <t>We will report on internal engagement and partnerships contributing to Sustainability 2030 outcomes, and update our record of sustainability-focused communities of practice and contacts across the University.</t>
         </is>
       </c>
-      <c r="H24" s="13" t="inlineStr">
+      <c r="H24" s="14" t="inlineStr">
         <is>
           <t>3a(ii)
 → view SR25 response</t>
         </is>
       </c>
-      <c r="I24" s="12" t="inlineStr">
+      <c r="I24" s="13" t="inlineStr">
         <is>
           <t>Met or exceeded</t>
         </is>
       </c>
-      <c r="J24" s="12" t="inlineStr">
+      <c r="J24" s="13" t="inlineStr">
         <is>
           <t>The Associate/Assistant Deans of Sustainability exist in every faculty. While we interface with teaching, the DVCA, and A/Ds for UG and Postgraduate teaching are where the embedding of sustainability in formal learning outcomes occurs.
 In the FoS the UG Chemistry laboratory sustainability upgrades is a great example of embedding sustainability early in learning for students.</t>
         </is>
       </c>
-      <c r="K24" s="12" t="inlineStr"/>
-      <c r="L24" s="14" t="n"/>
-      <c r="M24" s="14" t="n"/>
-      <c r="N24" s="14" t="n"/>
-      <c r="O24" s="14" t="n"/>
-      <c r="P24" s="14" t="n"/>
-      <c r="Q24" s="14" t="n"/>
+      <c r="K24" s="13" t="inlineStr"/>
+      <c r="L24" s="15" t="n"/>
+      <c r="M24" s="15" t="n"/>
+      <c r="N24" s="15" t="n"/>
+      <c r="O24" s="15" t="n"/>
+      <c r="P24" s="15" t="n"/>
+      <c r="Q24" s="15" t="n"/>
     </row>
     <row r="25"/>
   </sheetData>
@@ -1355,6 +1490,7 @@
     <hyperlink ref="H24" location="'3. SR25 responses'!B10"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -1364,7 +1500,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:R12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -1377,104 +1513,148 @@
     <col width="22" customWidth="1" min="8" max="8"/>
     <col width="22" customWidth="1" min="9" max="9"/>
     <col width="30" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="13" customWidth="1" min="13" max="13"/>
+    <col width="13" customWidth="1" min="14" max="14"/>
+    <col width="13" customWidth="1" min="15" max="15"/>
+    <col width="13" customWidth="1" min="16" max="16"/>
+    <col width="13" customWidth="1" min="17" max="17"/>
+    <col width="13" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
-    <row r="1"/>
-    <row r="2" ht="39" customHeight="1">
-      <c r="B2" s="1" t="inlineStr">
+    <row r="1" ht="8" customHeight="1">
+      <c r="A1" s="1" t="n"/>
+      <c r="B1" s="1" t="n"/>
+      <c r="C1" s="1" t="n"/>
+      <c r="D1" s="1" t="n"/>
+      <c r="E1" s="1" t="n"/>
+      <c r="F1" s="1" t="n"/>
+      <c r="G1" s="1" t="n"/>
+      <c r="H1" s="1" t="n"/>
+      <c r="I1" s="1" t="n"/>
+      <c r="J1" s="1" t="n"/>
+      <c r="K1" s="1" t="n"/>
+      <c r="L1" s="1" t="n"/>
+      <c r="M1" s="1" t="n"/>
+      <c r="N1" s="1" t="n"/>
+      <c r="O1" s="1" t="n"/>
+      <c r="P1" s="1" t="n"/>
+      <c r="Q1" s="1" t="n"/>
+      <c r="R1" s="1" t="n"/>
+    </row>
+    <row r="2" ht="58" customHeight="1">
+      <c r="A2" s="1" t="n"/>
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>Highlighted stories (optional)</t>
         </is>
       </c>
+      <c r="C2" s="1" t="n"/>
+      <c r="D2" s="1" t="n"/>
+      <c r="E2" s="1" t="n"/>
+      <c r="F2" s="1" t="n"/>
+      <c r="G2" s="1" t="n"/>
+      <c r="H2" s="1" t="n"/>
+      <c r="I2" s="1" t="n"/>
+      <c r="J2" s="1" t="n"/>
+      <c r="K2" s="1" t="n"/>
+      <c r="L2" s="1" t="n"/>
+      <c r="M2" s="1" t="n"/>
+      <c r="N2" s="1" t="n"/>
+      <c r="O2" s="1" t="n"/>
+      <c r="P2" s="1" t="n"/>
+      <c r="Q2" s="1" t="n"/>
+      <c r="R2" s="1" t="n"/>
     </row>
     <row r="3"/>
     <row r="4"/>
     <row r="5" ht="22" customHeight="1">
-      <c r="B5" s="15" t="inlineStr">
+      <c r="B5" s="16" t="inlineStr">
         <is>
           <t>How to use this spreadsheet</t>
         </is>
       </c>
-      <c r="C5" s="16" t="inlineStr">
-        <is>
-          <t>Please share up to 3 stories from 2026 which highlight your faculty's/portfolio's sustainability progress and/or impact. These stories can directly relate to Sustainability 2030 targets and indicators, or sustainability more generally. Due: Tuesday 15 December 2026 (early submission helps us develop case studies).</t>
+      <c r="C5" s="17" t="inlineStr">
+        <is>
+          <t>Please share up to 3 stories from 2026 which highlight your faculty's/portfolio's sustainability progress and/or impact. These stories can directly relate to Sustainability 2030 targets and indicators, or sustainability more generally. Due: Thursday 24 December 2026 (Christmas shutdown) (early submission helps us develop case studies).</t>
         </is>
       </c>
     </row>
     <row r="6"/>
     <row r="7"/>
     <row r="8" ht="39" customHeight="1">
-      <c r="B8" s="17" t="inlineStr">
+      <c r="B8" s="18" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="C8" s="17" t="inlineStr">
+      <c r="C8" s="18" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="D8" s="17" t="inlineStr">
+      <c r="D8" s="18" t="inlineStr">
         <is>
           <t>Related Sustainability 2030 targets (optional)</t>
         </is>
       </c>
-      <c r="E8" s="17" t="inlineStr">
+      <c r="E8" s="18" t="inlineStr">
         <is>
           <t>Images and other media</t>
         </is>
       </c>
-      <c r="F8" s="17" t="inlineStr">
+      <c r="F8" s="18" t="inlineStr">
         <is>
           <t>Links and supporting documentation</t>
         </is>
       </c>
     </row>
     <row r="9" ht="90" customHeight="1">
-      <c r="B9" s="18" t="inlineStr"/>
-      <c r="C9" s="18" t="inlineStr">
+      <c r="B9" s="19" t="inlineStr"/>
+      <c r="C9" s="19" t="inlineStr">
         <is>
           <t>• Please include a brief description of a project or activity that has made a significant contribution to sustainability at the University (up to 250 words)
 • Summarise the benefits. Benefits may relate to operational outcomes, environmental/social outcomes, and sector benefits.</t>
         </is>
       </c>
-      <c r="D9" s="18" t="inlineStr"/>
-      <c r="E9" s="18" t="inlineStr">
+      <c r="D9" s="19" t="inlineStr"/>
+      <c r="E9" s="19" t="inlineStr">
         <is>
           <t>(link to OneDrive/SharePoint files or published online content preferred)</t>
         </is>
       </c>
-      <c r="F9" s="18" t="inlineStr"/>
+      <c r="F9" s="19" t="inlineStr"/>
     </row>
     <row r="10" ht="120" customHeight="1">
       <c r="A10" t="n">
         <v>1</v>
       </c>
-      <c r="B10" s="14" t="n"/>
-      <c r="C10" s="14" t="n"/>
-      <c r="D10" s="14" t="n"/>
-      <c r="E10" s="14" t="n"/>
-      <c r="F10" s="14" t="n"/>
+      <c r="B10" s="15" t="n"/>
+      <c r="C10" s="15" t="n"/>
+      <c r="D10" s="15" t="n"/>
+      <c r="E10" s="15" t="n"/>
+      <c r="F10" s="15" t="n"/>
     </row>
     <row r="11" ht="120" customHeight="1">
       <c r="A11" t="n">
         <v>2</v>
       </c>
-      <c r="B11" s="14" t="n"/>
-      <c r="C11" s="14" t="n"/>
-      <c r="D11" s="14" t="n"/>
-      <c r="E11" s="14" t="n"/>
-      <c r="F11" s="14" t="n"/>
+      <c r="B11" s="15" t="n"/>
+      <c r="C11" s="15" t="n"/>
+      <c r="D11" s="15" t="n"/>
+      <c r="E11" s="15" t="n"/>
+      <c r="F11" s="15" t="n"/>
     </row>
     <row r="12" ht="120" customHeight="1">
       <c r="A12" t="n">
         <v>3</v>
       </c>
-      <c r="B12" s="14" t="n"/>
-      <c r="C12" s="14" t="n"/>
-      <c r="D12" s="14" t="n"/>
-      <c r="E12" s="14" t="n"/>
-      <c r="F12" s="14" t="n"/>
+      <c r="B12" s="15" t="n"/>
+      <c r="C12" s="15" t="n"/>
+      <c r="D12" s="15" t="n"/>
+      <c r="E12" s="15" t="n"/>
+      <c r="F12" s="15" t="n"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="1"/>
@@ -1482,6 +1662,7 @@
     <mergeCell ref="C5:F6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -1491,7 +1672,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I16"/>
+  <dimension ref="A1:R16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -1503,101 +1684,146 @@
     <col width="60" customWidth="1" min="7" max="7"/>
     <col width="34" customWidth="1" min="8" max="8"/>
     <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="13" customWidth="1" min="13" max="13"/>
+    <col width="13" customWidth="1" min="14" max="14"/>
+    <col width="13" customWidth="1" min="15" max="15"/>
+    <col width="13" customWidth="1" min="16" max="16"/>
+    <col width="13" customWidth="1" min="17" max="17"/>
+    <col width="13" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
-    <row r="1"/>
-    <row r="2" ht="39" customHeight="1">
-      <c r="B2" s="1" t="inlineStr">
+    <row r="1" ht="8" customHeight="1">
+      <c r="A1" s="1" t="n"/>
+      <c r="B1" s="1" t="n"/>
+      <c r="C1" s="1" t="n"/>
+      <c r="D1" s="1" t="n"/>
+      <c r="E1" s="1" t="n"/>
+      <c r="F1" s="1" t="n"/>
+      <c r="G1" s="1" t="n"/>
+      <c r="H1" s="1" t="n"/>
+      <c r="I1" s="1" t="n"/>
+      <c r="J1" s="1" t="n"/>
+      <c r="K1" s="1" t="n"/>
+      <c r="L1" s="1" t="n"/>
+      <c r="M1" s="1" t="n"/>
+      <c r="N1" s="1" t="n"/>
+      <c r="O1" s="1" t="n"/>
+      <c r="P1" s="1" t="n"/>
+      <c r="Q1" s="1" t="n"/>
+      <c r="R1" s="1" t="n"/>
+    </row>
+    <row r="2" ht="58" customHeight="1">
+      <c r="A2" s="1" t="n"/>
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>Your SR25 responses – Faculty of Science</t>
         </is>
       </c>
+      <c r="C2" s="1" t="n"/>
+      <c r="D2" s="1" t="n"/>
+      <c r="E2" s="1" t="n"/>
+      <c r="F2" s="1" t="n"/>
+      <c r="G2" s="1" t="n"/>
+      <c r="H2" s="1" t="n"/>
+      <c r="I2" s="1" t="n"/>
+      <c r="J2" s="1" t="n"/>
+      <c r="K2" s="1" t="n"/>
+      <c r="L2" s="1" t="n"/>
+      <c r="M2" s="1" t="n"/>
+      <c r="N2" s="1" t="n"/>
+      <c r="O2" s="1" t="n"/>
+      <c r="P2" s="1" t="n"/>
+      <c r="Q2" s="1" t="n"/>
+      <c r="R2" s="1" t="n"/>
     </row>
     <row r="3" ht="32" customHeight="1">
-      <c r="B3" s="16" t="inlineStr">
+      <c r="B3" s="17" t="inlineStr">
         <is>
           <t>Your responses to the end-2025 reporting request, against the former Sustainability Plan 2030 (SP2030) targets. For reference only – please do not edit. Use the 'Back to request' links to return to the reporting template.</t>
         </is>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">
-      <c r="B4" s="19" t="inlineStr">
+      <c r="B4" s="20" t="inlineStr">
         <is>
           <t>← Back to request</t>
         </is>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1">
-      <c r="B5" s="20" t="inlineStr">
+      <c r="B5" s="21" t="inlineStr">
         <is>
           <t>SCI</t>
         </is>
       </c>
     </row>
     <row r="6" ht="42" customHeight="1">
-      <c r="B6" s="7" t="inlineStr">
+      <c r="B6" s="8" t="inlineStr">
         <is>
           <t>SR25 ref</t>
         </is>
       </c>
-      <c r="C6" s="7" t="inlineStr">
+      <c r="C6" s="8" t="inlineStr">
         <is>
           <t>SP2030 target</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="D6" s="8" t="inlineStr">
         <is>
           <t>2025 reporting request</t>
         </is>
       </c>
-      <c r="E6" s="7" t="inlineStr">
+      <c r="E6" s="8" t="inlineStr">
         <is>
           <t>Confirmed end-2025 status</t>
         </is>
       </c>
-      <c r="F6" s="7" t="inlineStr">
+      <c r="F6" s="8" t="inlineStr">
         <is>
           <t>OPTION 1: Target-level reporting</t>
         </is>
       </c>
-      <c r="G6" s="7" t="inlineStr">
+      <c r="G6" s="8" t="inlineStr">
         <is>
           <t>OPTION 2: Indicator-level reporting</t>
         </is>
       </c>
-      <c r="H6" s="7" t="inlineStr">
+      <c r="H6" s="8" t="inlineStr">
         <is>
           <t>Supporting information/comments</t>
         </is>
       </c>
-      <c r="I6" s="7" t="inlineStr">
+      <c r="I6" s="8" t="inlineStr">
         <is>
           <t>Related SR26 indicator(s)</t>
         </is>
       </c>
     </row>
     <row r="7" ht="303" customHeight="1">
-      <c r="B7" s="10" t="inlineStr">
+      <c r="B7" s="11" t="inlineStr">
         <is>
           <t>1a(i)</t>
         </is>
       </c>
-      <c r="C7" s="12" t="inlineStr">
+      <c r="C7" s="13" t="inlineStr">
         <is>
           <t>The University is certified carbon neutral by 2025</t>
         </is>
       </c>
-      <c r="D7" s="12" t="inlineStr">
+      <c r="D7" s="13" t="inlineStr">
         <is>
           <t>Comment on progress to reduce air travel emissions in the faculty</t>
         </is>
       </c>
-      <c r="E7" s="12" t="inlineStr">
+      <c r="E7" s="13" t="inlineStr">
         <is>
           <t>Met or exceeded</t>
         </is>
       </c>
-      <c r="F7" s="12" t="inlineStr">
+      <c r="F7" s="13" t="inlineStr">
         <is>
           <t>Provide commentary with reference to data in the Flights dashboard (link in Column O)
 Science:
@@ -1608,47 +1834,47 @@
 2025 emissions are tracking at  3312 tCO2e for science - this would again achieve a 10% reduction from 2019 emissions (target: &lt;3547 tCO2e). However, the emission intensity just from flights is higher than the goal of 2.7tCO2eq per person for total workplace emissions to be in line with Paris goals.</t>
         </is>
       </c>
-      <c r="G7" s="12" t="inlineStr">
+      <c r="G7" s="13" t="inlineStr">
         <is>
           <t>For context: In order to have a reasonable chance of staying below 2oC the per capita carbon emissions per year should be below ~8.2 tCO2eq per person per year (calculated from total 3700Gt CO2 eq budget to 2050 and assuming 9 billion people on Earth). As time at work consistutes about 1/3 of a person's life this gives ~2.7 tCO2eq per person would be a scientifically based target for total workplace emissions (including flights). Note: in 2023 Australians emitted ~14.5 tCO2eq per person.
  [link 3700 GtCO2eq target: https://www.climatechangeauthority.gov.au/sites/default/files/Targets%20and%20Progress%20Review%20Final%20Report_Chapter%203.pdf]</t>
         </is>
       </c>
-      <c r="H7" s="12" t="inlineStr">
+      <c r="H7" s="13" t="inlineStr">
         <is>
           <t>https://app.powerbi.com/links/SI8xYFLga4?ctid=0e5bf3cf-1ff4-46b7-9176-52c538c22a4d&amp;pbi_source=linkShare&amp;bookmarkGuid=499326eb-68f1-43e0-a3e6-0f252ee44ccb</t>
         </is>
       </c>
-      <c r="I7" s="12" t="inlineStr"/>
+      <c r="I7" s="13" t="inlineStr"/>
     </row>
     <row r="8" ht="237" customHeight="1">
-      <c r="B8" s="10" t="inlineStr">
+      <c r="B8" s="11" t="inlineStr">
         <is>
           <t>2a</t>
         </is>
       </c>
-      <c r="C8" s="12" t="inlineStr">
+      <c r="C8" s="13" t="inlineStr">
         <is>
           <t>The University has curated living labs covering the priority areas of this Plan</t>
         </is>
       </c>
-      <c r="D8" s="12" t="inlineStr">
+      <c r="D8" s="13" t="inlineStr">
         <is>
           <t>Please provide a case study of a living lab which operates within the faculty/portfolio, including a description of its activities and impact. 
 Please note we will approach living labs funded through the Campus Living Lab Accelerator program (CLLAP) separately report on their activities.</t>
         </is>
       </c>
-      <c r="E8" s="12" t="inlineStr">
+      <c r="E8" s="13" t="inlineStr">
         <is>
           <t>Partially met</t>
         </is>
       </c>
-      <c r="F8" s="12" t="inlineStr">
+      <c r="F8" s="13" t="inlineStr">
         <is>
           <t>The faculty has many projects that can be considered living labs. A centralised approach is required to document them.</t>
         </is>
       </c>
-      <c r="G8" s="12" t="inlineStr">
+      <c r="G8" s="13" t="inlineStr">
         <is>
           <t xml:space="preserve">
 2025 examples include how the undergraduate chemistry teaching laboratories redesigned their practicals to use less reagents and safer chemicals to achieve the same learning outcomes.
@@ -1656,159 +1882,159 @@
 SAFES have worked on Indigenous food gardens and have an Indigenous food guide and there are examples of urban and woodland greening that serve as best practice examples across Australia</t>
         </is>
       </c>
-      <c r="H8" s="12" t="inlineStr">
+      <c r="H8" s="13" t="inlineStr">
         <is>
           <t>https://www.unimelb.edu.au/newsroom/news/2024/october/native-harvest-cookbook-aims-to-put-indigenous-food-in-every-aussie-kitchen
 https://theconversation.com/we-planted-two-woody-meadows-a-decade-ago-to-see-what-would-thrive-now-the-concept-is-popular-across-australia-269611</t>
         </is>
       </c>
-      <c r="I8" s="12" t="inlineStr">
+      <c r="I8" s="13" t="inlineStr">
         <is>
           <t>TR1(a), EN1(b)</t>
         </is>
       </c>
     </row>
     <row r="9" ht="237" customHeight="1">
-      <c r="B9" s="10" t="inlineStr">
+      <c r="B9" s="11" t="inlineStr">
         <is>
           <t>3a(i)</t>
         </is>
       </c>
-      <c r="C9" s="12" t="inlineStr">
+      <c r="C9" s="13" t="inlineStr">
         <is>
           <t>The University's Academic Divisions and portfolios support and learn from each other to embed sustainability in practice and in learning – formal, non-formal and informal</t>
         </is>
       </c>
-      <c r="D9" s="12" t="inlineStr">
+      <c r="D9" s="13" t="inlineStr">
         <is>
           <t>Please update data on sustainability-focused staff in the faculty/portfolio provided in the previous reporting period (additional staff/those who have left the University) (see Columns G [2024] and J [mid-2025])</t>
         </is>
       </c>
-      <c r="E9" s="12" t="inlineStr">
+      <c r="E9" s="13" t="inlineStr">
         <is>
           <t>Met or exceeded</t>
         </is>
       </c>
-      <c r="F9" s="12" t="inlineStr">
+      <c r="F9" s="13" t="inlineStr">
         <is>
           <t>2025 saw the faculty of science develop a strategy - with goals in sustainability detailed here: https://staff.unimelb.edu.au/science/temporary-assets-and-links/Draft-FoS-Strategic-Priorities-All-Staff-Forum-August-2025.pdf (not to be shared externally)
 We are the custodian faculty for the Melbourne Biodiversity Institute and Melbourne Energy Institute, we also contribute to Melbourne climate futures.
 Several of our researchers are lead authors under the IPCC assessment report 7: https://www.unimelb.edu.au/newsroom/news/2025/august/university-of-melbourne-researchers-contributing-to-global-climate-report</t>
         </is>
       </c>
-      <c r="G9" s="12" t="inlineStr">
+      <c r="G9" s="13" t="inlineStr">
         <is>
           <t>The faculty of science has sustainability focused staff that cover all of the SDGs with 590 staff members producing more than 4 outputs that fall under the SDG framework (8630 research outputs). 
 With a total of 954 academic staff members  in the Faculty of Science (857 FTE) -  62% (69% when considering FTE) of our staff have significant SDG aligned research outputs (&gt;4 outputs)</t>
         </is>
       </c>
-      <c r="H9" s="12" t="inlineStr">
+      <c r="H9" s="13" t="inlineStr">
         <is>
           <t>https://app.powerbi.com/groups/me/reports/10687142-d5e8-46ef-b6f9-3adbbe5950c9/7913ae78325b04001d16?ctid=0e5bf3cf-1ff4-46b7-9176-52c538c22a4d&amp;experience=power-bi</t>
         </is>
       </c>
-      <c r="I9" s="12" t="inlineStr"/>
+      <c r="I9" s="13" t="inlineStr"/>
     </row>
     <row r="10" ht="160" customHeight="1">
-      <c r="B10" s="10" t="inlineStr">
+      <c r="B10" s="11" t="inlineStr">
         <is>
           <t>3a(ii)</t>
         </is>
       </c>
-      <c r="C10" s="12" t="inlineStr">
+      <c r="C10" s="13" t="inlineStr">
         <is>
           <t>The University's Academic Divisions and portfolios support and learn from each other to embed sustainability in practice and in learning – formal, non-formal and informal</t>
         </is>
       </c>
-      <c r="D10" s="12" t="inlineStr">
+      <c r="D10" s="13" t="inlineStr">
         <is>
           <t>Please list sustainability-focused knowledge sharing activities or communities of practice active in the faculty/portfolio in 2025, and provide a short case study of one of these.</t>
         </is>
       </c>
-      <c r="E10" s="12" t="inlineStr">
+      <c r="E10" s="13" t="inlineStr">
         <is>
           <t>Met or exceeded</t>
         </is>
       </c>
-      <c r="F10" s="12" t="inlineStr">
+      <c r="F10" s="13" t="inlineStr">
         <is>
           <t>The Associate/Assistant Deans of Sustainability exist in every faculty. While we interface with teaching, the DVCA, and A/Ds for UG and Postgraduate teaching are where the embedding of sustainability in formal learning outcomes occurs.</t>
         </is>
       </c>
-      <c r="G10" s="12" t="inlineStr">
+      <c r="G10" s="13" t="inlineStr">
         <is>
           <t>In the FoS the UG Chemistry laboratory sustainability upgrades is a great example of embedding sustainability early in learning for students.</t>
         </is>
       </c>
-      <c r="H10" s="12" t="inlineStr"/>
-      <c r="I10" s="12" t="inlineStr">
+      <c r="H10" s="13" t="inlineStr"/>
+      <c r="I10" s="13" t="inlineStr">
         <is>
           <t>EN1(c)</t>
         </is>
       </c>
     </row>
     <row r="11" ht="188" customHeight="1">
-      <c r="B11" s="10" t="inlineStr">
+      <c r="B11" s="11" t="inlineStr">
         <is>
           <t>3d(ii)</t>
         </is>
       </c>
-      <c r="C11" s="12" t="inlineStr">
+      <c r="C11" s="13" t="inlineStr">
         <is>
           <t>Academic and professional staff have increased their participation in and contribution to formal and non_x0002_formal learning to develop their general and role-specific sustainability skills</t>
         </is>
       </c>
-      <c r="D11" s="12" t="inlineStr">
+      <c r="D11" s="13" t="inlineStr">
         <is>
           <t>Have any staff participated in sustainability-focused professional development in 2025? If yes, what kinds of activities have staff participated in and how are these learnings being applied in the faculty/portfolio?
 Please note, there is no need to include data on participation in Green Impact ('Green teams'), as this is reported on centrally.</t>
         </is>
       </c>
-      <c r="E11" s="12" t="inlineStr">
+      <c r="E11" s="13" t="inlineStr">
         <is>
           <t>Partially met</t>
         </is>
       </c>
-      <c r="F11" s="12" t="inlineStr">
+      <c r="F11" s="13" t="inlineStr">
         <is>
           <t>The Associate/Assistant Deans of Sustainability is heavily involved cross-faculty programs to share ideas.</t>
         </is>
       </c>
-      <c r="G11" s="12" t="inlineStr">
+      <c r="G11" s="13" t="inlineStr">
         <is>
           <t>Suggest that the relevant trainme model is promoted centrally to all faculties: https://uomtrainme.elmotalent.com.au/learning/view-activity/833/scorm/2057</t>
         </is>
       </c>
-      <c r="H11" s="12" t="inlineStr"/>
-      <c r="I11" s="12" t="inlineStr"/>
+      <c r="H11" s="13" t="inlineStr"/>
+      <c r="I11" s="13" t="inlineStr"/>
     </row>
     <row r="12" ht="254" customHeight="1">
-      <c r="B12" s="10" t="inlineStr">
+      <c r="B12" s="11" t="inlineStr">
         <is>
           <t>4a(ii)</t>
         </is>
       </c>
-      <c r="C12" s="12" t="inlineStr">
+      <c r="C12" s="13" t="inlineStr">
         <is>
           <t>Sustainability is integrated into curriculum to an extent that conscientiously extends, beyond a base threshold, each discipline’s (and associated professions/industries’) knowledge of the helpful and harmful impacts it has for the environmental and human systems we depend on</t>
         </is>
       </c>
-      <c r="D12" s="12" t="inlineStr">
+      <c r="D12" s="13" t="inlineStr">
         <is>
           <t>Please describe any efforts within your faculty to embed sustainability in the curriculum in line with this target.</t>
         </is>
       </c>
-      <c r="E12" s="12" t="inlineStr">
+      <c r="E12" s="13" t="inlineStr">
         <is>
           <t>Met or exceeded</t>
         </is>
       </c>
-      <c r="F12" s="12" t="inlineStr">
+      <c r="F12" s="13" t="inlineStr">
         <is>
           <t>Sustainability, conservation, biodiversity are elements of most courses and majors within the FoS. Several additional courses are being considered at PG level in 2026</t>
         </is>
       </c>
-      <c r="G12" s="12" t="inlineStr">
+      <c r="G12" s="13" t="inlineStr">
         <is>
           <t>The FoS education strategy https://staff.unimelb.edu.au/science/learning-and-teaching-support/education-strategy has been developed with the following targets related to sustainability:  
 Under Innovate: "Maintain a focus on embedding the principles of sustainability in our teaching and learning practices, including ‘green’ and sustainable laboratory initiatives"; Future ready graduates: "Our programs will embed the concepts of sustainability set out in the University’s Sustainability
@@ -1817,42 +2043,42 @@
 With the 12 month implementation plan noting that: "Understanding our students’ carbon footprint is the first step towards incorporating sustainability in teaching and learning."</t>
         </is>
       </c>
-      <c r="H12" s="12" t="inlineStr"/>
-      <c r="I12" s="12" t="inlineStr">
+      <c r="H12" s="13" t="inlineStr"/>
+      <c r="I12" s="13" t="inlineStr">
         <is>
           <t>EE1(a)</t>
         </is>
       </c>
     </row>
     <row r="13" ht="369" customHeight="1">
-      <c r="B13" s="10" t="inlineStr">
+      <c r="B13" s="11" t="inlineStr">
         <is>
           <t>4b(i)</t>
         </is>
       </c>
-      <c r="C13" s="12" t="inlineStr">
+      <c r="C13" s="13" t="inlineStr">
         <is>
           <t>Graduates have increased capabilities to shape, lead 
 and succeed in the careers, communities and industries 
 of sustainable societies (year on year).</t>
         </is>
       </c>
-      <c r="D13" s="12" t="inlineStr">
+      <c r="D13" s="13" t="inlineStr">
         <is>
           <t>Is there any way to measure graduate outcomes related to sustainability in your faculty? If so, please describe.</t>
         </is>
       </c>
-      <c r="E13" s="12" t="inlineStr">
+      <c r="E13" s="13" t="inlineStr">
         <is>
           <t>Met or exceeded</t>
         </is>
       </c>
-      <c r="F13" s="12" t="inlineStr">
+      <c r="F13" s="13" t="inlineStr">
         <is>
           <t>As above. FoS is the custodial faculty for the Office of Environmental Programs</t>
         </is>
       </c>
-      <c r="G13" s="12" t="inlineStr">
+      <c r="G13" s="13" t="inlineStr">
         <is>
           <t>The BSc had 208 graduates across the following environmental/sustainability focussed majors:
 Zoology 40
@@ -1875,35 +2101,35 @@
 24 Master of Urban Horticulture</t>
         </is>
       </c>
-      <c r="H13" s="12" t="inlineStr"/>
-      <c r="I13" s="12" t="inlineStr">
+      <c r="H13" s="13" t="inlineStr"/>
+      <c r="I13" s="13" t="inlineStr">
         <is>
           <t>EE1(d)</t>
         </is>
       </c>
     </row>
     <row r="14" ht="303" customHeight="1">
-      <c r="B14" s="10" t="inlineStr">
+      <c r="B14" s="11" t="inlineStr">
         <is>
           <t>5b(i)</t>
         </is>
       </c>
-      <c r="C14" s="12" t="inlineStr">
+      <c r="C14" s="13" t="inlineStr">
         <is>
           <t>The highest quality research is conducted that contributes to knowledge, action, and impact across the disciplinary and interdisciplinary dimensions of sustainability.</t>
         </is>
       </c>
-      <c r="D14" s="12" t="inlineStr">
+      <c r="D14" s="13" t="inlineStr">
         <is>
           <t>Please update data on sustainability-, climate- or environment-focused research institutes, and provide a case study of their key research impacts in 2025.</t>
         </is>
       </c>
-      <c r="E14" s="12" t="inlineStr">
+      <c r="E14" s="13" t="inlineStr">
         <is>
           <t>Met or exceeded</t>
         </is>
       </c>
-      <c r="F14" s="12" t="inlineStr">
+      <c r="F14" s="13" t="inlineStr">
         <is>
           <t>QS rankings, SDG research outputs all attest to our strength in environmental and sustainable research. 
 We have a research strategy which has clear deliverables for sustainability, including a focus on several "Big Research Challenges" which directly relate to Sustainability https://staff.unimelb.edu.au/science/research/research-governance/research-strategy-2023-2030/FOS-Research-strategy-_INTRANET-LINKS-FIXED.pdf
@@ -1913,36 +2139,36 @@
 https://science.unimelb.edu.au/about/news/australia-and-the-pacific-islands-solidarity-in-a-time-of-climate-crisis/_nocache</t>
         </is>
       </c>
-      <c r="G14" s="12" t="inlineStr"/>
-      <c r="H14" s="12" t="inlineStr"/>
-      <c r="I14" s="12" t="inlineStr">
+      <c r="G14" s="13" t="inlineStr"/>
+      <c r="H14" s="13" t="inlineStr"/>
+      <c r="I14" s="13" t="inlineStr">
         <is>
           <t>TR2(a), TR2(d)</t>
         </is>
       </c>
     </row>
     <row r="15" ht="171" customHeight="1">
-      <c r="B15" s="10" t="inlineStr">
+      <c r="B15" s="11" t="inlineStr">
         <is>
           <t>5c(ii)</t>
         </is>
       </c>
-      <c r="C15" s="12" t="inlineStr">
+      <c r="C15" s="13" t="inlineStr">
         <is>
           <t>Researchers make considered decisions on the sustainability impact of their research practices and activities</t>
         </is>
       </c>
-      <c r="D15" s="12" t="inlineStr">
+      <c r="D15" s="13" t="inlineStr">
         <is>
           <t>Are there any efforts within the faculty to make research practices more sustainable? If so, please describe these activities</t>
         </is>
       </c>
-      <c r="E15" s="12" t="inlineStr">
+      <c r="E15" s="13" t="inlineStr">
         <is>
           <t>Partially met</t>
         </is>
       </c>
-      <c r="F15" s="12" t="inlineStr">
+      <c r="F15" s="13" t="inlineStr">
         <is>
           <t>We have a research strategy and implimentation plan which has clear deliverables for sustainability; 
 Link for Research strategy: https://staff.unimelb.edu.au/science/research/research-governance/research-strategy-2023-2030               
@@ -1950,36 +2176,36 @@
 which for example includes "Action 10. Improve sustainability of our core business practices"</t>
         </is>
       </c>
-      <c r="G15" s="12" t="inlineStr"/>
-      <c r="H15" s="12" t="inlineStr"/>
-      <c r="I15" s="12" t="inlineStr">
+      <c r="G15" s="13" t="inlineStr"/>
+      <c r="H15" s="13" t="inlineStr"/>
+      <c r="I15" s="13" t="inlineStr">
         <is>
           <t>TR3(a), TR3(b)</t>
         </is>
       </c>
     </row>
     <row r="16" ht="270" customHeight="1">
-      <c r="B16" s="10" t="inlineStr">
+      <c r="B16" s="11" t="inlineStr">
         <is>
           <t>6a</t>
         </is>
       </c>
-      <c r="C16" s="12" t="inlineStr">
+      <c r="C16" s="13" t="inlineStr">
         <is>
           <t>The University has an increased understanding of sustainability from an Indigenous perspective through co-created or Indigenous-led reciprocal learning</t>
         </is>
       </c>
-      <c r="D16" s="12" t="inlineStr">
+      <c r="D16" s="13" t="inlineStr">
         <is>
           <t>Please provide a case study on activities in the faculty (related to education, research or partnerships) which operate at the nexus between Indigenous knowledges and the western concept of 'sustainability'.</t>
         </is>
       </c>
-      <c r="E16" s="12" t="inlineStr">
+      <c r="E16" s="13" t="inlineStr">
         <is>
           <t>Partially met</t>
         </is>
       </c>
-      <c r="F16" s="12" t="inlineStr">
+      <c r="F16" s="13" t="inlineStr">
         <is>
           <t>The Faculty of Science strategy has a specific goal of "Establish Indigenous lead caring for
 country course and resources " which sits under the theme of Living Sustaianbly. 
@@ -1987,9 +2213,9 @@
 Robyn Schofield working with Murujuga Rock Art Monitoring Program and being part of the Australian delegation that saw the inscription of Murujuga as a UN World Hertiage site in 2025 is one example.</t>
         </is>
       </c>
-      <c r="G16" s="12" t="inlineStr"/>
-      <c r="H16" s="12" t="inlineStr"/>
-      <c r="I16" s="12" t="inlineStr">
+      <c r="G16" s="13" t="inlineStr"/>
+      <c r="H16" s="13" t="inlineStr"/>
+      <c r="I16" s="13" t="inlineStr">
         <is>
           <t>EN1(a)</t>
         </is>
@@ -2003,6 +2229,7 @@
     <hyperlink ref="B4" location="'1. Reporting template'!A1"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/output/faculty_requests/SCI - SR26 sustainability reporting request.xlsx
+++ b/output/faculty_requests/SCI - SR26 sustainability reporting request.xlsx
@@ -686,7 +686,7 @@
     <outlinePr summaryBelow="1" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R25"/>
+  <dimension ref="A1:R24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -989,46 +989,64 @@
       <c r="P16" s="15" t="n"/>
       <c r="Q16" s="15" t="n"/>
     </row>
-    <row r="17" ht="188" customHeight="1">
+    <row r="17" ht="270" customHeight="1">
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>EE1(b)</t>
+          <t>TR1(a)</t>
         </is>
       </c>
       <c r="C17" s="12" t="inlineStr">
         <is>
-          <t>Exceptional education</t>
+          <t>Transformational research</t>
         </is>
       </c>
       <c r="D17" s="12" t="inlineStr">
         <is>
-          <t>Provide our students with learning experiences that help them build the knowledge, skills and relationships to lead change for sustainable societies.</t>
+          <t>Utilise the expertise of the University’s researchers through mutually beneficial partnerships to help address the University’s operational sustainability challenges.</t>
         </is>
       </c>
       <c r="E17" s="12" t="inlineStr">
         <is>
-          <t>Pilots of possible approaches for understanding and developing students’ sustainability self-efficacy</t>
+          <t>Expert-reviewed evidence of researchers contributing to operational sustainability priorities through partnerships, advisory input, living labs, applied projects or decision-support</t>
         </is>
       </c>
       <c r="F17" s="13" t="inlineStr">
         <is>
-          <t>Has your faculty piloted or trialled any approach in 2026 to understand or build students' confidence and capability to act on sustainability (sustainability self-efficacy)? If yes, briefly describe the approach, participating cohort, what was learned and next steps. If not, please respond 'none in 2026' – this is a new indicator and a nil response is useful.
-We are aware of the Sustainability Strengths Compass Living Lab project (CLLAP) and will collect it separately.</t>
+          <t>Please give any examples from 2026 of researchers in your faculty contributing to the University's own operational sustainability challenges (e.g. advising on campus energy, biodiversity, waste or buildings; applied projects; decision-support tools). Briefly describe the operational challenge, the researchers' contribution, the University team involved and the result.
+Please note, we will collect case studies on Campus Living Lab Accelerator Program projects directly from project owners - no need to include these.
+In end-2025 reporting your faculty reported on the related SP2030 target 2a (click the ref in Column H to see it in full in Tab 3).</t>
         </is>
       </c>
       <c r="G17" s="13" t="inlineStr">
         <is>
-          <t>This is a new indicator. We will use responses to establish a baseline of how (and whether) faculties are understanding student sustainability self-efficacy, and report on early pilots in the 2026 Sustainability Report. A nil response is useful to us.</t>
-        </is>
-      </c>
-      <c r="H17" s="13" t="inlineStr">
-        <is>
-          <t>N/A – new indicator</t>
-        </is>
-      </c>
-      <c r="I17" s="13" t="inlineStr"/>
-      <c r="J17" s="13" t="inlineStr"/>
-      <c r="K17" s="13" t="inlineStr"/>
+          <t>We will report on examples of researchers helping solve the University's own operational sustainability challenges, alongside Campus Living Lab Accelerator Program case studies collected directly from project owners, and share them with operational teams to identify further collaboration.</t>
+        </is>
+      </c>
+      <c r="H17" s="14" t="inlineStr">
+        <is>
+          <t>2a
+→ view SR25 response</t>
+        </is>
+      </c>
+      <c r="I17" s="13" t="inlineStr">
+        <is>
+          <t>Partially met</t>
+        </is>
+      </c>
+      <c r="J17" s="13" t="inlineStr">
+        <is>
+          <t>The faculty has many projects that can be considered living labs. A centralised approach is required to document them.
+2025 examples include how the undergraduate chemistry teaching laboratories redesigned their practicals to use less reagents and safer chemicals to achieve the same learning outcomes.
+Physics have redesigned the X-band radiation lab electricity usage resulting in the saving of a very significant percentage of electricity costs. Biosciences and vet school both conducted -80oC freezer sample clean out and efficiency awareness work. This is part of green laboratory certification.
+SAFES have worked on Indigenous food gardens and have an Indigenous food guide and there are examples of urban and woodland greening that serve as best practice examples across Australia</t>
+        </is>
+      </c>
+      <c r="K17" s="13" t="inlineStr">
+        <is>
+          <t>https://www.unimelb.edu.au/newsroom/news/2024/october/native-harvest-cookbook-aims-to-put-indigenous-food-in-every-aussie-kitchen
+https://theconversation.com/we-planted-two-woody-meadows-a-decade-ago-to-see-what-would-thrive-now-the-concept-is-popular-across-australia-269611</t>
+        </is>
+      </c>
       <c r="L17" s="15" t="n"/>
       <c r="M17" s="15" t="n"/>
       <c r="N17" s="15" t="n"/>
@@ -1039,7 +1057,7 @@
     <row r="18" ht="270" customHeight="1">
       <c r="B18" s="11" t="inlineStr">
         <is>
-          <t>TR1(a)</t>
+          <t>TR2(a)</t>
         </is>
       </c>
       <c r="C18" s="12" t="inlineStr">
@@ -1049,51 +1067,48 @@
       </c>
       <c r="D18" s="12" t="inlineStr">
         <is>
-          <t>Utilise the expertise of the University’s researchers through mutually beneficial partnerships to help address the University’s operational sustainability challenges.</t>
+          <t>Deliver high-quality research and partnerships that contribute to sustainability outcomes and demonstrable societal benefit.</t>
         </is>
       </c>
       <c r="E18" s="12" t="inlineStr">
         <is>
-          <t>Expert-reviewed evidence of researchers contributing to operational sustainability priorities through partnerships, advisory input, living labs, applied projects or decision-support</t>
+          <t>Evidence of sustainability-related research impact across diverse pathways, could include policy, industry, community, practice, cultural and institutional outcomes</t>
         </is>
       </c>
       <c r="F18" s="13" t="inlineStr">
         <is>
-          <t>Please give any examples from 2026 of researchers in your faculty contributing to the University's own operational sustainability challenges (e.g. advising on campus energy, biodiversity, waste or buildings; applied projects; decision-support tools). Briefly describe the operational challenge, the researchers' contribution, the University team involved and the result.
-Please note, we will collect case studies on Campus Living Lab Accelerator Program projects directly from project owners - no need to include these.
-In end-2025 reporting your faculty reported on the related SP2030 target 2a (click the ref in Column H to see it in full in Tab 3).</t>
+          <t>Please give any examples from 2026 of sustainability-related research from your faculty that has had impact beyond academia – on policy, industry, community, practice, cultural or institutional outcomes. Briefly describe the research, the partner or user, and the resulting change or influence, with links (e.g. Pursuit articles, policy submissions, reports).
+We will source University-wide research metrics (e.g. SDG-mapped publications via SciVal) from Melbourne Research and Enterprise (MRE) – publication counts are not required.
+In end-2025 reporting your faculty reported on the related SP2030 target 5b(i) (click the ref in Column H to see it in full in Tab 3).</t>
         </is>
       </c>
       <c r="G18" s="13" t="inlineStr">
         <is>
-          <t>We will report on examples of researchers helping solve the University's own operational sustainability challenges, alongside Campus Living Lab Accelerator Program case studies collected directly from project owners, and share them with operational teams to identify further collaboration.</t>
+          <t>We will collate research impact examples across faculties to show the breadth of sustainability-related research impact in the Transformational research section of the 2026 Sustainability Report, complementing University-wide metrics from Melbourne Research and Enterprise (MRE).</t>
         </is>
       </c>
       <c r="H18" s="14" t="inlineStr">
         <is>
-          <t>2a
+          <t>5b(i)
 → view SR25 response</t>
         </is>
       </c>
       <c r="I18" s="13" t="inlineStr">
         <is>
-          <t>Partially met</t>
+          <t>Met or exceeded</t>
         </is>
       </c>
       <c r="J18" s="13" t="inlineStr">
         <is>
-          <t>The faculty has many projects that can be considered living labs. A centralised approach is required to document them.
-2025 examples include how the undergraduate chemistry teaching laboratories redesigned their practicals to use less reagents and safer chemicals to achieve the same learning outcomes.
-Physics have redesigned the X-band radiation lab electricity usage resulting in the saving of a very significant percentage of electricity costs. Biosciences and vet school both conducted -80oC freezer sample clean out and efficiency awareness work. This is part of green laboratory certification.
-SAFES have worked on Indigenous food gardens and have an Indigenous food guide and there are examples of urban and woodland greening that serve as best practice examples across Australia</t>
-        </is>
-      </c>
-      <c r="K18" s="13" t="inlineStr">
-        <is>
-          <t>https://www.unimelb.edu.au/newsroom/news/2024/october/native-harvest-cookbook-aims-to-put-indigenous-food-in-every-aussie-kitchen
-https://theconversation.com/we-planted-two-woody-meadows-a-decade-ago-to-see-what-would-thrive-now-the-concept-is-popular-across-australia-269611</t>
-        </is>
-      </c>
+          <t>QS rankings, SDG research outputs all attest to our strength in environmental and sustainable research. 
+We have a research strategy which has clear deliverables for sustainability, including a focus on several "Big Research Challenges" which directly relate to Sustainability https://staff.unimelb.edu.au/science/research/research-governance/research-strategy-2023-2030/FOS-Research-strategy-_INTRANET-LINKS-FIXED.pdf
+We had a Science at Melbourne Public lecture on environmental pollution: 
+https://science.unimelb.edu.au/about/news/dont-drink-the-water-or-breathe-the-air-pollution-and-solutions 
+and the climate crisis:
+https://science.unimelb.edu.au/about/news/australia-and-the-pacific-islands-solidarity-in-a-time-of-climate-crisis/_nocache</t>
+        </is>
+      </c>
+      <c r="K18" s="13" t="inlineStr"/>
       <c r="L18" s="15" t="n"/>
       <c r="M18" s="15" t="n"/>
       <c r="N18" s="15" t="n"/>
@@ -1101,10 +1116,10 @@
       <c r="P18" s="15" t="n"/>
       <c r="Q18" s="15" t="n"/>
     </row>
-    <row r="19" ht="270" customHeight="1">
+    <row r="19" ht="237" customHeight="1">
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>TR2(a)</t>
+          <t>TR2(d)</t>
         </is>
       </c>
       <c r="C19" s="12" t="inlineStr">
@@ -1119,19 +1134,19 @@
       </c>
       <c r="E19" s="12" t="inlineStr">
         <is>
-          <t>Evidence of sustainability-related research impact across diverse pathways, could include policy, industry, community, practice, cultural and institutional outcomes</t>
+          <t>Case-based evidence demonstrating how research has contributed to meaningful sustainability outcomes.</t>
         </is>
       </c>
       <c r="F19" s="13" t="inlineStr">
         <is>
-          <t>Please give any examples from 2026 of sustainability-related research from your faculty that has had impact beyond academia – on policy, industry, community, practice, cultural or institutional outcomes. Briefly describe the research, the partner or user, and the resulting change or influence, with links (e.g. Pursuit articles, policy submissions, reports).
-We will source University-wide research metrics (e.g. SDG-mapped publications via SciVal) from Melbourne Research and Enterprise (MRE) – publication counts are not required.
+          <t>Please give any examples of research activity from your faculty that has contributed to a meaningful sustainability outcome: the research, stakeholders involved, pathway to impact and evidence of the outcome. These can be the examples from TR2(a) described in more detail.
+We are also seeking examples from Melbourne Climate Futures, the Melbourne Biodiversity Institute and Strategic Communications.
 In end-2025 reporting your faculty reported on the related SP2030 target 5b(i) (click the ref in Column H to see it in full in Tab 3).</t>
         </is>
       </c>
       <c r="G19" s="13" t="inlineStr">
         <is>
-          <t>We will collate research impact examples across faculties to show the breadth of sustainability-related research impact in the Transformational research section of the 2026 Sustainability Report, complementing University-wide metrics from Melbourne Research and Enterprise (MRE).</t>
+          <t>We will select the strongest examples to develop as full research case studies for the 2026 Sustainability Report (we may contact you for more detail and images).</t>
         </is>
       </c>
       <c r="H19" s="14" t="inlineStr">
@@ -1163,10 +1178,10 @@
       <c r="P19" s="15" t="n"/>
       <c r="Q19" s="15" t="n"/>
     </row>
-    <row r="20" ht="237" customHeight="1">
+    <row r="20" ht="188" customHeight="1">
       <c r="B20" s="11" t="inlineStr">
         <is>
-          <t>TR2(d)</t>
+          <t>TR3(b)</t>
         </is>
       </c>
       <c r="C20" s="12" t="inlineStr">
@@ -1176,45 +1191,42 @@
       </c>
       <c r="D20" s="12" t="inlineStr">
         <is>
-          <t>Deliver high-quality research and partnerships that contribute to sustainability outcomes and demonstrable societal benefit.</t>
+          <t>Embed sustainability within research systems, processes, capability and culture, so research is conducted responsibly, efficiently and with reduced environmental impact.</t>
         </is>
       </c>
       <c r="E20" s="12" t="inlineStr">
         <is>
-          <t>Case-based evidence demonstrating how research has contributed to meaningful sustainability outcomes.</t>
+          <t>Demonstrated examples of more sustainable research practices in laboratories, fieldwork, procurement, travel or infrastructure use</t>
         </is>
       </c>
       <c r="F20" s="13" t="inlineStr">
         <is>
-          <t>Please give any examples of research activity from your faculty that has contributed to a meaningful sustainability outcome: the research, stakeholders involved, pathway to impact and evidence of the outcome. These can be the examples from TR2(a) described in more detail.
-We are also seeking examples from Melbourne Climate Futures, the Melbourne Biodiversity Institute and Strategic Communications.
-In end-2025 reporting your faculty reported on the related SP2030 target 5b(i) (click the ref in Column H to see it in full in Tab 3).</t>
+          <t>Are there any efforts within the faculty to make research practices more sustainable (e.g. green lab certification, equipment sharing, reduced research travel, sustainable fieldwork, sustainable procurement of research consumables)? If so, please give any examples and any evidence of uptake, resource savings or emissions reductions.
+In end-2025 reporting your faculty reported on the related SP2030 target 5c(ii) (click the ref in Column H to see it in full in Tab 3).</t>
         </is>
       </c>
       <c r="G20" s="13" t="inlineStr">
         <is>
-          <t>We will select the strongest examples to develop as full research case studies for the 2026 Sustainability Report (we may contact you for more detail and images).</t>
+          <t>We will report on ways the University is making research practices more sustainable in the 2026 Sustainability Report, and share practical examples (e.g. green labs) across faculties.</t>
         </is>
       </c>
       <c r="H20" s="14" t="inlineStr">
         <is>
-          <t>5b(i)
+          <t>5c(ii)
 → view SR25 response</t>
         </is>
       </c>
       <c r="I20" s="13" t="inlineStr">
         <is>
-          <t>Met or exceeded</t>
+          <t>Partially met</t>
         </is>
       </c>
       <c r="J20" s="13" t="inlineStr">
         <is>
-          <t>QS rankings, SDG research outputs all attest to our strength in environmental and sustainable research. 
-We have a research strategy which has clear deliverables for sustainability, including a focus on several "Big Research Challenges" which directly relate to Sustainability https://staff.unimelb.edu.au/science/research/research-governance/research-strategy-2023-2030/FOS-Research-strategy-_INTRANET-LINKS-FIXED.pdf
-We had a Science at Melbourne Public lecture on environmental pollution: 
-https://science.unimelb.edu.au/about/news/dont-drink-the-water-or-breathe-the-air-pollution-and-solutions 
-and the climate crisis:
-https://science.unimelb.edu.au/about/news/australia-and-the-pacific-islands-solidarity-in-a-time-of-climate-crisis/_nocache</t>
+          <t>We have a research strategy and implimentation plan which has clear deliverables for sustainability; 
+Link for Research strategy: https://staff.unimelb.edu.au/science/research/research-governance/research-strategy-2023-2030               
+Link for Implimentation Plan: https://staff.unimelb.edu.au/science/research/research-governance/research-strategy-2023-2030/Research-Strategy-Implementation-Plan_FINAL_12Dec24.pdf       
+which for example includes "Action 10. Improve sustainability of our core business practices"</t>
         </is>
       </c>
       <c r="K20" s="13" t="inlineStr"/>
@@ -1228,38 +1240,38 @@
     <row r="21" ht="188" customHeight="1">
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t>TR3(b)</t>
+          <t>EN1(a)</t>
         </is>
       </c>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>Transformational research</t>
+          <t>Enablers</t>
         </is>
       </c>
       <c r="D21" s="12" t="inlineStr">
         <is>
-          <t>Embed sustainability within research systems, processes, capability and culture, so research is conducted responsibly, efficiently and with reduced environmental impact.</t>
+          <t>Enablers</t>
         </is>
       </c>
       <c r="E21" s="12" t="inlineStr">
         <is>
-          <t>Demonstrated examples of more sustainable research practices in laboratories, fieldwork, procurement, travel or infrastructure use</t>
+          <t>Evidence of sustainability outcomes informed by Indigenous knowledges</t>
         </is>
       </c>
       <c r="F21" s="13" t="inlineStr">
         <is>
-          <t>Are there any efforts within the faculty to make research practices more sustainable (e.g. green lab certification, equipment sharing, reduced research travel, sustainable fieldwork, sustainable procurement of research consumables)? If so, please give any examples and any evidence of uptake, resource savings or emissions reductions.
-In end-2025 reporting your faculty reported on the related SP2030 target 5c(ii) (click the ref in Column H to see it in full in Tab 3).</t>
+          <t>Please give any examples of activity in your faculty (education, research, engagement or operations) where Indigenous knowledges informed a sustainability outcome. Describe the activity, how Indigenous knowledges were incorporated or co-created and with whom, and the result. Please confirm that appropriate permissions are in place for sharing.
+In end-2025 reporting your faculty reported on the related SP2030 target 6a (click the ref in Column H to see it in full in Tab 3).</t>
         </is>
       </c>
       <c r="G21" s="13" t="inlineStr">
         <is>
-          <t>We will report on ways the University is making research practices more sustainable in the 2026 Sustainability Report, and share practical examples (e.g. green labs) across faculties.</t>
+          <t>We will report on the ways Indigenous knowledges inform sustainability activities across the University, and develop selected examples into case studies with appropriate permissions.</t>
         </is>
       </c>
       <c r="H21" s="14" t="inlineStr">
         <is>
-          <t>5c(ii)
+          <t>6a
 → view SR25 response</t>
         </is>
       </c>
@@ -1270,10 +1282,10 @@
       </c>
       <c r="J21" s="13" t="inlineStr">
         <is>
-          <t>We have a research strategy and implimentation plan which has clear deliverables for sustainability; 
-Link for Research strategy: https://staff.unimelb.edu.au/science/research/research-governance/research-strategy-2023-2030               
-Link for Implimentation Plan: https://staff.unimelb.edu.au/science/research/research-governance/research-strategy-2023-2030/Research-Strategy-Implementation-Plan_FINAL_12Dec24.pdf       
-which for example includes "Action 10. Improve sustainability of our core business practices"</t>
+          <t>The Faculty of Science strategy has a specific goal of "Establish Indigenous lead caring for
+country course and resources " which sits under the theme of Living Sustaianbly. 
+The Indigenous Knowledges Institute and strong Indigenous A/D portfolio within the faculty of science continues to advance and uplift Indigenous knowledge, free, prior and informed consent for working on country, cultural awareness, co-designed research and cultural training - new Indigneous leadership and TrainMe - both online and face to face staff training great examples. 
+Robyn Schofield working with Murujuga Rock Art Monitoring Program and being part of the Australian delegation that saw the inscription of Murujuga as a UN World Hertiage site in 2025 is one example.</t>
         </is>
       </c>
       <c r="K21" s="13" t="inlineStr"/>
@@ -1284,10 +1296,10 @@
       <c r="P21" s="15" t="n"/>
       <c r="Q21" s="15" t="n"/>
     </row>
-    <row r="22" ht="188" customHeight="1">
+    <row r="22" ht="220" customHeight="1">
       <c r="B22" s="11" t="inlineStr">
         <is>
-          <t>EN1(a)</t>
+          <t>EN1(b)</t>
         </is>
       </c>
       <c r="C22" s="12" t="inlineStr">
@@ -1302,23 +1314,24 @@
       </c>
       <c r="E22" s="12" t="inlineStr">
         <is>
-          <t>Evidence of sustainability outcomes informed by Indigenous knowledges</t>
+          <t>Living laboratories enabling applied learning, research and operational sustainability outcomes</t>
         </is>
       </c>
       <c r="F22" s="13" t="inlineStr">
         <is>
-          <t>Please give any examples of activity in your faculty (education, research, engagement or operations) where Indigenous knowledges informed a sustainability outcome. Describe the activity, how Indigenous knowledges were incorporated or co-created and with whom, and the result. Please confirm that appropriate permissions are in place for sharing.
-In end-2025 reporting your faculty reported on the related SP2030 target 6a (click the ref in Column H to see it in full in Tab 3).</t>
+          <t>Please give any examples of sustainability-related living labs operating within your faculty in 2026 – their activities, who is involved (students, researchers, operational staff) and their outputs, outcomes or impact.
+Please note, we will collect case studies on Campus Living Lab Accelerator Program projects directly from project owners - no need to include these.
+In end-2025 reporting your faculty reported on the related SP2030 target 2a (click the ref in Column H to see it in full in Tab 3).</t>
         </is>
       </c>
       <c r="G22" s="13" t="inlineStr">
         <is>
-          <t>We will report on the ways Indigenous knowledges inform sustainability activities across the University, and develop selected examples into case studies with appropriate permissions.</t>
+          <t>We will share examples of sustainability-related living labs from across the University in the 2026 Sustainability Report, alongside Campus Living Lab Accelerator Program case studies collected directly from project owners.</t>
         </is>
       </c>
       <c r="H22" s="14" t="inlineStr">
         <is>
-          <t>6a
+          <t>2a
 → view SR25 response</t>
         </is>
       </c>
@@ -1329,13 +1342,18 @@
       </c>
       <c r="J22" s="13" t="inlineStr">
         <is>
-          <t>The Faculty of Science strategy has a specific goal of "Establish Indigenous lead caring for
-country course and resources " which sits under the theme of Living Sustaianbly. 
-The Indigenous Knowledges Institute and strong Indigenous A/D portfolio within the faculty of science continues to advance and uplift Indigenous knowledge, free, prior and informed consent for working on country, cultural awareness, co-designed research and cultural training - new Indigneous leadership and TrainMe - both online and face to face staff training great examples. 
-Robyn Schofield working with Murujuga Rock Art Monitoring Program and being part of the Australian delegation that saw the inscription of Murujuga as a UN World Hertiage site in 2025 is one example.</t>
-        </is>
-      </c>
-      <c r="K22" s="13" t="inlineStr"/>
+          <t>The faculty has many projects that can be considered living labs. A centralised approach is required to document them.
+2025 examples include how the undergraduate chemistry teaching laboratories redesigned their practicals to use less reagents and safer chemicals to achieve the same learning outcomes.
+Physics have redesigned the X-band radiation lab electricity usage resulting in the saving of a very significant percentage of electricity costs. Biosciences and vet school both conducted -80oC freezer sample clean out and efficiency awareness work. This is part of green laboratory certification.
+SAFES have worked on Indigenous food gardens and have an Indigenous food guide and there are examples of urban and woodland greening that serve as best practice examples across Australia</t>
+        </is>
+      </c>
+      <c r="K22" s="13" t="inlineStr">
+        <is>
+          <t>https://www.unimelb.edu.au/newsroom/news/2024/october/native-harvest-cookbook-aims-to-put-indigenous-food-in-every-aussie-kitchen
+https://theconversation.com/we-planted-two-woody-meadows-a-decade-ago-to-see-what-would-thrive-now-the-concept-is-popular-across-australia-269611</t>
+        </is>
+      </c>
       <c r="L22" s="15" t="n"/>
       <c r="M22" s="15" t="n"/>
       <c r="N22" s="15" t="n"/>
@@ -1343,10 +1361,10 @@
       <c r="P22" s="15" t="n"/>
       <c r="Q22" s="15" t="n"/>
     </row>
-    <row r="23" ht="220" customHeight="1">
+    <row r="23" ht="154" customHeight="1">
       <c r="B23" s="11" t="inlineStr">
         <is>
-          <t>EN1(b)</t>
+          <t>EN1(c)</t>
         </is>
       </c>
       <c r="C23" s="12" t="inlineStr">
@@ -1361,46 +1379,38 @@
       </c>
       <c r="E23" s="12" t="inlineStr">
         <is>
-          <t>Living laboratories enabling applied learning, research and operational sustainability outcomes</t>
+          <t>Coordinated internal engagement and external partnerships contributing to delivery of sustainability outcomes across priority areas.</t>
         </is>
       </c>
       <c r="F23" s="13" t="inlineStr">
         <is>
-          <t>Please give any examples of sustainability-related living labs operating within your faculty in 2026 – their activities, who is involved (students, researchers, operational staff) and their outputs, outcomes or impact.
-Please note, we will collect case studies on Campus Living Lab Accelerator Program projects directly from project owners - no need to include these.
-In end-2025 reporting your faculty reported on the related SP2030 target 2a (click the ref in Column H to see it in full in Tab 3).</t>
+          <t>Please list the key sustainability-focused communities of practice, internal networks or external partnerships active in your faculty in 2026 (name, partners, priority area), and give any examples of activity that contributed to a Sustainability 2030 outcome.
+In end-2025 reporting your faculty reported on the related SP2030 target 3a(ii) (click the ref in Column H to see it in full in Tab 3).</t>
         </is>
       </c>
       <c r="G23" s="13" t="inlineStr">
         <is>
-          <t>We will share examples of sustainability-related living labs from across the University in the 2026 Sustainability Report, alongside Campus Living Lab Accelerator Program case studies collected directly from project owners.</t>
+          <t>We will report on internal engagement and partnerships contributing to Sustainability 2030 outcomes, and update our record of sustainability-focused communities of practice and contacts across the University.</t>
         </is>
       </c>
       <c r="H23" s="14" t="inlineStr">
         <is>
-          <t>2a
+          <t>3a(ii)
 → view SR25 response</t>
         </is>
       </c>
       <c r="I23" s="13" t="inlineStr">
         <is>
-          <t>Partially met</t>
+          <t>Met or exceeded</t>
         </is>
       </c>
       <c r="J23" s="13" t="inlineStr">
         <is>
-          <t>The faculty has many projects that can be considered living labs. A centralised approach is required to document them.
-2025 examples include how the undergraduate chemistry teaching laboratories redesigned their practicals to use less reagents and safer chemicals to achieve the same learning outcomes.
-Physics have redesigned the X-band radiation lab electricity usage resulting in the saving of a very significant percentage of electricity costs. Biosciences and vet school both conducted -80oC freezer sample clean out and efficiency awareness work. This is part of green laboratory certification.
-SAFES have worked on Indigenous food gardens and have an Indigenous food guide and there are examples of urban and woodland greening that serve as best practice examples across Australia</t>
-        </is>
-      </c>
-      <c r="K23" s="13" t="inlineStr">
-        <is>
-          <t>https://www.unimelb.edu.au/newsroom/news/2024/october/native-harvest-cookbook-aims-to-put-indigenous-food-in-every-aussie-kitchen
-https://theconversation.com/we-planted-two-woody-meadows-a-decade-ago-to-see-what-would-thrive-now-the-concept-is-popular-across-australia-269611</t>
-        </is>
-      </c>
+          <t>The Associate/Assistant Deans of Sustainability exist in every faculty. While we interface with teaching, the DVCA, and A/Ds for UG and Postgraduate teaching are where the embedding of sustainability in formal learning outcomes occurs.
+In the FoS the UG Chemistry laboratory sustainability upgrades is a great example of embedding sustainability early in learning for students.</t>
+        </is>
+      </c>
+      <c r="K23" s="13" t="inlineStr"/>
       <c r="L23" s="15" t="n"/>
       <c r="M23" s="15" t="n"/>
       <c r="N23" s="15" t="n"/>
@@ -1408,64 +1418,7 @@
       <c r="P23" s="15" t="n"/>
       <c r="Q23" s="15" t="n"/>
     </row>
-    <row r="24" ht="154" customHeight="1">
-      <c r="B24" s="11" t="inlineStr">
-        <is>
-          <t>EN1(c)</t>
-        </is>
-      </c>
-      <c r="C24" s="12" t="inlineStr">
-        <is>
-          <t>Enablers</t>
-        </is>
-      </c>
-      <c r="D24" s="12" t="inlineStr">
-        <is>
-          <t>Enablers</t>
-        </is>
-      </c>
-      <c r="E24" s="12" t="inlineStr">
-        <is>
-          <t>Coordinated internal engagement and external partnerships contributing to delivery of sustainability outcomes across priority areas.</t>
-        </is>
-      </c>
-      <c r="F24" s="13" t="inlineStr">
-        <is>
-          <t>Please list the key sustainability-focused communities of practice, internal networks or external partnerships active in your faculty in 2026 (name, partners, priority area), and give any examples of activity that contributed to a Sustainability 2030 outcome.
-In end-2025 reporting your faculty reported on the related SP2030 target 3a(ii) (click the ref in Column H to see it in full in Tab 3).</t>
-        </is>
-      </c>
-      <c r="G24" s="13" t="inlineStr">
-        <is>
-          <t>We will report on internal engagement and partnerships contributing to Sustainability 2030 outcomes, and update our record of sustainability-focused communities of practice and contacts across the University.</t>
-        </is>
-      </c>
-      <c r="H24" s="14" t="inlineStr">
-        <is>
-          <t>3a(ii)
-→ view SR25 response</t>
-        </is>
-      </c>
-      <c r="I24" s="13" t="inlineStr">
-        <is>
-          <t>Met or exceeded</t>
-        </is>
-      </c>
-      <c r="J24" s="13" t="inlineStr">
-        <is>
-          <t>The Associate/Assistant Deans of Sustainability exist in every faculty. While we interface with teaching, the DVCA, and A/Ds for UG and Postgraduate teaching are where the embedding of sustainability in formal learning outcomes occurs.
-In the FoS the UG Chemistry laboratory sustainability upgrades is a great example of embedding sustainability early in learning for students.</t>
-        </is>
-      </c>
-      <c r="K24" s="13" t="inlineStr"/>
-      <c r="L24" s="15" t="n"/>
-      <c r="M24" s="15" t="n"/>
-      <c r="N24" s="15" t="n"/>
-      <c r="O24" s="15" t="n"/>
-      <c r="P24" s="15" t="n"/>
-      <c r="Q24" s="15" t="n"/>
-    </row>
-    <row r="25"/>
+    <row r="24"/>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="1"/>
   <mergeCells count="4">
@@ -1475,19 +1428,19 @@
     <mergeCell ref="B4:C8"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="P16:P24" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please select from the dropdown" type="list">
+    <dataValidation sqref="P16:P23" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please select from the dropdown" type="list">
       <formula1>=Lists!$C$2:$C$4</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
     <hyperlink ref="H16" location="'3. SR25 responses'!B12"/>
-    <hyperlink ref="H18" location="'3. SR25 responses'!B8"/>
+    <hyperlink ref="H17" location="'3. SR25 responses'!B8"/>
+    <hyperlink ref="H18" location="'3. SR25 responses'!B14"/>
     <hyperlink ref="H19" location="'3. SR25 responses'!B14"/>
-    <hyperlink ref="H20" location="'3. SR25 responses'!B14"/>
-    <hyperlink ref="H21" location="'3. SR25 responses'!B15"/>
-    <hyperlink ref="H22" location="'3. SR25 responses'!B16"/>
-    <hyperlink ref="H23" location="'3. SR25 responses'!B8"/>
-    <hyperlink ref="H24" location="'3. SR25 responses'!B10"/>
+    <hyperlink ref="H20" location="'3. SR25 responses'!B15"/>
+    <hyperlink ref="H21" location="'3. SR25 responses'!B16"/>
+    <hyperlink ref="H22" location="'3. SR25 responses'!B8"/>
+    <hyperlink ref="H23" location="'3. SR25 responses'!B10"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/output/faculty_requests/SCI - SR26 sustainability reporting request.xlsx
+++ b/output/faculty_requests/SCI - SR26 sustainability reporting request.xlsx
@@ -703,9 +703,9 @@
     <col width="48" customWidth="1" min="12" max="12"/>
     <col width="48" customWidth="1" min="13" max="13"/>
     <col width="30" customWidth="1" min="14" max="14"/>
-    <col width="30" customWidth="1" min="15" max="15"/>
-    <col width="20" customWidth="1" min="16" max="16"/>
-    <col width="24" customWidth="1" min="17" max="17"/>
+    <col width="36" customWidth="1" min="15" max="15"/>
+    <col width="13" customWidth="1" min="16" max="16"/>
+    <col width="13" customWidth="1" min="17" max="17"/>
     <col width="13" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
@@ -764,7 +764,8 @@
         <is>
           <t>• For each row below, describe progress towards the target (Column L) and/or respond to the 2026 reporting request (Column M)
 • Provide supporting information if required (Column N), including links to documents or images
-• Note the source of your information and any limitations (Column O), then confirm the information is accurate (Columns P–Q)
+• Note the source of your information, any limitations and the person closest to the data (Column O)
+• Please return the spreadsheet once it has been reviewed and confirmed by your area's senior lead
 • Where a related end-2025 target existed, click the ref in Column H to see your full SR25 response (Tab 3)
 • Use Tab 2 of this spreadsheet to highlight key sustainability stories (optional)
 • 2026 is a transition year: Sustainability 2030 launched ~20 October 2026, so report on activity across all of 2026 and any early actions since launch. No target status rating is requested this year.
@@ -803,7 +804,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="60" customHeight="1">
+    <row r="14" ht="42" customHeight="1">
       <c r="B14" s="8" t="inlineStr">
         <is>
           <t>Ref</t>
@@ -871,17 +872,7 @@
       </c>
       <c r="O14" s="9" t="inlineStr">
         <is>
-          <t>Data source and limitations</t>
-        </is>
-      </c>
-      <c r="P14" s="9" t="inlineStr">
-        <is>
-          <t>Data owner confirms information is accurate</t>
-        </is>
-      </c>
-      <c r="Q14" s="9" t="inlineStr">
-        <is>
-          <t>Confirmed by (name, role, date)</t>
+          <t>Data source, limitations and contact person</t>
         </is>
       </c>
     </row>
@@ -913,17 +904,7 @@
       </c>
       <c r="O15" s="10" t="inlineStr">
         <is>
-          <t>Where did this information come from (system, report, survey, person)? Note any gaps or limitations.</t>
-        </is>
-      </c>
-      <c r="P15" s="10" t="inlineStr">
-        <is>
-          <t>Select 'Yes' to confirm the information provided is accurate and can be used for reporting</t>
-        </is>
-      </c>
-      <c r="Q15" s="10" t="inlineStr">
-        <is>
-          <t>Name, role and date of the person confirming</t>
+          <t>Where did this information come from (system, report, survey)? Note any gaps or limitations, and the person closest to the data we can follow up with.</t>
         </is>
       </c>
     </row>
@@ -986,8 +967,6 @@
       <c r="M16" s="15" t="n"/>
       <c r="N16" s="15" t="n"/>
       <c r="O16" s="15" t="n"/>
-      <c r="P16" s="15" t="n"/>
-      <c r="Q16" s="15" t="n"/>
     </row>
     <row r="17" ht="270" customHeight="1">
       <c r="B17" s="11" t="inlineStr">
@@ -1051,8 +1030,6 @@
       <c r="M17" s="15" t="n"/>
       <c r="N17" s="15" t="n"/>
       <c r="O17" s="15" t="n"/>
-      <c r="P17" s="15" t="n"/>
-      <c r="Q17" s="15" t="n"/>
     </row>
     <row r="18" ht="270" customHeight="1">
       <c r="B18" s="11" t="inlineStr">
@@ -1113,8 +1090,6 @@
       <c r="M18" s="15" t="n"/>
       <c r="N18" s="15" t="n"/>
       <c r="O18" s="15" t="n"/>
-      <c r="P18" s="15" t="n"/>
-      <c r="Q18" s="15" t="n"/>
     </row>
     <row r="19" ht="237" customHeight="1">
       <c r="B19" s="11" t="inlineStr">
@@ -1175,8 +1150,6 @@
       <c r="M19" s="15" t="n"/>
       <c r="N19" s="15" t="n"/>
       <c r="O19" s="15" t="n"/>
-      <c r="P19" s="15" t="n"/>
-      <c r="Q19" s="15" t="n"/>
     </row>
     <row r="20" ht="188" customHeight="1">
       <c r="B20" s="11" t="inlineStr">
@@ -1234,8 +1207,6 @@
       <c r="M20" s="15" t="n"/>
       <c r="N20" s="15" t="n"/>
       <c r="O20" s="15" t="n"/>
-      <c r="P20" s="15" t="n"/>
-      <c r="Q20" s="15" t="n"/>
     </row>
     <row r="21" ht="188" customHeight="1">
       <c r="B21" s="11" t="inlineStr">
@@ -1293,8 +1264,6 @@
       <c r="M21" s="15" t="n"/>
       <c r="N21" s="15" t="n"/>
       <c r="O21" s="15" t="n"/>
-      <c r="P21" s="15" t="n"/>
-      <c r="Q21" s="15" t="n"/>
     </row>
     <row r="22" ht="220" customHeight="1">
       <c r="B22" s="11" t="inlineStr">
@@ -1358,8 +1327,6 @@
       <c r="M22" s="15" t="n"/>
       <c r="N22" s="15" t="n"/>
       <c r="O22" s="15" t="n"/>
-      <c r="P22" s="15" t="n"/>
-      <c r="Q22" s="15" t="n"/>
     </row>
     <row r="23" ht="154" customHeight="1">
       <c r="B23" s="11" t="inlineStr">
@@ -1384,13 +1351,13 @@
       </c>
       <c r="F23" s="13" t="inlineStr">
         <is>
-          <t>Please list the key sustainability-focused communities of practice, internal networks or external partnerships active in your faculty in 2026 (name, partners, priority area), and give any examples of activity that contributed to a Sustainability 2030 outcome.
+          <t>Please list the key sustainability-focused communities of practice, internal networks or external partnerships active in your faculty in 2026 (name, partners, priority area), and give any examples of activity that contributed to a sustainability outcome.
 In end-2025 reporting your faculty reported on the related SP2030 target 3a(ii) (click the ref in Column H to see it in full in Tab 3).</t>
         </is>
       </c>
       <c r="G23" s="13" t="inlineStr">
         <is>
-          <t>We will report on internal engagement and partnerships contributing to Sustainability 2030 outcomes, and update our record of sustainability-focused communities of practice and contacts across the University.</t>
+          <t>We will report on internal engagement and partnerships contributing to sustainability outcomes, and update our record of sustainability-focused communities of practice and contacts across the University.</t>
         </is>
       </c>
       <c r="H23" s="14" t="inlineStr">
@@ -1415,23 +1382,16 @@
       <c r="M23" s="15" t="n"/>
       <c r="N23" s="15" t="n"/>
       <c r="O23" s="15" t="n"/>
-      <c r="P23" s="15" t="n"/>
-      <c r="Q23" s="15" t="n"/>
     </row>
     <row r="24"/>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="1"/>
   <mergeCells count="4">
     <mergeCell ref="C13:G13"/>
-    <mergeCell ref="L13:Q13"/>
+    <mergeCell ref="L13:O13"/>
     <mergeCell ref="D4:G8"/>
     <mergeCell ref="B4:C8"/>
   </mergeCells>
-  <dataValidations count="1">
-    <dataValidation sqref="P16:P23" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please select from the dropdown" type="list">
-      <formula1>=Lists!$C$2:$C$4</formula1>
-    </dataValidation>
-  </dataValidations>
   <hyperlinks>
     <hyperlink ref="H16" location="'3. SR25 responses'!B12"/>
     <hyperlink ref="H17" location="'3. SR25 responses'!B8"/>
